--- a/NCD_Brand_Tagging.xlsx
+++ b/NCD_Brand_Tagging.xlsx
@@ -2,9 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17220" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" state="visible" r:id="rId1"/>
@@ -12,7 +11,7 @@
     <sheet name="New Staple Items" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1" iterateDelta="0.0001"/>
 </workbook>
 </file>
 
@@ -29,40 +28,47 @@
     </font>
     <font>
       <name val="Arial"/>
+      <family val="2"/>
       <b val="1"/>
-      <color rgb="00542916"/>
+      <color rgb="FF542916"/>
       <sz val="14"/>
     </font>
     <font>
       <name val="Arial"/>
-      <color rgb="002B241C"/>
+      <family val="2"/>
+      <color rgb="FF2B241C"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
-      <color rgb="002B241C"/>
+      <family val="2"/>
+      <color rgb="FF2B241C"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Arial"/>
+      <family val="2"/>
       <b val="1"/>
-      <color rgb="00542916"/>
+      <color rgb="FF542916"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Arial"/>
+      <family val="2"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Arial"/>
+      <family val="2"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
+      <family val="2"/>
       <i val="1"/>
-      <color rgb="00808080"/>
+      <color rgb="FF808080"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -75,14 +81,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2565C"/>
-        <bgColor rgb="00F2565C"/>
+        <fgColor rgb="FFF2565C"/>
+        <bgColor rgb="FFF2565C"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF9C4"/>
-        <bgColor rgb="00FFF9C4"/>
+        <fgColor rgb="FFFFF9C4"/>
+        <bgColor rgb="FFFFF9C4"/>
       </patternFill>
     </fill>
   </fills>
@@ -96,17 +102,18 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00D9D9D9"/>
+        <color rgb="FFD9D9D9"/>
       </left>
       <right style="thin">
-        <color rgb="00D9D9D9"/>
+        <color rgb="FFD9D9D9"/>
       </right>
       <top style="thin">
-        <color rgb="00D9D9D9"/>
+        <color rgb="FFD9D9D9"/>
       </top>
       <bottom style="thin">
-        <color rgb="00D9D9D9"/>
+        <color rgb="FFD9D9D9"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -149,7 +156,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -533,7 +540,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:A26"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
   </cols>
@@ -546,7 +553,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr"/>
+      <c r="A2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -570,7 +577,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr"/>
+      <c r="A6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -657,7 +664,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr"/>
+      <c r="A19" s="2" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
@@ -695,7 +702,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr"/>
+      <c r="A25" s="2" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
@@ -716,7 +723,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:J119"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
@@ -725,9 +732,7 @@
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="22" customWidth="1" min="6" max="6"/>
     <col width="30" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="8" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -806,7 +811,9 @@
           <t>1kg/Box</t>
         </is>
       </c>
-      <c r="F2" s="8" t="n"/>
+      <c r="F2" s="8" t="n">
+        <v>3</v>
+      </c>
       <c r="G2" s="8" t="inlineStr">
         <is>
           <t>yc</t>
@@ -846,7 +853,9 @@
           <t>1kg/Box</t>
         </is>
       </c>
-      <c r="F3" s="8" t="n"/>
+      <c r="F3" s="8" t="n">
+        <v>1</v>
+      </c>
       <c r="G3" s="8" t="inlineStr">
         <is>
           <t>yc</t>
@@ -1126,7 +1135,9 @@
           <t>1kg/Box</t>
         </is>
       </c>
-      <c r="F10" s="8" t="n"/>
+      <c r="F10" s="8" t="n">
+        <v>3</v>
+      </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
           <t>yc</t>
@@ -1166,7 +1177,9 @@
           <t>500g/Box</t>
         </is>
       </c>
-      <c r="F11" s="8" t="n"/>
+      <c r="F11" s="8" t="n">
+        <v>5</v>
+      </c>
       <c r="G11" s="8" t="inlineStr">
         <is>
           <t>yc</t>
@@ -1206,7 +1219,9 @@
           <t>500g/Box</t>
         </is>
       </c>
-      <c r="F12" s="8" t="n"/>
+      <c r="F12" s="8" t="n">
+        <v>5</v>
+      </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
           <t>yc</t>
@@ -1432,7 +1447,9 @@
           <t>ถ้วย</t>
         </is>
       </c>
-      <c r="F18" s="8" t="n"/>
+      <c r="F18" s="8" t="n">
+        <v>40</v>
+      </c>
       <c r="G18" s="8" t="inlineStr">
         <is>
           <t>yc</t>
@@ -1504,7 +1521,9 @@
           <t>ขวด</t>
         </is>
       </c>
-      <c r="F20" s="8" t="n"/>
+      <c r="F20" s="8" t="n">
+        <v>12</v>
+      </c>
       <c r="G20" s="8" t="inlineStr">
         <is>
           <t>yc</t>
@@ -1542,7 +1561,9 @@
           <t>ถุง</t>
         </is>
       </c>
-      <c r="F21" s="8" t="n"/>
+      <c r="F21" s="8" t="n">
+        <v>5</v>
+      </c>
       <c r="G21" s="8" t="inlineStr">
         <is>
           <t>yc</t>
@@ -1582,7 +1603,9 @@
           <t>ถุง</t>
         </is>
       </c>
-      <c r="F22" s="8" t="n"/>
+      <c r="F22" s="8" t="n">
+        <v>5</v>
+      </c>
       <c r="G22" s="8" t="inlineStr">
         <is>
           <t>yc</t>
@@ -1622,7 +1645,9 @@
           <t>ถุง</t>
         </is>
       </c>
-      <c r="F23" s="8" t="n"/>
+      <c r="F23" s="8" t="n">
+        <v>5</v>
+      </c>
       <c r="G23" s="8" t="inlineStr">
         <is>
           <t>yc</t>
@@ -1662,7 +1687,9 @@
           <t>ถุง</t>
         </is>
       </c>
-      <c r="F24" s="8" t="n"/>
+      <c r="F24" s="8" t="n">
+        <v>5</v>
+      </c>
       <c r="G24" s="8" t="inlineStr">
         <is>
           <t>yc</t>
@@ -1702,7 +1729,9 @@
           <t>ถุง</t>
         </is>
       </c>
-      <c r="F25" s="8" t="n"/>
+      <c r="F25" s="8" t="n">
+        <v>5</v>
+      </c>
       <c r="G25" s="8" t="inlineStr">
         <is>
           <t>yc</t>
@@ -1742,7 +1771,9 @@
           <t>ถุง</t>
         </is>
       </c>
-      <c r="F26" s="8" t="n"/>
+      <c r="F26" s="8" t="n">
+        <v>5</v>
+      </c>
       <c r="G26" s="8" t="inlineStr">
         <is>
           <t>yc</t>
@@ -1782,7 +1813,9 @@
           <t>กระปุก</t>
         </is>
       </c>
-      <c r="F27" s="8" t="n"/>
+      <c r="F27" s="8" t="n">
+        <v>5</v>
+      </c>
       <c r="G27" s="8" t="inlineStr">
         <is>
           <t>yc</t>
@@ -1820,7 +1853,9 @@
           <t>กระปุก</t>
         </is>
       </c>
-      <c r="F28" s="8" t="n"/>
+      <c r="F28" s="8" t="n">
+        <v>5</v>
+      </c>
       <c r="G28" s="8" t="inlineStr">
         <is>
           <t>yc</t>
@@ -1858,7 +1893,9 @@
           <t>กระปุก</t>
         </is>
       </c>
-      <c r="F29" s="8" t="n"/>
+      <c r="F29" s="8" t="n">
+        <v>5</v>
+      </c>
       <c r="G29" s="8" t="inlineStr">
         <is>
           <t>yc</t>
@@ -1896,7 +1933,9 @@
           <t>750g/pack</t>
         </is>
       </c>
-      <c r="F30" s="8" t="n"/>
+      <c r="F30" s="8" t="n">
+        <v>2</v>
+      </c>
       <c r="G30" s="8" t="inlineStr">
         <is>
           <t>yc</t>
@@ -1936,7 +1975,9 @@
           <t>454g/pack</t>
         </is>
       </c>
-      <c r="F31" s="8" t="n"/>
+      <c r="F31" s="8" t="n">
+        <v>2</v>
+      </c>
       <c r="G31" s="8" t="inlineStr">
         <is>
           <t>yc</t>
@@ -1976,7 +2017,9 @@
           <t>300g/pack</t>
         </is>
       </c>
-      <c r="F32" s="8" t="n"/>
+      <c r="F32" s="8" t="n">
+        <v>1</v>
+      </c>
       <c r="G32" s="8" t="inlineStr">
         <is>
           <t>yc</t>
@@ -2016,7 +2059,9 @@
           <t>1,000g/box</t>
         </is>
       </c>
-      <c r="F33" s="8" t="n"/>
+      <c r="F33" s="8" t="n">
+        <v>1</v>
+      </c>
       <c r="G33" s="8" t="inlineStr">
         <is>
           <t>yc</t>
@@ -2056,7 +2101,9 @@
           <t>2,000g/box</t>
         </is>
       </c>
-      <c r="F34" s="8" t="n"/>
+      <c r="F34" s="8" t="n">
+        <v>1</v>
+      </c>
       <c r="G34" s="8" t="inlineStr">
         <is>
           <t>yc</t>
@@ -2096,7 +2143,9 @@
           <t>400g/pack</t>
         </is>
       </c>
-      <c r="F35" s="8" t="n"/>
+      <c r="F35" s="8" t="n">
+        <v>1</v>
+      </c>
       <c r="G35" s="8" t="inlineStr">
         <is>
           <t>yc</t>
@@ -2134,7 +2183,9 @@
           <t>400g/pack</t>
         </is>
       </c>
-      <c r="F36" s="8" t="n"/>
+      <c r="F36" s="8" t="n">
+        <v>1</v>
+      </c>
       <c r="G36" s="8" t="inlineStr">
         <is>
           <t>yc</t>
@@ -2172,7 +2223,9 @@
           <t>400g/pack</t>
         </is>
       </c>
-      <c r="F37" s="8" t="n"/>
+      <c r="F37" s="8" t="n">
+        <v>1</v>
+      </c>
       <c r="G37" s="8" t="inlineStr">
         <is>
           <t>yc</t>
@@ -2248,7 +2301,9 @@
           <t>400g/pack</t>
         </is>
       </c>
-      <c r="F39" s="8" t="n"/>
+      <c r="F39" s="8" t="n">
+        <v>1</v>
+      </c>
       <c r="G39" s="8" t="inlineStr">
         <is>
           <t>yc</t>
@@ -2288,7 +2343,9 @@
           <t>400g/pack</t>
         </is>
       </c>
-      <c r="F40" s="8" t="n"/>
+      <c r="F40" s="8" t="n">
+        <v>1</v>
+      </c>
       <c r="G40" s="8" t="inlineStr">
         <is>
           <t>yc</t>
@@ -2328,7 +2385,9 @@
           <t>400g/pack</t>
         </is>
       </c>
-      <c r="F41" s="8" t="n"/>
+      <c r="F41" s="8" t="n">
+        <v>1</v>
+      </c>
       <c r="G41" s="8" t="inlineStr">
         <is>
           <t>yc</t>
@@ -2368,7 +2427,9 @@
           <t>1,000g/pack</t>
         </is>
       </c>
-      <c r="F42" s="8" t="n"/>
+      <c r="F42" s="8" t="n">
+        <v>1</v>
+      </c>
       <c r="G42" s="8" t="inlineStr">
         <is>
           <t>yc</t>
@@ -2406,7 +2467,9 @@
           <t>1,000g/pack</t>
         </is>
       </c>
-      <c r="F43" s="8" t="n"/>
+      <c r="F43" s="8" t="n">
+        <v>1</v>
+      </c>
       <c r="G43" s="8" t="inlineStr">
         <is>
           <t>yc</t>
@@ -2444,7 +2507,9 @@
           <t>250g/box</t>
         </is>
       </c>
-      <c r="F44" s="8" t="n"/>
+      <c r="F44" s="8" t="n">
+        <v>3</v>
+      </c>
       <c r="G44" s="8" t="inlineStr">
         <is>
           <t>yc</t>
@@ -2552,7 +2617,9 @@
           <t>300g/box</t>
         </is>
       </c>
-      <c r="F47" s="8" t="n"/>
+      <c r="F47" s="8" t="n">
+        <v>2</v>
+      </c>
       <c r="G47" s="8" t="inlineStr">
         <is>
           <t>yc</t>
@@ -2626,7 +2693,9 @@
           <t>500g/pack</t>
         </is>
       </c>
-      <c r="F49" s="8" t="n"/>
+      <c r="F49" s="8" t="n">
+        <v>1</v>
+      </c>
       <c r="G49" s="8" t="inlineStr">
         <is>
           <t>yc</t>
@@ -2666,7 +2735,9 @@
           <t>ลูก</t>
         </is>
       </c>
-      <c r="F50" s="8" t="n"/>
+      <c r="F50" s="8" t="n">
+        <v>6</v>
+      </c>
       <c r="G50" s="8" t="inlineStr">
         <is>
           <t>yc</t>
@@ -2706,7 +2777,9 @@
           <t>1,000g/bottle</t>
         </is>
       </c>
-      <c r="F51" s="8" t="n"/>
+      <c r="F51" s="8" t="n">
+        <v>2</v>
+      </c>
       <c r="G51" s="8" t="inlineStr">
         <is>
           <t>yc</t>
@@ -2746,7 +2819,9 @@
           <t>1,000g/bottle</t>
         </is>
       </c>
-      <c r="F52" s="8" t="n"/>
+      <c r="F52" s="8" t="n">
+        <v>2</v>
+      </c>
       <c r="G52" s="8" t="inlineStr">
         <is>
           <t>yc</t>
@@ -2786,7 +2861,9 @@
           <t>1,000g/pack</t>
         </is>
       </c>
-      <c r="F53" s="8" t="n"/>
+      <c r="F53" s="8" t="n">
+        <v>2</v>
+      </c>
       <c r="G53" s="8" t="inlineStr">
         <is>
           <t>yc</t>
@@ -2906,7 +2983,9 @@
           <t>50/pack</t>
         </is>
       </c>
-      <c r="F56" s="8" t="n"/>
+      <c r="F56" s="8" t="n">
+        <v>2</v>
+      </c>
       <c r="G56" s="8" t="inlineStr">
         <is>
           <t>yc</t>
@@ -2949,7 +3028,7 @@
       <c r="F57" s="8" t="n"/>
       <c r="G57" s="8" t="inlineStr">
         <is>
-          <t>yc</t>
+          <t>shared</t>
         </is>
       </c>
       <c r="H57" s="6" t="n">
@@ -2986,10 +3065,12 @@
           <t>50/pack</t>
         </is>
       </c>
-      <c r="F58" s="8" t="n"/>
+      <c r="F58" s="8" t="n">
+        <v>2</v>
+      </c>
       <c r="G58" s="8" t="inlineStr">
         <is>
-          <t>yc</t>
+          <t>shared</t>
         </is>
       </c>
       <c r="H58" s="6" t="n">
@@ -3026,10 +3107,12 @@
           <t>50/pack</t>
         </is>
       </c>
-      <c r="F59" s="8" t="n"/>
+      <c r="F59" s="8" t="n">
+        <v>2</v>
+      </c>
       <c r="G59" s="8" t="inlineStr">
         <is>
-          <t>yc</t>
+          <t>shared</t>
         </is>
       </c>
       <c r="H59" s="6" t="n">
@@ -3066,10 +3149,12 @@
           <t>50/pack</t>
         </is>
       </c>
-      <c r="F60" s="8" t="n"/>
+      <c r="F60" s="8" t="n">
+        <v>2</v>
+      </c>
       <c r="G60" s="8" t="inlineStr">
         <is>
-          <t>yc</t>
+          <t>shared</t>
         </is>
       </c>
       <c r="H60" s="6" t="n">
@@ -3106,7 +3191,9 @@
           <t>50/pack</t>
         </is>
       </c>
-      <c r="F61" s="8" t="n"/>
+      <c r="F61" s="8" t="n">
+        <v>2</v>
+      </c>
       <c r="G61" s="8" t="inlineStr">
         <is>
           <t>yc</t>
@@ -3146,7 +3233,9 @@
           <t>50/pack</t>
         </is>
       </c>
-      <c r="F62" s="8" t="n"/>
+      <c r="F62" s="8" t="n">
+        <v>2</v>
+      </c>
       <c r="G62" s="8" t="inlineStr">
         <is>
           <t>yc</t>
@@ -3226,10 +3315,12 @@
           <t>50/pack</t>
         </is>
       </c>
-      <c r="F64" s="8" t="n"/>
+      <c r="F64" s="8" t="n">
+        <v>2</v>
+      </c>
       <c r="G64" s="8" t="inlineStr">
         <is>
-          <t>yc</t>
+          <t>shared</t>
         </is>
       </c>
       <c r="H64" s="6" t="n">
@@ -3266,10 +3357,12 @@
           <t>100/pack</t>
         </is>
       </c>
-      <c r="F65" s="8" t="n"/>
+      <c r="F65" s="8" t="n">
+        <v>2</v>
+      </c>
       <c r="G65" s="8" t="inlineStr">
         <is>
-          <t>yc</t>
+          <t>shared</t>
         </is>
       </c>
       <c r="H65" s="6" t="n">
@@ -3306,10 +3399,12 @@
           <t>100/pack</t>
         </is>
       </c>
-      <c r="F66" s="8" t="n"/>
+      <c r="F66" s="8" t="n">
+        <v>5</v>
+      </c>
       <c r="G66" s="8" t="inlineStr">
         <is>
-          <t>yc</t>
+          <t>shared</t>
         </is>
       </c>
       <c r="H66" s="6" t="n">
@@ -3346,10 +3441,12 @@
           <t>100/pack</t>
         </is>
       </c>
-      <c r="F67" s="8" t="n"/>
+      <c r="F67" s="8" t="n">
+        <v>1</v>
+      </c>
       <c r="G67" s="8" t="inlineStr">
         <is>
-          <t>yc</t>
+          <t>shared</t>
         </is>
       </c>
       <c r="H67" s="6" t="n">
@@ -3429,7 +3526,7 @@
       <c r="F69" s="8" t="n"/>
       <c r="G69" s="8" t="inlineStr">
         <is>
-          <t>yc</t>
+          <t>shared</t>
         </is>
       </c>
       <c r="H69" s="6" t="n">
@@ -3469,7 +3566,7 @@
       <c r="F70" s="8" t="n"/>
       <c r="G70" s="8" t="inlineStr">
         <is>
-          <t>yc</t>
+          <t>staple</t>
         </is>
       </c>
       <c r="H70" s="6" t="n">
@@ -5272,7 +5369,9 @@
           <t>กระปุก</t>
         </is>
       </c>
-      <c r="F117" s="8" t="n"/>
+      <c r="F117" s="8" t="n">
+        <v>5</v>
+      </c>
       <c r="G117" s="8" t="inlineStr">
         <is>
           <t>yc</t>
@@ -5380,7 +5479,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F42"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
@@ -5422,7 +5521,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="28" customHeight="1">
       <c r="A2" s="9" t="n">
         <v>1</v>
       </c>

--- a/NCD_Brand_Tagging.xlsx
+++ b/NCD_Brand_Tagging.xlsx
@@ -3028,7 +3028,7 @@
       <c r="F57" s="8" t="n"/>
       <c r="G57" s="8" t="inlineStr">
         <is>
-          <t>shared</t>
+          <t>yc</t>
         </is>
       </c>
       <c r="H57" s="6" t="n">
@@ -5553,11 +5553,27 @@
       <c r="A3" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="11" t="n"/>
-      <c r="C3" s="11" t="n"/>
-      <c r="D3" s="11" t="n"/>
+      <c r="B3" s="11" t="inlineStr">
+        <is>
+          <t>Cup (14oz) - Staple</t>
+        </is>
+      </c>
+      <c r="C3" s="11" t="inlineStr">
+        <is>
+          <t>CUP/ถ้วย</t>
+        </is>
+      </c>
+      <c r="D3" s="11" t="inlineStr">
+        <is>
+          <t>50/pack</t>
+        </is>
+      </c>
       <c r="E3" s="8" t="n"/>
-      <c r="F3" s="11" t="n"/>
+      <c r="F3" s="11" t="inlineStr">
+        <is>
+          <t>Same size/spec as YC Cup 14oz (it-056) but printed with Staple logo — separate stock item, not shared. Fill in Par NCD.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="8" t="n">

--- a/NCD_Brand_Tagging.xlsx
+++ b/NCD_Brand_Tagging.xlsx
@@ -2,8 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17220" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" state="visible" r:id="rId1"/>
@@ -11,7 +12,7 @@
     <sheet name="New Staple Items" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1" iterateDelta="0.0001"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -28,47 +29,40 @@
     </font>
     <font>
       <name val="Arial"/>
-      <family val="2"/>
       <b val="1"/>
-      <color rgb="FF542916"/>
+      <color rgb="00542916"/>
       <sz val="14"/>
     </font>
     <font>
       <name val="Arial"/>
-      <family val="2"/>
-      <color rgb="FF2B241C"/>
+      <color rgb="002B241C"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
-      <family val="2"/>
-      <color rgb="FF2B241C"/>
+      <color rgb="002B241C"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Arial"/>
-      <family val="2"/>
       <b val="1"/>
-      <color rgb="FF542916"/>
+      <color rgb="00542916"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Arial"/>
-      <family val="2"/>
       <b val="1"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Arial"/>
-      <family val="2"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
-      <family val="2"/>
       <i val="1"/>
-      <color rgb="FF808080"/>
+      <color rgb="00808080"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -81,14 +75,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2565C"/>
-        <bgColor rgb="FFF2565C"/>
+        <fgColor rgb="00F2565C"/>
+        <bgColor rgb="00F2565C"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF9C4"/>
-        <bgColor rgb="FFFFF9C4"/>
+        <fgColor rgb="00FFF9C4"/>
+        <bgColor rgb="00FFF9C4"/>
       </patternFill>
     </fill>
   </fills>
@@ -102,18 +96,17 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFD9D9D9"/>
+        <color rgb="00D9D9D9"/>
       </left>
       <right style="thin">
-        <color rgb="FFD9D9D9"/>
+        <color rgb="00D9D9D9"/>
       </right>
       <top style="thin">
-        <color rgb="FFD9D9D9"/>
+        <color rgb="00D9D9D9"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFD9D9D9"/>
+        <color rgb="00D9D9D9"/>
       </bottom>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -143,6 +136,9 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -151,12 +147,9 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -236,14 +229,19 @@
     <author>System</author>
   </authors>
   <commentList>
-    <comment ref="F1" authorId="0" shapeId="0">
+    <comment ref="E1" authorId="0" shapeId="0">
+      <text>
+        <t>Only fill in if NCD needs a different, clearer name than the one shown at other branches (e.g. to tell a YC-branded item apart from a Staple-branded version of the same kind of thing). Leave blank otherwise — this never changes what other branches see.</t>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="0" shapeId="0">
       <text>
         <t>Fill in a number if NCD carries this item (normal full-stock qty). Leave blank if NCD does NOT carry it at all.</t>
       </text>
     </comment>
-    <comment ref="G1" authorId="0" shapeId="0">
+    <comment ref="H1" authorId="0" shapeId="0">
       <text>
-        <t>Only matters if Par NCD (column F) is filled in. Pick yc / staple / shared from the dropdown.</t>
+        <t>Only matters if Par NCD (column G) is filled in. Pick yc / staple / shared from the dropdown.</t>
       </text>
     </comment>
   </commentList>
@@ -539,8 +537,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A26"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <dimension ref="A1:A36"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
   </cols>
@@ -553,7 +551,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n"/>
+      <c r="A2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -577,7 +575,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n"/>
+      <c r="A6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -589,123 +587,189 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Column F 'Par NCD' — how many NCD should stock as normal full stock.</t>
+          <t xml:space="preserve">  Column E 'Display Name at NCD' — ONLY fill this in if NCD staff need to see a</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Leave BLANK if NCD will NOT carry this item at all (same rule as the other</t>
+          <t xml:space="preserve">    different name than what NVP/SND/KCN already show, to avoid confusion between</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    branch columns — blank = not stocked there). This matches columns H/I/J which</t>
+          <t xml:space="preserve">    a YC version and a Staple version of the same kind of item (e.g. cups/lids/bags</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    show how NVP/SND/KCN already handle each item, for reference only — not editable.</t>
+          <t xml:space="preserve">    printed with a brand logo — same product type, different physical item per brand).</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Column G 'Brand for NCD' is pre-filled with 'yc' as a starting guess.</t>
+          <t xml:space="preserve">    Leave BLANK for everything else — the item keeps its normal name everywhere,</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Only matters for items NCD actually carries (Par NCD is not blank).</t>
+          <t xml:space="preserve">    including at NCD. This never changes what NVP/SND/KCN staff see.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Please review every row and change it where needed:</t>
+          <t xml:space="preserve">  Column G 'Par NCD' — how many NCD should stock as normal full stock.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    yc      = YC-only product, not sold under Staple</t>
+          <t xml:space="preserve">    Leave BLANK if NCD will NOT carry this item at all (same rule as the other</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    staple  = Staple-only product</t>
+          <t xml:space="preserve">    branch columns — blank = not stocked there). This matches columns I/J/K which</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    shared  = same product sold under both brands (e.g. cups, spoons, cleaning supplies)</t>
+          <t xml:space="preserve">    show how NVP/SND/KCN already handle each item, for reference only — not editable.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Click any cell in column G to pick from the dropdown.</t>
+          <t xml:space="preserve">  Column H 'Brand for NCD' is pre-filled with 'yc' as a starting guess.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n"/>
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Only matters for items NCD actually carries (Par NCD is not blank).</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>Sheet 'New Staple Items' — add any product that does not exist in the system yet.</t>
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Please review every row and change it where needed:</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Row 4 is a filled-in example — please delete it before sending back, or just add</t>
+          <t xml:space="preserve">    yc      = YC-only product, not sold under Staple</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  your rows below it.</t>
+          <t xml:space="preserve">    staple  = Staple-only product</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Category can be an existing one (see 'Existing Items' sheet) or a brand-new category name.</t>
+          <t xml:space="preserve">    shared  = same physical product sold under both brands with no branding difference</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">  Click any cell in column H to pick from the dropdown.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Note: showing a different name only at NCD (column E) needs a small feature that does</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>not exist in the app yet — NCD is not even set up as a branch in the system yet</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>(opens Sep 2569). This is captured here now so it's ready to build when NCD launches.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Sheet 'New Staple Items' — add any product that does not exist in the system yet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Row 4 is a filled-in example — please delete it before sending back, or just add</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  your rows below it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Category can be an existing one (see 'Existing Items' sheet) or a brand-new category name.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">  Par level = normal full-stock quantity to keep on the shelf at NCD.</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="2" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
         <is>
           <t>When done, send this file back and it will be imported directly into the system.</t>
         </is>
@@ -722,17 +786,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J119"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <dimension ref="A1:K119"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="34" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="30" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="10"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -758,30 +825,35 @@
       </c>
       <c r="E1" s="5" t="inlineStr">
         <is>
+          <t>Display Name at NCD (blank = same)</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="F1" s="5" t="inlineStr">
+      <c r="G1" s="5" t="inlineStr">
         <is>
           <t>Par NCD (blank = not carried at NCD)</t>
         </is>
       </c>
-      <c r="G1" s="5" t="inlineStr">
+      <c r="H1" s="5" t="inlineStr">
         <is>
           <t>Brand for NCD (yc / staple / shared)</t>
         </is>
       </c>
-      <c r="H1" s="5" t="inlineStr">
+      <c r="I1" s="5" t="inlineStr">
         <is>
           <t>Par NVP (ref)</t>
         </is>
       </c>
-      <c r="I1" s="5" t="inlineStr">
+      <c r="J1" s="5" t="inlineStr">
         <is>
           <t>Par SND (ref)</t>
         </is>
       </c>
-      <c r="J1" s="5" t="inlineStr">
+      <c r="K1" s="5" t="inlineStr">
         <is>
           <t>Par KCN (ref)</t>
         </is>
@@ -806,26 +878,25 @@
           <t>Greek Yogurt 1kg</t>
         </is>
       </c>
-      <c r="E2" s="7" t="inlineStr">
+      <c r="E2" s="8" t="n"/>
+      <c r="F2" s="7" t="inlineStr">
         <is>
           <t>1kg/Box</t>
         </is>
       </c>
-      <c r="F2" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="G2" s="8" t="inlineStr">
-        <is>
-          <t>yc</t>
-        </is>
-      </c>
-      <c r="H2" s="6" t="n">
-        <v>6</v>
+      <c r="G2" s="9" t="n"/>
+      <c r="H2" s="9" t="inlineStr">
+        <is>
+          <t>yc</t>
+        </is>
       </c>
       <c r="I2" s="6" t="n">
         <v>6</v>
       </c>
       <c r="J2" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="K2" s="6" t="n">
         <v>4</v>
       </c>
     </row>
@@ -848,26 +919,25 @@
           <t>Yuzu</t>
         </is>
       </c>
-      <c r="E3" s="7" t="inlineStr">
+      <c r="E3" s="8" t="n"/>
+      <c r="F3" s="7" t="inlineStr">
         <is>
           <t>1kg/Box</t>
         </is>
       </c>
-      <c r="F3" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G3" s="8" t="inlineStr">
-        <is>
-          <t>yc</t>
-        </is>
-      </c>
-      <c r="H3" s="6" t="n">
-        <v>1</v>
+      <c r="G3" s="9" t="n"/>
+      <c r="H3" s="9" t="inlineStr">
+        <is>
+          <t>yc</t>
+        </is>
       </c>
       <c r="I3" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J3" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" s="6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -890,24 +960,25 @@
           <t>Kyoho</t>
         </is>
       </c>
-      <c r="E4" s="7" t="inlineStr">
+      <c r="E4" s="8" t="n"/>
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>1kg/Box</t>
         </is>
       </c>
-      <c r="F4" s="8" t="n"/>
-      <c r="G4" s="8" t="inlineStr">
-        <is>
-          <t>yc</t>
-        </is>
-      </c>
-      <c r="H4" s="6" t="n">
-        <v>1</v>
+      <c r="G4" s="9" t="n"/>
+      <c r="H4" s="9" t="inlineStr">
+        <is>
+          <t>yc</t>
+        </is>
       </c>
       <c r="I4" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J4" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" s="6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -930,24 +1001,25 @@
           <t>Mint</t>
         </is>
       </c>
-      <c r="E5" s="7" t="inlineStr">
+      <c r="E5" s="8" t="n"/>
+      <c r="F5" s="7" t="inlineStr">
         <is>
           <t>1kg/Box</t>
         </is>
       </c>
-      <c r="F5" s="8" t="n"/>
-      <c r="G5" s="8" t="inlineStr">
-        <is>
-          <t>yc</t>
-        </is>
-      </c>
-      <c r="H5" s="6" t="n">
-        <v>1</v>
+      <c r="G5" s="9" t="n"/>
+      <c r="H5" s="9" t="inlineStr">
+        <is>
+          <t>yc</t>
+        </is>
       </c>
       <c r="I5" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J5" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" s="6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -970,24 +1042,25 @@
           <t>Vanilla</t>
         </is>
       </c>
-      <c r="E6" s="7" t="inlineStr">
+      <c r="E6" s="8" t="n"/>
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>1kg/Box</t>
         </is>
       </c>
-      <c r="F6" s="8" t="n"/>
-      <c r="G6" s="8" t="inlineStr">
-        <is>
-          <t>yc</t>
-        </is>
-      </c>
-      <c r="H6" s="6" t="n">
-        <v>1</v>
+      <c r="G6" s="9" t="n"/>
+      <c r="H6" s="9" t="inlineStr">
+        <is>
+          <t>yc</t>
+        </is>
       </c>
       <c r="I6" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J6" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" s="6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1010,24 +1083,25 @@
           <t>Pineapple</t>
         </is>
       </c>
-      <c r="E7" s="7" t="inlineStr">
+      <c r="E7" s="8" t="n"/>
+      <c r="F7" s="7" t="inlineStr">
         <is>
           <t>1kg/Box</t>
         </is>
       </c>
-      <c r="F7" s="8" t="n"/>
-      <c r="G7" s="8" t="inlineStr">
-        <is>
-          <t>yc</t>
-        </is>
-      </c>
-      <c r="H7" s="6" t="n">
-        <v>1</v>
+      <c r="G7" s="9" t="n"/>
+      <c r="H7" s="9" t="inlineStr">
+        <is>
+          <t>yc</t>
+        </is>
       </c>
       <c r="I7" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J7" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" s="6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1050,24 +1124,25 @@
           <t>Biscoff</t>
         </is>
       </c>
-      <c r="E8" s="7" t="inlineStr">
+      <c r="E8" s="8" t="n"/>
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>1kg/Box</t>
         </is>
       </c>
-      <c r="F8" s="8" t="n"/>
-      <c r="G8" s="8" t="inlineStr">
-        <is>
-          <t>yc</t>
-        </is>
-      </c>
-      <c r="H8" s="6" t="n">
-        <v>2</v>
+      <c r="G8" s="9" t="n"/>
+      <c r="H8" s="9" t="inlineStr">
+        <is>
+          <t>yc</t>
+        </is>
       </c>
       <c r="I8" s="6" t="n">
         <v>2</v>
       </c>
       <c r="J8" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="K8" s="6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1090,24 +1165,25 @@
           <t>Overnight oats biscoff</t>
         </is>
       </c>
-      <c r="E9" s="7" t="inlineStr">
+      <c r="E9" s="8" t="n"/>
+      <c r="F9" s="7" t="inlineStr">
         <is>
           <t>1kg/Box</t>
         </is>
       </c>
-      <c r="F9" s="8" t="n"/>
-      <c r="G9" s="8" t="inlineStr">
-        <is>
-          <t>yc</t>
-        </is>
-      </c>
-      <c r="H9" s="6" t="n">
-        <v>1</v>
+      <c r="G9" s="9" t="n"/>
+      <c r="H9" s="9" t="inlineStr">
+        <is>
+          <t>yc</t>
+        </is>
       </c>
       <c r="I9" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J9" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" s="6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1130,26 +1206,25 @@
           <t>Plain Yogurt (ธรรมชาติ)</t>
         </is>
       </c>
-      <c r="E10" s="7" t="inlineStr">
+      <c r="E10" s="8" t="n"/>
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>1kg/Box</t>
         </is>
       </c>
-      <c r="F10" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="G10" s="8" t="inlineStr">
-        <is>
-          <t>yc</t>
-        </is>
-      </c>
-      <c r="H10" s="6" t="n">
-        <v>6</v>
+      <c r="G10" s="9" t="n"/>
+      <c r="H10" s="9" t="inlineStr">
+        <is>
+          <t>yc</t>
+        </is>
       </c>
       <c r="I10" s="6" t="n">
         <v>6</v>
       </c>
       <c r="J10" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="K10" s="6" t="n">
         <v>4</v>
       </c>
     </row>
@@ -1172,26 +1247,25 @@
           <t>Greek Yogurt 500g</t>
         </is>
       </c>
-      <c r="E11" s="7" t="inlineStr">
+      <c r="E11" s="8" t="n"/>
+      <c r="F11" s="7" t="inlineStr">
         <is>
           <t>500g/Box</t>
         </is>
       </c>
-      <c r="F11" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="G11" s="8" t="inlineStr">
-        <is>
-          <t>yc</t>
-        </is>
-      </c>
-      <c r="H11" s="6" t="n">
+      <c r="G11" s="9" t="n"/>
+      <c r="H11" s="9" t="inlineStr">
+        <is>
+          <t>yc</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="I11" s="6" t="n">
+      <c r="J11" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="J11" s="6" t="n">
+      <c r="K11" s="6" t="n">
         <v>7</v>
       </c>
     </row>
@@ -1214,26 +1288,25 @@
           <t>Plain Yogurt 500g</t>
         </is>
       </c>
-      <c r="E12" s="7" t="inlineStr">
+      <c r="E12" s="8" t="n"/>
+      <c r="F12" s="7" t="inlineStr">
         <is>
           <t>500g/Box</t>
         </is>
       </c>
-      <c r="F12" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="G12" s="8" t="inlineStr">
-        <is>
-          <t>yc</t>
-        </is>
-      </c>
-      <c r="H12" s="6" t="n">
+      <c r="G12" s="9" t="n"/>
+      <c r="H12" s="9" t="inlineStr">
+        <is>
+          <t>yc</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="I12" s="6" t="n">
+      <c r="J12" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="J12" s="6" t="n">
+      <c r="K12" s="6" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1256,24 +1329,25 @@
           <t>R-ACAI Bowl</t>
         </is>
       </c>
-      <c r="E13" s="7" t="inlineStr">
+      <c r="E13" s="8" t="n"/>
+      <c r="F13" s="7" t="inlineStr">
         <is>
           <t>Bowl</t>
         </is>
       </c>
-      <c r="F13" s="8" t="n"/>
-      <c r="G13" s="8" t="inlineStr">
-        <is>
-          <t>yc</t>
-        </is>
-      </c>
-      <c r="H13" s="6" t="n">
-        <v>15</v>
+      <c r="G13" s="9" t="n"/>
+      <c r="H13" s="9" t="inlineStr">
+        <is>
+          <t>yc</t>
+        </is>
       </c>
       <c r="I13" s="6" t="n">
         <v>15</v>
       </c>
-      <c r="J13" s="6" t="n"/>
+      <c r="J13" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="K13" s="6" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="6" t="n">
@@ -1294,24 +1368,25 @@
           <t>S-ACAI Cup (mini)</t>
         </is>
       </c>
-      <c r="E14" s="7" t="inlineStr">
+      <c r="E14" s="8" t="n"/>
+      <c r="F14" s="7" t="inlineStr">
         <is>
           <t>Cup</t>
         </is>
       </c>
-      <c r="F14" s="8" t="n"/>
-      <c r="G14" s="8" t="inlineStr">
-        <is>
-          <t>yc</t>
-        </is>
-      </c>
-      <c r="H14" s="6" t="n">
-        <v>15</v>
+      <c r="G14" s="9" t="n"/>
+      <c r="H14" s="9" t="inlineStr">
+        <is>
+          <t>yc</t>
+        </is>
       </c>
       <c r="I14" s="6" t="n">
         <v>15</v>
       </c>
-      <c r="J14" s="6" t="n"/>
+      <c r="J14" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="K14" s="6" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="6" t="n">
@@ -1332,22 +1407,23 @@
           <t>น้ำ Ice cream / Soft Serve</t>
         </is>
       </c>
-      <c r="E15" s="7" t="inlineStr">
+      <c r="E15" s="8" t="n"/>
+      <c r="F15" s="7" t="inlineStr">
         <is>
           <t>2kg/Bag</t>
         </is>
       </c>
-      <c r="F15" s="8" t="n"/>
-      <c r="G15" s="8" t="inlineStr">
-        <is>
-          <t>yc</t>
-        </is>
-      </c>
-      <c r="H15" s="6" t="n">
+      <c r="G15" s="9" t="n"/>
+      <c r="H15" s="9" t="inlineStr">
+        <is>
+          <t>yc</t>
+        </is>
+      </c>
+      <c r="I15" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="I15" s="6" t="n"/>
       <c r="J15" s="6" t="n"/>
+      <c r="K15" s="6" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="6" t="n">
@@ -1368,22 +1444,23 @@
           <t>Granola โรย Ice cream</t>
         </is>
       </c>
-      <c r="E16" s="7" t="inlineStr">
+      <c r="E16" s="8" t="n"/>
+      <c r="F16" s="7" t="inlineStr">
         <is>
           <t>g.</t>
         </is>
       </c>
-      <c r="F16" s="8" t="n"/>
-      <c r="G16" s="8" t="inlineStr">
-        <is>
-          <t>yc</t>
-        </is>
-      </c>
-      <c r="H16" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I16" s="6" t="n"/>
+      <c r="G16" s="9" t="n"/>
+      <c r="H16" s="9" t="inlineStr">
+        <is>
+          <t>yc</t>
+        </is>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>1</v>
+      </c>
       <c r="J16" s="6" t="n"/>
+      <c r="K16" s="6" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="6" t="n">
@@ -1404,24 +1481,25 @@
           <t>Softserve ถ้วยกระดาษ</t>
         </is>
       </c>
-      <c r="E17" s="7" t="inlineStr">
+      <c r="E17" s="8" t="n"/>
+      <c r="F17" s="7" t="inlineStr">
         <is>
           <t>ถ้วย</t>
         </is>
       </c>
-      <c r="F17" s="8" t="n"/>
-      <c r="G17" s="8" t="inlineStr">
-        <is>
-          <t>yc</t>
-        </is>
-      </c>
-      <c r="H17" s="6" t="n">
-        <v>0</v>
+      <c r="G17" s="9" t="n"/>
+      <c r="H17" s="9" t="inlineStr">
+        <is>
+          <t>yc</t>
+        </is>
       </c>
       <c r="I17" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="J17" s="6" t="n"/>
+      <c r="J17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" s="6" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="6" t="n">
@@ -1442,26 +1520,25 @@
           <t>Shake (แช่แข็ง)</t>
         </is>
       </c>
-      <c r="E18" s="7" t="inlineStr">
+      <c r="E18" s="8" t="n"/>
+      <c r="F18" s="7" t="inlineStr">
         <is>
           <t>ถ้วย</t>
         </is>
       </c>
-      <c r="F18" s="8" t="n">
-        <v>40</v>
-      </c>
-      <c r="G18" s="8" t="inlineStr">
-        <is>
-          <t>yc</t>
-        </is>
-      </c>
-      <c r="H18" s="6" t="n">
+      <c r="G18" s="9" t="n"/>
+      <c r="H18" s="9" t="inlineStr">
+        <is>
+          <t>yc</t>
+        </is>
+      </c>
+      <c r="I18" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="I18" s="6" t="n">
+      <c r="J18" s="6" t="n">
         <v>80</v>
       </c>
-      <c r="J18" s="6" t="n"/>
+      <c r="K18" s="6" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="6" t="n">
@@ -1482,20 +1559,21 @@
           <t>Peanut Butter</t>
         </is>
       </c>
-      <c r="E19" s="7" t="inlineStr">
+      <c r="E19" s="8" t="n"/>
+      <c r="F19" s="7" t="inlineStr">
         <is>
           <t>กระปุก</t>
         </is>
       </c>
-      <c r="F19" s="8" t="n"/>
-      <c r="G19" s="8" t="inlineStr">
-        <is>
-          <t>yc</t>
-        </is>
-      </c>
-      <c r="H19" s="6" t="n"/>
+      <c r="G19" s="9" t="n"/>
+      <c r="H19" s="9" t="inlineStr">
+        <is>
+          <t>yc</t>
+        </is>
+      </c>
       <c r="I19" s="6" t="n"/>
       <c r="J19" s="6" t="n"/>
+      <c r="K19" s="6" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="6" t="n">
@@ -1516,26 +1594,25 @@
           <t>Water น้ำดื่ม</t>
         </is>
       </c>
-      <c r="E20" s="7" t="inlineStr">
+      <c r="E20" s="8" t="n"/>
+      <c r="F20" s="7" t="inlineStr">
         <is>
           <t>ขวด</t>
         </is>
       </c>
-      <c r="F20" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="G20" s="8" t="inlineStr">
-        <is>
-          <t>yc</t>
-        </is>
-      </c>
-      <c r="H20" s="6" t="n">
-        <v>12</v>
+      <c r="G20" s="9" t="n"/>
+      <c r="H20" s="9" t="inlineStr">
+        <is>
+          <t>yc</t>
+        </is>
       </c>
       <c r="I20" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="J20" s="6" t="n"/>
+      <c r="J20" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="K20" s="6" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="n">
@@ -1556,26 +1633,25 @@
           <t>ถุงสตรอเบอรี่</t>
         </is>
       </c>
-      <c r="E21" s="7" t="inlineStr">
+      <c r="E21" s="8" t="n"/>
+      <c r="F21" s="7" t="inlineStr">
         <is>
           <t>ถุง</t>
         </is>
       </c>
-      <c r="F21" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="G21" s="8" t="inlineStr">
-        <is>
-          <t>yc</t>
-        </is>
-      </c>
-      <c r="H21" s="6" t="n">
+      <c r="G21" s="9" t="n"/>
+      <c r="H21" s="9" t="inlineStr">
+        <is>
+          <t>yc</t>
+        </is>
+      </c>
+      <c r="I21" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="I21" s="6" t="n">
+      <c r="J21" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="J21" s="6" t="n">
+      <c r="K21" s="6" t="n">
         <v>5</v>
       </c>
     </row>
@@ -1598,26 +1674,25 @@
           <t>ถุงบลูเบอรี่</t>
         </is>
       </c>
-      <c r="E22" s="7" t="inlineStr">
+      <c r="E22" s="8" t="n"/>
+      <c r="F22" s="7" t="inlineStr">
         <is>
           <t>ถุง</t>
         </is>
       </c>
-      <c r="F22" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="G22" s="8" t="inlineStr">
-        <is>
-          <t>yc</t>
-        </is>
-      </c>
-      <c r="H22" s="6" t="n">
+      <c r="G22" s="9" t="n"/>
+      <c r="H22" s="9" t="inlineStr">
+        <is>
+          <t>yc</t>
+        </is>
+      </c>
+      <c r="I22" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="I22" s="6" t="n">
+      <c r="J22" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="J22" s="6" t="n">
+      <c r="K22" s="6" t="n">
         <v>5</v>
       </c>
     </row>
@@ -1640,26 +1715,25 @@
           <t>ถุงธรรมชาติ</t>
         </is>
       </c>
-      <c r="E23" s="7" t="inlineStr">
+      <c r="E23" s="8" t="n"/>
+      <c r="F23" s="7" t="inlineStr">
         <is>
           <t>ถุง</t>
         </is>
       </c>
-      <c r="F23" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="G23" s="8" t="inlineStr">
-        <is>
-          <t>yc</t>
-        </is>
-      </c>
-      <c r="H23" s="6" t="n">
+      <c r="G23" s="9" t="n"/>
+      <c r="H23" s="9" t="inlineStr">
+        <is>
+          <t>yc</t>
+        </is>
+      </c>
+      <c r="I23" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="I23" s="6" t="n">
+      <c r="J23" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="J23" s="6" t="n">
+      <c r="K23" s="6" t="n">
         <v>5</v>
       </c>
     </row>
@@ -1682,26 +1756,25 @@
           <t>ถุงลิ้นจี่</t>
         </is>
       </c>
-      <c r="E24" s="7" t="inlineStr">
+      <c r="E24" s="8" t="n"/>
+      <c r="F24" s="7" t="inlineStr">
         <is>
           <t>ถุง</t>
         </is>
       </c>
-      <c r="F24" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="G24" s="8" t="inlineStr">
-        <is>
-          <t>yc</t>
-        </is>
-      </c>
-      <c r="H24" s="6" t="n">
+      <c r="G24" s="9" t="n"/>
+      <c r="H24" s="9" t="inlineStr">
+        <is>
+          <t>yc</t>
+        </is>
+      </c>
+      <c r="I24" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="I24" s="6" t="n">
+      <c r="J24" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="J24" s="6" t="n">
+      <c r="K24" s="6" t="n">
         <v>5</v>
       </c>
     </row>
@@ -1724,26 +1797,25 @@
           <t>ถุงยูส</t>
         </is>
       </c>
-      <c r="E25" s="7" t="inlineStr">
+      <c r="E25" s="8" t="n"/>
+      <c r="F25" s="7" t="inlineStr">
         <is>
           <t>ถุง</t>
         </is>
       </c>
-      <c r="F25" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="G25" s="8" t="inlineStr">
-        <is>
-          <t>yc</t>
-        </is>
-      </c>
-      <c r="H25" s="6" t="n">
+      <c r="G25" s="9" t="n"/>
+      <c r="H25" s="9" t="inlineStr">
+        <is>
+          <t>yc</t>
+        </is>
+      </c>
+      <c r="I25" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="I25" s="6" t="n">
+      <c r="J25" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="J25" s="6" t="n">
+      <c r="K25" s="6" t="n">
         <v>5</v>
       </c>
     </row>
@@ -1766,26 +1838,25 @@
           <t>ถุงพีช</t>
         </is>
       </c>
-      <c r="E26" s="7" t="inlineStr">
+      <c r="E26" s="8" t="n"/>
+      <c r="F26" s="7" t="inlineStr">
         <is>
           <t>ถุง</t>
         </is>
       </c>
-      <c r="F26" s="8" t="n">
+      <c r="G26" s="9" t="n"/>
+      <c r="H26" s="9" t="inlineStr">
+        <is>
+          <t>yc</t>
+        </is>
+      </c>
+      <c r="I26" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="J26" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="G26" s="8" t="inlineStr">
-        <is>
-          <t>yc</t>
-        </is>
-      </c>
-      <c r="H26" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="I26" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="J26" s="6" t="n">
+      <c r="K26" s="6" t="n">
         <v>5</v>
       </c>
     </row>
@@ -1808,26 +1879,25 @@
           <t>Cornflakes Malt (M)</t>
         </is>
       </c>
-      <c r="E27" s="7" t="inlineStr">
+      <c r="E27" s="8" t="n"/>
+      <c r="F27" s="7" t="inlineStr">
         <is>
           <t>กระปุก</t>
         </is>
       </c>
-      <c r="F27" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="G27" s="8" t="inlineStr">
-        <is>
-          <t>yc</t>
-        </is>
-      </c>
-      <c r="H27" s="6" t="n">
-        <v>4</v>
+      <c r="G27" s="9" t="n"/>
+      <c r="H27" s="9" t="inlineStr">
+        <is>
+          <t>yc</t>
+        </is>
       </c>
       <c r="I27" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="J27" s="6" t="n"/>
+      <c r="J27" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="K27" s="6" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="6" t="n">
@@ -1848,26 +1918,25 @@
           <t>Granola (M)</t>
         </is>
       </c>
-      <c r="E28" s="7" t="inlineStr">
+      <c r="E28" s="8" t="n"/>
+      <c r="F28" s="7" t="inlineStr">
         <is>
           <t>กระปุก</t>
         </is>
       </c>
-      <c r="F28" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="G28" s="8" t="inlineStr">
-        <is>
-          <t>yc</t>
-        </is>
-      </c>
-      <c r="H28" s="6" t="n">
-        <v>4</v>
+      <c r="G28" s="9" t="n"/>
+      <c r="H28" s="9" t="inlineStr">
+        <is>
+          <t>yc</t>
+        </is>
       </c>
       <c r="I28" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="J28" s="6" t="n"/>
+      <c r="J28" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="K28" s="6" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="n">
@@ -1888,26 +1957,25 @@
           <t>Choc Chip Cookies</t>
         </is>
       </c>
-      <c r="E29" s="7" t="inlineStr">
+      <c r="E29" s="8" t="n"/>
+      <c r="F29" s="7" t="inlineStr">
         <is>
           <t>กระปุก</t>
         </is>
       </c>
-      <c r="F29" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="G29" s="8" t="inlineStr">
-        <is>
-          <t>yc</t>
-        </is>
-      </c>
-      <c r="H29" s="6" t="n">
-        <v>0</v>
+      <c r="G29" s="9" t="n"/>
+      <c r="H29" s="9" t="inlineStr">
+        <is>
+          <t>yc</t>
+        </is>
       </c>
       <c r="I29" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="J29" s="6" t="n"/>
+      <c r="J29" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" s="6" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="6" t="n">
@@ -1928,26 +1996,25 @@
           <t>Cookies Crumbs</t>
         </is>
       </c>
-      <c r="E30" s="7" t="inlineStr">
+      <c r="E30" s="8" t="n"/>
+      <c r="F30" s="7" t="inlineStr">
         <is>
           <t>750g/pack</t>
         </is>
       </c>
-      <c r="F30" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="G30" s="8" t="inlineStr">
-        <is>
-          <t>yc</t>
-        </is>
-      </c>
-      <c r="H30" s="6" t="n">
-        <v>1</v>
+      <c r="G30" s="9" t="n"/>
+      <c r="H30" s="9" t="inlineStr">
+        <is>
+          <t>yc</t>
+        </is>
       </c>
       <c r="I30" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J30" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K30" s="6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1970,26 +2037,25 @@
           <t>Oreo</t>
         </is>
       </c>
-      <c r="E31" s="7" t="inlineStr">
+      <c r="E31" s="8" t="n"/>
+      <c r="F31" s="7" t="inlineStr">
         <is>
           <t>454g/pack</t>
         </is>
       </c>
-      <c r="F31" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="G31" s="8" t="inlineStr">
-        <is>
-          <t>yc</t>
-        </is>
-      </c>
-      <c r="H31" s="6" t="n">
-        <v>2</v>
+      <c r="G31" s="9" t="n"/>
+      <c r="H31" s="9" t="inlineStr">
+        <is>
+          <t>yc</t>
+        </is>
       </c>
       <c r="I31" s="6" t="n">
         <v>2</v>
       </c>
       <c r="J31" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="K31" s="6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2012,26 +2078,25 @@
           <t>Choc Chips</t>
         </is>
       </c>
-      <c r="E32" s="7" t="inlineStr">
+      <c r="E32" s="8" t="n"/>
+      <c r="F32" s="7" t="inlineStr">
         <is>
           <t>300g/pack</t>
         </is>
       </c>
-      <c r="F32" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G32" s="8" t="inlineStr">
-        <is>
-          <t>yc</t>
-        </is>
-      </c>
-      <c r="H32" s="6" t="n">
-        <v>1</v>
+      <c r="G32" s="9" t="n"/>
+      <c r="H32" s="9" t="inlineStr">
+        <is>
+          <t>yc</t>
+        </is>
       </c>
       <c r="I32" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J32" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K32" s="6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2054,26 +2119,25 @@
           <t>Cornflakes (Topping)</t>
         </is>
       </c>
-      <c r="E33" s="7" t="inlineStr">
+      <c r="E33" s="8" t="n"/>
+      <c r="F33" s="7" t="inlineStr">
         <is>
           <t>1,000g/box</t>
         </is>
       </c>
-      <c r="F33" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G33" s="8" t="inlineStr">
-        <is>
-          <t>yc</t>
-        </is>
-      </c>
-      <c r="H33" s="6" t="n">
-        <v>1</v>
+      <c r="G33" s="9" t="n"/>
+      <c r="H33" s="9" t="inlineStr">
+        <is>
+          <t>yc</t>
+        </is>
       </c>
       <c r="I33" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J33" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K33" s="6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2096,26 +2160,25 @@
           <t>Granola (Topping)</t>
         </is>
       </c>
-      <c r="E34" s="7" t="inlineStr">
+      <c r="E34" s="8" t="n"/>
+      <c r="F34" s="7" t="inlineStr">
         <is>
           <t>2,000g/box</t>
         </is>
       </c>
-      <c r="F34" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G34" s="8" t="inlineStr">
-        <is>
-          <t>yc</t>
-        </is>
-      </c>
-      <c r="H34" s="6" t="n">
-        <v>1</v>
+      <c r="G34" s="9" t="n"/>
+      <c r="H34" s="9" t="inlineStr">
+        <is>
+          <t>yc</t>
+        </is>
       </c>
       <c r="I34" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J34" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K34" s="6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2138,26 +2201,25 @@
           <t>Almond</t>
         </is>
       </c>
-      <c r="E35" s="7" t="inlineStr">
+      <c r="E35" s="8" t="n"/>
+      <c r="F35" s="7" t="inlineStr">
         <is>
           <t>400g/pack</t>
         </is>
       </c>
-      <c r="F35" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G35" s="8" t="inlineStr">
-        <is>
-          <t>yc</t>
-        </is>
-      </c>
-      <c r="H35" s="6" t="n">
-        <v>1</v>
+      <c r="G35" s="9" t="n"/>
+      <c r="H35" s="9" t="inlineStr">
+        <is>
+          <t>yc</t>
+        </is>
       </c>
       <c r="I35" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="J35" s="6" t="n"/>
+      <c r="J35" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K35" s="6" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="6" t="n">
@@ -2178,26 +2240,25 @@
           <t>Pecan</t>
         </is>
       </c>
-      <c r="E36" s="7" t="inlineStr">
+      <c r="E36" s="8" t="n"/>
+      <c r="F36" s="7" t="inlineStr">
         <is>
           <t>400g/pack</t>
         </is>
       </c>
-      <c r="F36" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G36" s="8" t="inlineStr">
-        <is>
-          <t>yc</t>
-        </is>
-      </c>
-      <c r="H36" s="6" t="n">
-        <v>1</v>
+      <c r="G36" s="9" t="n"/>
+      <c r="H36" s="9" t="inlineStr">
+        <is>
+          <t>yc</t>
+        </is>
       </c>
       <c r="I36" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="J36" s="6" t="n"/>
+      <c r="J36" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K36" s="6" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="6" t="n">
@@ -2218,26 +2279,25 @@
           <t>Walnut</t>
         </is>
       </c>
-      <c r="E37" s="7" t="inlineStr">
+      <c r="E37" s="8" t="n"/>
+      <c r="F37" s="7" t="inlineStr">
         <is>
           <t>400g/pack</t>
         </is>
       </c>
-      <c r="F37" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G37" s="8" t="inlineStr">
-        <is>
-          <t>yc</t>
-        </is>
-      </c>
-      <c r="H37" s="6" t="n">
-        <v>1</v>
+      <c r="G37" s="9" t="n"/>
+      <c r="H37" s="9" t="inlineStr">
+        <is>
+          <t>yc</t>
+        </is>
       </c>
       <c r="I37" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="J37" s="6" t="n"/>
+      <c r="J37" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K37" s="6" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="6" t="n">
@@ -2258,24 +2318,25 @@
           <t>Coconut Chips</t>
         </is>
       </c>
-      <c r="E38" s="7" t="inlineStr">
+      <c r="E38" s="8" t="n"/>
+      <c r="F38" s="7" t="inlineStr">
         <is>
           <t>130g/box</t>
         </is>
       </c>
-      <c r="F38" s="8" t="n"/>
-      <c r="G38" s="8" t="inlineStr">
-        <is>
-          <t>yc</t>
-        </is>
-      </c>
-      <c r="H38" s="6" t="n">
-        <v>0</v>
+      <c r="G38" s="9" t="n"/>
+      <c r="H38" s="9" t="inlineStr">
+        <is>
+          <t>yc</t>
+        </is>
       </c>
       <c r="I38" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="J38" s="6" t="n"/>
+      <c r="J38" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" s="6" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="6" t="n">
@@ -2296,26 +2357,25 @@
           <t>Chia Seed</t>
         </is>
       </c>
-      <c r="E39" s="7" t="inlineStr">
+      <c r="E39" s="8" t="n"/>
+      <c r="F39" s="7" t="inlineStr">
         <is>
           <t>400g/pack</t>
         </is>
       </c>
-      <c r="F39" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G39" s="8" t="inlineStr">
-        <is>
-          <t>yc</t>
-        </is>
-      </c>
-      <c r="H39" s="6" t="n">
-        <v>1</v>
+      <c r="G39" s="9" t="n"/>
+      <c r="H39" s="9" t="inlineStr">
+        <is>
+          <t>yc</t>
+        </is>
       </c>
       <c r="I39" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J39" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K39" s="6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2338,26 +2398,25 @@
           <t>Flax Seed</t>
         </is>
       </c>
-      <c r="E40" s="7" t="inlineStr">
+      <c r="E40" s="8" t="n"/>
+      <c r="F40" s="7" t="inlineStr">
         <is>
           <t>400g/pack</t>
         </is>
       </c>
-      <c r="F40" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G40" s="8" t="inlineStr">
-        <is>
-          <t>yc</t>
-        </is>
-      </c>
-      <c r="H40" s="6" t="n">
-        <v>1</v>
+      <c r="G40" s="9" t="n"/>
+      <c r="H40" s="9" t="inlineStr">
+        <is>
+          <t>yc</t>
+        </is>
       </c>
       <c r="I40" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J40" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K40" s="6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2380,26 +2439,25 @@
           <t>Cacao Nibs</t>
         </is>
       </c>
-      <c r="E41" s="7" t="inlineStr">
+      <c r="E41" s="8" t="n"/>
+      <c r="F41" s="7" t="inlineStr">
         <is>
           <t>400g/pack</t>
         </is>
       </c>
-      <c r="F41" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G41" s="8" t="inlineStr">
-        <is>
-          <t>yc</t>
-        </is>
-      </c>
-      <c r="H41" s="6" t="n">
-        <v>1</v>
+      <c r="G41" s="9" t="n"/>
+      <c r="H41" s="9" t="inlineStr">
+        <is>
+          <t>yc</t>
+        </is>
       </c>
       <c r="I41" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J41" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K41" s="6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2422,26 +2480,25 @@
           <t>Grape Jelly</t>
         </is>
       </c>
-      <c r="E42" s="7" t="inlineStr">
+      <c r="E42" s="8" t="n"/>
+      <c r="F42" s="7" t="inlineStr">
         <is>
           <t>1,000g/pack</t>
         </is>
       </c>
-      <c r="F42" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G42" s="8" t="inlineStr">
-        <is>
-          <t>yc</t>
-        </is>
-      </c>
-      <c r="H42" s="6" t="n">
-        <v>1</v>
+      <c r="G42" s="9" t="n"/>
+      <c r="H42" s="9" t="inlineStr">
+        <is>
+          <t>yc</t>
+        </is>
       </c>
       <c r="I42" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="J42" s="6" t="n"/>
+      <c r="J42" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K42" s="6" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="6" t="n">
@@ -2462,26 +2519,25 @@
           <t>Honey Jelly</t>
         </is>
       </c>
-      <c r="E43" s="7" t="inlineStr">
+      <c r="E43" s="8" t="n"/>
+      <c r="F43" s="7" t="inlineStr">
         <is>
           <t>1,000g/pack</t>
         </is>
       </c>
-      <c r="F43" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G43" s="8" t="inlineStr">
-        <is>
-          <t>yc</t>
-        </is>
-      </c>
-      <c r="H43" s="6" t="n">
-        <v>1</v>
+      <c r="G43" s="9" t="n"/>
+      <c r="H43" s="9" t="inlineStr">
+        <is>
+          <t>yc</t>
+        </is>
       </c>
       <c r="I43" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="J43" s="6" t="n"/>
+      <c r="J43" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K43" s="6" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="6" t="n">
@@ -2502,26 +2558,25 @@
           <t>Strawberry (250g)</t>
         </is>
       </c>
-      <c r="E44" s="7" t="inlineStr">
+      <c r="E44" s="8" t="n"/>
+      <c r="F44" s="7" t="inlineStr">
         <is>
           <t>250g/box</t>
         </is>
       </c>
-      <c r="F44" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="G44" s="8" t="inlineStr">
-        <is>
-          <t>yc</t>
-        </is>
-      </c>
-      <c r="H44" s="6" t="n">
-        <v>4</v>
+      <c r="G44" s="9" t="n"/>
+      <c r="H44" s="9" t="inlineStr">
+        <is>
+          <t>yc</t>
+        </is>
       </c>
       <c r="I44" s="6" t="n">
         <v>4</v>
       </c>
       <c r="J44" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="K44" s="6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2544,20 +2599,21 @@
           <t>Strawberry (500g)</t>
         </is>
       </c>
-      <c r="E45" s="7" t="inlineStr">
+      <c r="E45" s="8" t="n"/>
+      <c r="F45" s="7" t="inlineStr">
         <is>
           <t>500g/box</t>
         </is>
       </c>
-      <c r="F45" s="8" t="n"/>
-      <c r="G45" s="8" t="inlineStr">
-        <is>
-          <t>yc</t>
-        </is>
-      </c>
-      <c r="H45" s="6" t="n"/>
+      <c r="G45" s="9" t="n"/>
+      <c r="H45" s="9" t="inlineStr">
+        <is>
+          <t>yc</t>
+        </is>
+      </c>
       <c r="I45" s="6" t="n"/>
       <c r="J45" s="6" t="n"/>
+      <c r="K45" s="6" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="6" t="n">
@@ -2578,20 +2634,21 @@
           <t>Blueberry (125g)</t>
         </is>
       </c>
-      <c r="E46" s="7" t="inlineStr">
+      <c r="E46" s="8" t="n"/>
+      <c r="F46" s="7" t="inlineStr">
         <is>
           <t>125g/box</t>
         </is>
       </c>
-      <c r="F46" s="8" t="n"/>
-      <c r="G46" s="8" t="inlineStr">
-        <is>
-          <t>yc</t>
-        </is>
-      </c>
-      <c r="H46" s="6" t="n"/>
+      <c r="G46" s="9" t="n"/>
+      <c r="H46" s="9" t="inlineStr">
+        <is>
+          <t>yc</t>
+        </is>
+      </c>
       <c r="I46" s="6" t="n"/>
       <c r="J46" s="6" t="n"/>
+      <c r="K46" s="6" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="6" t="n">
@@ -2612,26 +2669,25 @@
           <t>Blueberry (300g)</t>
         </is>
       </c>
-      <c r="E47" s="7" t="inlineStr">
+      <c r="E47" s="8" t="n"/>
+      <c r="F47" s="7" t="inlineStr">
         <is>
           <t>300g/box</t>
         </is>
       </c>
-      <c r="F47" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="G47" s="8" t="inlineStr">
-        <is>
-          <t>yc</t>
-        </is>
-      </c>
-      <c r="H47" s="6" t="n">
-        <v>3</v>
+      <c r="G47" s="9" t="n"/>
+      <c r="H47" s="9" t="inlineStr">
+        <is>
+          <t>yc</t>
+        </is>
       </c>
       <c r="I47" s="6" t="n">
         <v>3</v>
       </c>
       <c r="J47" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="K47" s="6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2654,20 +2710,21 @@
           <t>Blueberry (500g)</t>
         </is>
       </c>
-      <c r="E48" s="7" t="inlineStr">
+      <c r="E48" s="8" t="n"/>
+      <c r="F48" s="7" t="inlineStr">
         <is>
           <t>500g/box</t>
         </is>
       </c>
-      <c r="F48" s="8" t="n"/>
-      <c r="G48" s="8" t="inlineStr">
-        <is>
-          <t>yc</t>
-        </is>
-      </c>
-      <c r="H48" s="6" t="n"/>
+      <c r="G48" s="9" t="n"/>
+      <c r="H48" s="9" t="inlineStr">
+        <is>
+          <t>yc</t>
+        </is>
+      </c>
       <c r="I48" s="6" t="n"/>
       <c r="J48" s="6" t="n"/>
+      <c r="K48" s="6" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="6" t="n">
@@ -2688,26 +2745,25 @@
           <t>Apple Cinnamon</t>
         </is>
       </c>
-      <c r="E49" s="7" t="inlineStr">
+      <c r="E49" s="8" t="n"/>
+      <c r="F49" s="7" t="inlineStr">
         <is>
           <t>500g/pack</t>
         </is>
       </c>
-      <c r="F49" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G49" s="8" t="inlineStr">
-        <is>
-          <t>yc</t>
-        </is>
-      </c>
-      <c r="H49" s="6" t="n">
-        <v>1</v>
+      <c r="G49" s="9" t="n"/>
+      <c r="H49" s="9" t="inlineStr">
+        <is>
+          <t>yc</t>
+        </is>
       </c>
       <c r="I49" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J49" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K49" s="6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2730,26 +2786,25 @@
           <t>Banana</t>
         </is>
       </c>
-      <c r="E50" s="7" t="inlineStr">
+      <c r="E50" s="8" t="n"/>
+      <c r="F50" s="7" t="inlineStr">
         <is>
           <t>ลูก</t>
         </is>
       </c>
-      <c r="F50" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="G50" s="8" t="inlineStr">
-        <is>
-          <t>yc</t>
-        </is>
-      </c>
-      <c r="H50" s="6" t="n">
-        <v>0</v>
+      <c r="G50" s="9" t="n"/>
+      <c r="H50" s="9" t="inlineStr">
+        <is>
+          <t>yc</t>
+        </is>
       </c>
       <c r="I50" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J50" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" s="6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2772,26 +2827,25 @@
           <t>Honey</t>
         </is>
       </c>
-      <c r="E51" s="7" t="inlineStr">
+      <c r="E51" s="8" t="n"/>
+      <c r="F51" s="7" t="inlineStr">
         <is>
           <t>1,000g/bottle</t>
         </is>
       </c>
-      <c r="F51" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="G51" s="8" t="inlineStr">
-        <is>
-          <t>yc</t>
-        </is>
-      </c>
-      <c r="H51" s="6" t="n">
-        <v>1</v>
+      <c r="G51" s="9" t="n"/>
+      <c r="H51" s="9" t="inlineStr">
+        <is>
+          <t>yc</t>
+        </is>
       </c>
       <c r="I51" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J51" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K51" s="6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2814,26 +2868,25 @@
           <t>Caramel</t>
         </is>
       </c>
-      <c r="E52" s="7" t="inlineStr">
+      <c r="E52" s="8" t="n"/>
+      <c r="F52" s="7" t="inlineStr">
         <is>
           <t>1,000g/bottle</t>
         </is>
       </c>
-      <c r="F52" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="G52" s="8" t="inlineStr">
-        <is>
-          <t>yc</t>
-        </is>
-      </c>
-      <c r="H52" s="6" t="n">
-        <v>1</v>
+      <c r="G52" s="9" t="n"/>
+      <c r="H52" s="9" t="inlineStr">
+        <is>
+          <t>yc</t>
+        </is>
       </c>
       <c r="I52" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J52" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K52" s="6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2856,26 +2909,25 @@
           <t>Peanut Butter Sauce</t>
         </is>
       </c>
-      <c r="E53" s="7" t="inlineStr">
+      <c r="E53" s="8" t="n"/>
+      <c r="F53" s="7" t="inlineStr">
         <is>
           <t>1,000g/pack</t>
         </is>
       </c>
-      <c r="F53" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="G53" s="8" t="inlineStr">
-        <is>
-          <t>yc</t>
-        </is>
-      </c>
-      <c r="H53" s="6" t="n">
-        <v>1</v>
+      <c r="G53" s="9" t="n"/>
+      <c r="H53" s="9" t="inlineStr">
+        <is>
+          <t>yc</t>
+        </is>
       </c>
       <c r="I53" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J53" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K53" s="6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2898,24 +2950,25 @@
           <t>Cup P (5oz)</t>
         </is>
       </c>
-      <c r="E54" s="7" t="inlineStr">
+      <c r="E54" s="8" t="n"/>
+      <c r="F54" s="7" t="inlineStr">
         <is>
           <t>50/pack</t>
         </is>
       </c>
-      <c r="F54" s="8" t="n"/>
-      <c r="G54" s="8" t="inlineStr">
-        <is>
-          <t>yc</t>
-        </is>
-      </c>
-      <c r="H54" s="6" t="n">
-        <v>1</v>
+      <c r="G54" s="9" t="n"/>
+      <c r="H54" s="9" t="inlineStr">
+        <is>
+          <t>yc</t>
+        </is>
       </c>
       <c r="I54" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J54" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K54" s="6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2938,24 +2991,25 @@
           <t>Cup S (9oz)</t>
         </is>
       </c>
-      <c r="E55" s="7" t="inlineStr">
+      <c r="E55" s="8" t="n"/>
+      <c r="F55" s="7" t="inlineStr">
         <is>
           <t>50/pack</t>
         </is>
       </c>
-      <c r="F55" s="8" t="n"/>
-      <c r="G55" s="8" t="inlineStr">
-        <is>
-          <t>yc</t>
-        </is>
-      </c>
-      <c r="H55" s="6" t="n">
-        <v>2</v>
+      <c r="G55" s="9" t="n"/>
+      <c r="H55" s="9" t="inlineStr">
+        <is>
+          <t>yc</t>
+        </is>
       </c>
       <c r="I55" s="6" t="n">
         <v>2</v>
       </c>
       <c r="J55" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="K55" s="6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2978,26 +3032,25 @@
           <t>Small Bowl</t>
         </is>
       </c>
-      <c r="E56" s="7" t="inlineStr">
+      <c r="E56" s="8" t="n"/>
+      <c r="F56" s="7" t="inlineStr">
         <is>
           <t>50/pack</t>
         </is>
       </c>
-      <c r="F56" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="G56" s="8" t="inlineStr">
-        <is>
-          <t>yc</t>
-        </is>
-      </c>
-      <c r="H56" s="6" t="n">
-        <v>1</v>
+      <c r="G56" s="9" t="n"/>
+      <c r="H56" s="9" t="inlineStr">
+        <is>
+          <t>yc</t>
+        </is>
       </c>
       <c r="I56" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J56" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K56" s="6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3020,24 +3073,29 @@
           <t>Cup (14oz)</t>
         </is>
       </c>
-      <c r="E57" s="7" t="inlineStr">
+      <c r="E57" s="8" t="inlineStr">
+        <is>
+          <t>YC Cup (14oz)</t>
+        </is>
+      </c>
+      <c r="F57" s="7" t="inlineStr">
         <is>
           <t>50/pack</t>
         </is>
       </c>
-      <c r="F57" s="8" t="n"/>
-      <c r="G57" s="8" t="inlineStr">
-        <is>
-          <t>yc</t>
-        </is>
-      </c>
-      <c r="H57" s="6" t="n">
-        <v>2</v>
+      <c r="G57" s="9" t="n"/>
+      <c r="H57" s="9" t="inlineStr">
+        <is>
+          <t>yc</t>
+        </is>
       </c>
       <c r="I57" s="6" t="n">
         <v>2</v>
       </c>
       <c r="J57" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="K57" s="6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3060,26 +3118,25 @@
           <t>Cup 3oz (Topping)</t>
         </is>
       </c>
-      <c r="E58" s="7" t="inlineStr">
+      <c r="E58" s="8" t="n"/>
+      <c r="F58" s="7" t="inlineStr">
         <is>
           <t>50/pack</t>
         </is>
       </c>
-      <c r="F58" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="G58" s="8" t="inlineStr">
-        <is>
-          <t>shared</t>
-        </is>
-      </c>
-      <c r="H58" s="6" t="n">
-        <v>2</v>
+      <c r="G58" s="9" t="n"/>
+      <c r="H58" s="9" t="inlineStr">
+        <is>
+          <t>yc</t>
+        </is>
       </c>
       <c r="I58" s="6" t="n">
         <v>2</v>
       </c>
       <c r="J58" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="K58" s="6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3102,26 +3159,25 @@
           <t>Cup+Lid (Big) 3oz</t>
         </is>
       </c>
-      <c r="E59" s="7" t="inlineStr">
+      <c r="E59" s="8" t="n"/>
+      <c r="F59" s="7" t="inlineStr">
         <is>
           <t>50/pack</t>
         </is>
       </c>
-      <c r="F59" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="G59" s="8" t="inlineStr">
-        <is>
-          <t>shared</t>
-        </is>
-      </c>
-      <c r="H59" s="6" t="n">
-        <v>2</v>
+      <c r="G59" s="9" t="n"/>
+      <c r="H59" s="9" t="inlineStr">
+        <is>
+          <t>yc</t>
+        </is>
       </c>
       <c r="I59" s="6" t="n">
         <v>2</v>
       </c>
       <c r="J59" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="K59" s="6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3144,26 +3200,25 @@
           <t>Cup+Lid (Small) 1oz</t>
         </is>
       </c>
-      <c r="E60" s="7" t="inlineStr">
+      <c r="E60" s="8" t="n"/>
+      <c r="F60" s="7" t="inlineStr">
         <is>
           <t>50/pack</t>
         </is>
       </c>
-      <c r="F60" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="G60" s="8" t="inlineStr">
-        <is>
-          <t>shared</t>
-        </is>
-      </c>
-      <c r="H60" s="6" t="n">
-        <v>2</v>
+      <c r="G60" s="9" t="n"/>
+      <c r="H60" s="9" t="inlineStr">
+        <is>
+          <t>yc</t>
+        </is>
       </c>
       <c r="I60" s="6" t="n">
         <v>2</v>
       </c>
       <c r="J60" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="K60" s="6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3186,26 +3241,25 @@
           <t>Bowl Lid</t>
         </is>
       </c>
-      <c r="E61" s="7" t="inlineStr">
+      <c r="E61" s="8" t="n"/>
+      <c r="F61" s="7" t="inlineStr">
         <is>
           <t>50/pack</t>
         </is>
       </c>
-      <c r="F61" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="G61" s="8" t="inlineStr">
-        <is>
-          <t>yc</t>
-        </is>
-      </c>
-      <c r="H61" s="6" t="n">
-        <v>2</v>
+      <c r="G61" s="9" t="n"/>
+      <c r="H61" s="9" t="inlineStr">
+        <is>
+          <t>yc</t>
+        </is>
       </c>
       <c r="I61" s="6" t="n">
         <v>2</v>
       </c>
       <c r="J61" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="K61" s="6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3228,26 +3282,25 @@
           <t>Smoothies Lid</t>
         </is>
       </c>
-      <c r="E62" s="7" t="inlineStr">
+      <c r="E62" s="8" t="n"/>
+      <c r="F62" s="7" t="inlineStr">
         <is>
           <t>50/pack</t>
         </is>
       </c>
-      <c r="F62" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="G62" s="8" t="inlineStr">
-        <is>
-          <t>yc</t>
-        </is>
-      </c>
-      <c r="H62" s="6" t="n">
-        <v>2</v>
+      <c r="G62" s="9" t="n"/>
+      <c r="H62" s="9" t="inlineStr">
+        <is>
+          <t>yc</t>
+        </is>
       </c>
       <c r="I62" s="6" t="n">
         <v>2</v>
       </c>
       <c r="J62" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="K62" s="6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3270,24 +3323,25 @@
           <t>Lid S (92)</t>
         </is>
       </c>
-      <c r="E63" s="7" t="inlineStr">
+      <c r="E63" s="8" t="n"/>
+      <c r="F63" s="7" t="inlineStr">
         <is>
           <t>50/pack</t>
         </is>
       </c>
-      <c r="F63" s="8" t="n"/>
-      <c r="G63" s="8" t="inlineStr">
-        <is>
-          <t>yc</t>
-        </is>
-      </c>
-      <c r="H63" s="6" t="n">
-        <v>2</v>
+      <c r="G63" s="9" t="n"/>
+      <c r="H63" s="9" t="inlineStr">
+        <is>
+          <t>yc</t>
+        </is>
       </c>
       <c r="I63" s="6" t="n">
         <v>2</v>
       </c>
       <c r="J63" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="K63" s="6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3310,26 +3364,25 @@
           <t>Lid Top / Lid P (75)</t>
         </is>
       </c>
-      <c r="E64" s="7" t="inlineStr">
+      <c r="E64" s="8" t="n"/>
+      <c r="F64" s="7" t="inlineStr">
         <is>
           <t>50/pack</t>
         </is>
       </c>
-      <c r="F64" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="G64" s="8" t="inlineStr">
-        <is>
-          <t>shared</t>
-        </is>
-      </c>
-      <c r="H64" s="6" t="n">
-        <v>2</v>
+      <c r="G64" s="9" t="n"/>
+      <c r="H64" s="9" t="inlineStr">
+        <is>
+          <t>yc</t>
+        </is>
       </c>
       <c r="I64" s="6" t="n">
         <v>2</v>
       </c>
       <c r="J64" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="K64" s="6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3352,26 +3405,25 @@
           <t>Wood Spoon in bag</t>
         </is>
       </c>
-      <c r="E65" s="7" t="inlineStr">
+      <c r="E65" s="8" t="n"/>
+      <c r="F65" s="7" t="inlineStr">
         <is>
           <t>100/pack</t>
         </is>
       </c>
-      <c r="F65" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="G65" s="8" t="inlineStr">
-        <is>
-          <t>shared</t>
-        </is>
-      </c>
-      <c r="H65" s="6" t="n">
-        <v>1</v>
+      <c r="G65" s="9" t="n"/>
+      <c r="H65" s="9" t="inlineStr">
+        <is>
+          <t>yc</t>
+        </is>
       </c>
       <c r="I65" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J65" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K65" s="6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3394,26 +3446,25 @@
           <t>Wood Spoon</t>
         </is>
       </c>
-      <c r="E66" s="7" t="inlineStr">
+      <c r="E66" s="8" t="n"/>
+      <c r="F66" s="7" t="inlineStr">
         <is>
           <t>100/pack</t>
         </is>
       </c>
-      <c r="F66" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="G66" s="8" t="inlineStr">
-        <is>
-          <t>shared</t>
-        </is>
-      </c>
-      <c r="H66" s="6" t="n">
-        <v>3</v>
+      <c r="G66" s="9" t="n"/>
+      <c r="H66" s="9" t="inlineStr">
+        <is>
+          <t>yc</t>
+        </is>
       </c>
       <c r="I66" s="6" t="n">
         <v>3</v>
       </c>
       <c r="J66" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="K66" s="6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3436,26 +3487,25 @@
           <t>Tester Spoon ช้อนชิม</t>
         </is>
       </c>
-      <c r="E67" s="7" t="inlineStr">
+      <c r="E67" s="8" t="n"/>
+      <c r="F67" s="7" t="inlineStr">
         <is>
           <t>100/pack</t>
         </is>
       </c>
-      <c r="F67" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G67" s="8" t="inlineStr">
-        <is>
-          <t>shared</t>
-        </is>
-      </c>
-      <c r="H67" s="6" t="n">
-        <v>1</v>
+      <c r="G67" s="9" t="n"/>
+      <c r="H67" s="9" t="inlineStr">
+        <is>
+          <t>yc</t>
+        </is>
       </c>
       <c r="I67" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J67" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K67" s="6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3478,24 +3528,25 @@
           <t>Short Spoon (ช้อนถ้วยP)</t>
         </is>
       </c>
-      <c r="E68" s="7" t="inlineStr">
+      <c r="E68" s="8" t="n"/>
+      <c r="F68" s="7" t="inlineStr">
         <is>
           <t>100/pack</t>
         </is>
       </c>
-      <c r="F68" s="8" t="n"/>
-      <c r="G68" s="8" t="inlineStr">
-        <is>
-          <t>yc</t>
-        </is>
-      </c>
-      <c r="H68" s="6" t="n">
-        <v>2</v>
+      <c r="G68" s="9" t="n"/>
+      <c r="H68" s="9" t="inlineStr">
+        <is>
+          <t>yc</t>
+        </is>
       </c>
       <c r="I68" s="6" t="n">
         <v>2</v>
       </c>
       <c r="J68" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="K68" s="6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3518,24 +3569,25 @@
           <t>Straw/หลอด - ใหญ่</t>
         </is>
       </c>
-      <c r="E69" s="7" t="inlineStr">
+      <c r="E69" s="8" t="n"/>
+      <c r="F69" s="7" t="inlineStr">
         <is>
           <t>100/pack</t>
         </is>
       </c>
-      <c r="F69" s="8" t="n"/>
-      <c r="G69" s="8" t="inlineStr">
-        <is>
-          <t>shared</t>
-        </is>
-      </c>
-      <c r="H69" s="6" t="n">
-        <v>2</v>
+      <c r="G69" s="9" t="n"/>
+      <c r="H69" s="9" t="inlineStr">
+        <is>
+          <t>yc</t>
+        </is>
       </c>
       <c r="I69" s="6" t="n">
         <v>2</v>
       </c>
       <c r="J69" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="K69" s="6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3558,24 +3610,25 @@
           <t>Straw/หลอด - เล็ก</t>
         </is>
       </c>
-      <c r="E70" s="7" t="inlineStr">
+      <c r="E70" s="8" t="n"/>
+      <c r="F70" s="7" t="inlineStr">
         <is>
           <t>100/pack</t>
         </is>
       </c>
-      <c r="F70" s="8" t="n"/>
-      <c r="G70" s="8" t="inlineStr">
-        <is>
-          <t>staple</t>
-        </is>
-      </c>
-      <c r="H70" s="6" t="n">
-        <v>1</v>
+      <c r="G70" s="9" t="n"/>
+      <c r="H70" s="9" t="inlineStr">
+        <is>
+          <t>yc</t>
+        </is>
       </c>
       <c r="I70" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="J70" s="6" t="n"/>
+      <c r="J70" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K70" s="6" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="6" t="n">
@@ -3596,24 +3649,25 @@
           <t>Fail Bag ถุงฟลอย</t>
         </is>
       </c>
-      <c r="E71" s="7" t="inlineStr">
+      <c r="E71" s="8" t="n"/>
+      <c r="F71" s="7" t="inlineStr">
         <is>
           <t>ใบ</t>
         </is>
       </c>
-      <c r="F71" s="8" t="n"/>
-      <c r="G71" s="8" t="inlineStr">
-        <is>
-          <t>yc</t>
-        </is>
-      </c>
-      <c r="H71" s="6" t="n">
-        <v>2</v>
+      <c r="G71" s="9" t="n"/>
+      <c r="H71" s="9" t="inlineStr">
+        <is>
+          <t>yc</t>
+        </is>
       </c>
       <c r="I71" s="6" t="n">
         <v>2</v>
       </c>
       <c r="J71" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="K71" s="6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3636,24 +3690,25 @@
           <t>ถุงกระดาษแก้วเดี่ยว</t>
         </is>
       </c>
-      <c r="E72" s="7" t="inlineStr">
+      <c r="E72" s="8" t="n"/>
+      <c r="F72" s="7" t="inlineStr">
         <is>
           <t>ใบ</t>
         </is>
       </c>
-      <c r="F72" s="8" t="n"/>
-      <c r="G72" s="8" t="inlineStr">
-        <is>
-          <t>yc</t>
-        </is>
-      </c>
-      <c r="H72" s="6" t="n">
-        <v>40</v>
+      <c r="G72" s="9" t="n"/>
+      <c r="H72" s="9" t="inlineStr">
+        <is>
+          <t>yc</t>
+        </is>
       </c>
       <c r="I72" s="6" t="n">
         <v>40</v>
       </c>
       <c r="J72" s="6" t="n">
+        <v>40</v>
+      </c>
+      <c r="K72" s="6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3676,24 +3731,25 @@
           <t>ถุงกระดาษแก้วคู่</t>
         </is>
       </c>
-      <c r="E73" s="7" t="inlineStr">
+      <c r="E73" s="8" t="n"/>
+      <c r="F73" s="7" t="inlineStr">
         <is>
           <t>ใบ</t>
         </is>
       </c>
-      <c r="F73" s="8" t="n"/>
-      <c r="G73" s="8" t="inlineStr">
-        <is>
-          <t>yc</t>
-        </is>
-      </c>
-      <c r="H73" s="6" t="n">
-        <v>40</v>
+      <c r="G73" s="9" t="n"/>
+      <c r="H73" s="9" t="inlineStr">
+        <is>
+          <t>yc</t>
+        </is>
       </c>
       <c r="I73" s="6" t="n">
         <v>40</v>
       </c>
       <c r="J73" s="6" t="n">
+        <v>40</v>
+      </c>
+      <c r="K73" s="6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3716,24 +3772,25 @@
           <t>ถุงกระดาษใหญ่</t>
         </is>
       </c>
-      <c r="E74" s="7" t="inlineStr">
+      <c r="E74" s="8" t="n"/>
+      <c r="F74" s="7" t="inlineStr">
         <is>
           <t>ใบ</t>
         </is>
       </c>
-      <c r="F74" s="8" t="n"/>
-      <c r="G74" s="8" t="inlineStr">
-        <is>
-          <t>yc</t>
-        </is>
-      </c>
-      <c r="H74" s="6" t="n">
-        <v>30</v>
+      <c r="G74" s="9" t="n"/>
+      <c r="H74" s="9" t="inlineStr">
+        <is>
+          <t>yc</t>
+        </is>
       </c>
       <c r="I74" s="6" t="n">
         <v>30</v>
       </c>
       <c r="J74" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="K74" s="6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3756,24 +3813,25 @@
           <t>กระดาษกันหก</t>
         </is>
       </c>
-      <c r="E75" s="7" t="inlineStr">
+      <c r="E75" s="8" t="n"/>
+      <c r="F75" s="7" t="inlineStr">
         <is>
           <t>ห่อ (500ชิ้น)</t>
         </is>
       </c>
-      <c r="F75" s="8" t="n"/>
-      <c r="G75" s="8" t="inlineStr">
-        <is>
-          <t>yc</t>
-        </is>
-      </c>
-      <c r="H75" s="6" t="n">
-        <v>1</v>
+      <c r="G75" s="9" t="n"/>
+      <c r="H75" s="9" t="inlineStr">
+        <is>
+          <t>yc</t>
+        </is>
       </c>
       <c r="I75" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="J75" s="6" t="n"/>
+      <c r="J75" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K75" s="6" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="6" t="n">
@@ -3794,24 +3852,25 @@
           <t>ฟอยล์แก้ว</t>
         </is>
       </c>
-      <c r="E76" s="7" t="inlineStr">
+      <c r="E76" s="8" t="n"/>
+      <c r="F76" s="7" t="inlineStr">
         <is>
           <t>อัน</t>
         </is>
       </c>
-      <c r="F76" s="8" t="n"/>
-      <c r="G76" s="8" t="inlineStr">
-        <is>
-          <t>yc</t>
-        </is>
-      </c>
-      <c r="H76" s="6" t="n">
-        <v>30</v>
+      <c r="G76" s="9" t="n"/>
+      <c r="H76" s="9" t="inlineStr">
+        <is>
+          <t>yc</t>
+        </is>
       </c>
       <c r="I76" s="6" t="n">
         <v>30</v>
       </c>
       <c r="J76" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="K76" s="6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3834,24 +3893,25 @@
           <t>ฐานรองแก้วเดี่ยว</t>
         </is>
       </c>
-      <c r="E77" s="7" t="inlineStr">
+      <c r="E77" s="8" t="n"/>
+      <c r="F77" s="7" t="inlineStr">
         <is>
           <t>อัน</t>
         </is>
       </c>
-      <c r="F77" s="8" t="n"/>
-      <c r="G77" s="8" t="inlineStr">
-        <is>
-          <t>yc</t>
-        </is>
-      </c>
-      <c r="H77" s="6" t="n">
-        <v>40</v>
+      <c r="G77" s="9" t="n"/>
+      <c r="H77" s="9" t="inlineStr">
+        <is>
+          <t>yc</t>
+        </is>
       </c>
       <c r="I77" s="6" t="n">
         <v>40</v>
       </c>
       <c r="J77" s="6" t="n">
+        <v>40</v>
+      </c>
+      <c r="K77" s="6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3874,24 +3934,25 @@
           <t>ฐานรองแก้ว (คู่)</t>
         </is>
       </c>
-      <c r="E78" s="7" t="inlineStr">
+      <c r="E78" s="8" t="n"/>
+      <c r="F78" s="7" t="inlineStr">
         <is>
           <t>อัน</t>
         </is>
       </c>
-      <c r="F78" s="8" t="n"/>
-      <c r="G78" s="8" t="inlineStr">
-        <is>
-          <t>yc</t>
-        </is>
-      </c>
-      <c r="H78" s="6" t="n">
-        <v>30</v>
+      <c r="G78" s="9" t="n"/>
+      <c r="H78" s="9" t="inlineStr">
+        <is>
+          <t>yc</t>
+        </is>
       </c>
       <c r="I78" s="6" t="n">
         <v>30</v>
       </c>
       <c r="J78" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="K78" s="6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3914,24 +3975,25 @@
           <t>Zip Bag Small / ถุงซิป</t>
         </is>
       </c>
-      <c r="E79" s="7" t="inlineStr">
+      <c r="E79" s="8" t="n"/>
+      <c r="F79" s="7" t="inlineStr">
         <is>
           <t>Pack</t>
         </is>
       </c>
-      <c r="F79" s="8" t="n"/>
-      <c r="G79" s="8" t="inlineStr">
-        <is>
-          <t>yc</t>
-        </is>
-      </c>
-      <c r="H79" s="6" t="n">
-        <v>1</v>
+      <c r="G79" s="9" t="n"/>
+      <c r="H79" s="9" t="inlineStr">
+        <is>
+          <t>yc</t>
+        </is>
       </c>
       <c r="I79" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J79" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K79" s="6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3954,24 +4016,25 @@
           <t>Bag 4x14</t>
         </is>
       </c>
-      <c r="E80" s="7" t="inlineStr">
+      <c r="E80" s="8" t="n"/>
+      <c r="F80" s="7" t="inlineStr">
         <is>
           <t>Pack</t>
         </is>
       </c>
-      <c r="F80" s="8" t="n"/>
-      <c r="G80" s="8" t="inlineStr">
-        <is>
-          <t>yc</t>
-        </is>
-      </c>
-      <c r="H80" s="6" t="n">
-        <v>2</v>
+      <c r="G80" s="9" t="n"/>
+      <c r="H80" s="9" t="inlineStr">
+        <is>
+          <t>yc</t>
+        </is>
       </c>
       <c r="I80" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="J80" s="6" t="n"/>
+      <c r="J80" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="K80" s="6" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="6" t="n">
@@ -3992,24 +4055,25 @@
           <t>Bag 6x14</t>
         </is>
       </c>
-      <c r="E81" s="7" t="inlineStr">
+      <c r="E81" s="8" t="n"/>
+      <c r="F81" s="7" t="inlineStr">
         <is>
           <t>Pack</t>
         </is>
       </c>
-      <c r="F81" s="8" t="n"/>
-      <c r="G81" s="8" t="inlineStr">
-        <is>
-          <t>yc</t>
-        </is>
-      </c>
-      <c r="H81" s="6" t="n">
-        <v>2</v>
+      <c r="G81" s="9" t="n"/>
+      <c r="H81" s="9" t="inlineStr">
+        <is>
+          <t>yc</t>
+        </is>
       </c>
       <c r="I81" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="J81" s="6" t="n"/>
+      <c r="J81" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="K81" s="6" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="6" t="n">
@@ -4030,24 +4094,25 @@
           <t>Bag 8x14</t>
         </is>
       </c>
-      <c r="E82" s="7" t="inlineStr">
+      <c r="E82" s="8" t="n"/>
+      <c r="F82" s="7" t="inlineStr">
         <is>
           <t>Pack</t>
         </is>
       </c>
-      <c r="F82" s="8" t="n"/>
-      <c r="G82" s="8" t="inlineStr">
-        <is>
-          <t>yc</t>
-        </is>
-      </c>
-      <c r="H82" s="6" t="n">
-        <v>2</v>
+      <c r="G82" s="9" t="n"/>
+      <c r="H82" s="9" t="inlineStr">
+        <is>
+          <t>yc</t>
+        </is>
       </c>
       <c r="I82" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="J82" s="6" t="n"/>
+      <c r="J82" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="K82" s="6" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="6" t="n">
@@ -4068,24 +4133,25 @@
           <t>Bag 9x14</t>
         </is>
       </c>
-      <c r="E83" s="7" t="inlineStr">
+      <c r="E83" s="8" t="n"/>
+      <c r="F83" s="7" t="inlineStr">
         <is>
           <t>Pack</t>
         </is>
       </c>
-      <c r="F83" s="8" t="n"/>
-      <c r="G83" s="8" t="inlineStr">
-        <is>
-          <t>yc</t>
-        </is>
-      </c>
-      <c r="H83" s="6" t="n">
-        <v>2</v>
+      <c r="G83" s="9" t="n"/>
+      <c r="H83" s="9" t="inlineStr">
+        <is>
+          <t>yc</t>
+        </is>
       </c>
       <c r="I83" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="J83" s="6" t="n"/>
+      <c r="J83" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="K83" s="6" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="6" t="n">
@@ -4106,24 +4172,25 @@
           <t>Bag Sticker สติ๊กเกอร์ลิ้น</t>
         </is>
       </c>
-      <c r="E84" s="7" t="inlineStr">
+      <c r="E84" s="8" t="n"/>
+      <c r="F84" s="7" t="inlineStr">
         <is>
           <t>Sheet</t>
         </is>
       </c>
-      <c r="F84" s="8" t="n"/>
-      <c r="G84" s="8" t="inlineStr">
-        <is>
-          <t>yc</t>
-        </is>
-      </c>
-      <c r="H84" s="6" t="n">
-        <v>4</v>
+      <c r="G84" s="9" t="n"/>
+      <c r="H84" s="9" t="inlineStr">
+        <is>
+          <t>yc</t>
+        </is>
       </c>
       <c r="I84" s="6" t="n">
         <v>4</v>
       </c>
       <c r="J84" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="K84" s="6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4146,24 +4213,25 @@
           <t>Sticker Roll (สก๊อตเทป)</t>
         </is>
       </c>
-      <c r="E85" s="7" t="inlineStr">
+      <c r="E85" s="8" t="n"/>
+      <c r="F85" s="7" t="inlineStr">
         <is>
           <t>Roll</t>
         </is>
       </c>
-      <c r="F85" s="8" t="n"/>
-      <c r="G85" s="8" t="inlineStr">
-        <is>
-          <t>yc</t>
-        </is>
-      </c>
-      <c r="H85" s="6" t="n">
-        <v>2</v>
+      <c r="G85" s="9" t="n"/>
+      <c r="H85" s="9" t="inlineStr">
+        <is>
+          <t>yc</t>
+        </is>
       </c>
       <c r="I85" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="J85" s="6" t="n"/>
+      <c r="J85" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="K85" s="6" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="6" t="n">
@@ -4184,24 +4252,25 @@
           <t>Print Paper กระดาษปริ้น</t>
         </is>
       </c>
-      <c r="E86" s="7" t="inlineStr">
+      <c r="E86" s="8" t="n"/>
+      <c r="F86" s="7" t="inlineStr">
         <is>
           <t>Roll</t>
         </is>
       </c>
-      <c r="F86" s="8" t="n"/>
-      <c r="G86" s="8" t="inlineStr">
-        <is>
-          <t>yc</t>
-        </is>
-      </c>
-      <c r="H86" s="6" t="n">
-        <v>3</v>
+      <c r="G86" s="9" t="n"/>
+      <c r="H86" s="9" t="inlineStr">
+        <is>
+          <t>yc</t>
+        </is>
       </c>
       <c r="I86" s="6" t="n">
         <v>3</v>
       </c>
       <c r="J86" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="K86" s="6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4224,24 +4293,25 @@
           <t>Gloves YG S / ถุงมือ</t>
         </is>
       </c>
-      <c r="E87" s="7" t="inlineStr">
+      <c r="E87" s="8" t="n"/>
+      <c r="F87" s="7" t="inlineStr">
         <is>
           <t>Box</t>
         </is>
       </c>
-      <c r="F87" s="8" t="n"/>
-      <c r="G87" s="8" t="inlineStr">
-        <is>
-          <t>yc</t>
-        </is>
-      </c>
-      <c r="H87" s="6" t="n">
-        <v>1</v>
+      <c r="G87" s="9" t="n"/>
+      <c r="H87" s="9" t="inlineStr">
+        <is>
+          <t>yc</t>
+        </is>
       </c>
       <c r="I87" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="J87" s="6" t="n"/>
+      <c r="J87" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K87" s="6" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="6" t="n">
@@ -4262,24 +4332,25 @@
           <t>Gloves YG M / ถุงมือ</t>
         </is>
       </c>
-      <c r="E88" s="7" t="inlineStr">
+      <c r="E88" s="8" t="n"/>
+      <c r="F88" s="7" t="inlineStr">
         <is>
           <t>Box</t>
         </is>
       </c>
-      <c r="F88" s="8" t="n"/>
-      <c r="G88" s="8" t="inlineStr">
-        <is>
-          <t>yc</t>
-        </is>
-      </c>
-      <c r="H88" s="6" t="n">
-        <v>1</v>
+      <c r="G88" s="9" t="n"/>
+      <c r="H88" s="9" t="inlineStr">
+        <is>
+          <t>yc</t>
+        </is>
       </c>
       <c r="I88" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="J88" s="6" t="n"/>
+      <c r="J88" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K88" s="6" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="6" t="n">
@@ -4300,24 +4371,25 @@
           <t>Gloves YG L / ถุงมือ</t>
         </is>
       </c>
-      <c r="E89" s="7" t="inlineStr">
+      <c r="E89" s="8" t="n"/>
+      <c r="F89" s="7" t="inlineStr">
         <is>
           <t>Box</t>
         </is>
       </c>
-      <c r="F89" s="8" t="n"/>
-      <c r="G89" s="8" t="inlineStr">
-        <is>
-          <t>yc</t>
-        </is>
-      </c>
-      <c r="H89" s="6" t="n">
-        <v>1</v>
+      <c r="G89" s="9" t="n"/>
+      <c r="H89" s="9" t="inlineStr">
+        <is>
+          <t>yc</t>
+        </is>
       </c>
       <c r="I89" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="J89" s="6" t="n"/>
+      <c r="J89" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K89" s="6" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="6" t="n">
@@ -4338,24 +4410,25 @@
           <t>Black Bag 30x40 / ถุงขยะ</t>
         </is>
       </c>
-      <c r="E90" s="7" t="inlineStr">
+      <c r="E90" s="8" t="n"/>
+      <c r="F90" s="7" t="inlineStr">
         <is>
           <t>Roll</t>
         </is>
       </c>
-      <c r="F90" s="8" t="n"/>
-      <c r="G90" s="8" t="inlineStr">
-        <is>
-          <t>yc</t>
-        </is>
-      </c>
-      <c r="H90" s="6" t="n">
-        <v>1</v>
+      <c r="G90" s="9" t="n"/>
+      <c r="H90" s="9" t="inlineStr">
+        <is>
+          <t>yc</t>
+        </is>
       </c>
       <c r="I90" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="J90" s="6" t="n"/>
+      <c r="J90" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K90" s="6" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="6" t="n">
@@ -4376,22 +4449,23 @@
           <t>Black Bag 24x28 / ถุงขยะ</t>
         </is>
       </c>
-      <c r="E91" s="7" t="inlineStr">
+      <c r="E91" s="8" t="n"/>
+      <c r="F91" s="7" t="inlineStr">
         <is>
           <t>Roll</t>
         </is>
       </c>
-      <c r="F91" s="8" t="n"/>
-      <c r="G91" s="8" t="inlineStr">
-        <is>
-          <t>yc</t>
-        </is>
-      </c>
-      <c r="H91" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I91" s="6" t="n"/>
+      <c r="G91" s="9" t="n"/>
+      <c r="H91" s="9" t="inlineStr">
+        <is>
+          <t>yc</t>
+        </is>
+      </c>
+      <c r="I91" s="6" t="n">
+        <v>1</v>
+      </c>
       <c r="J91" s="6" t="n"/>
+      <c r="K91" s="6" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="6" t="n">
@@ -4412,24 +4486,25 @@
           <t>Dry Tissue / ทิชชู่แห้ง</t>
         </is>
       </c>
-      <c r="E92" s="7" t="inlineStr">
+      <c r="E92" s="8" t="n"/>
+      <c r="F92" s="7" t="inlineStr">
         <is>
           <t>Pack</t>
         </is>
       </c>
-      <c r="F92" s="8" t="n"/>
-      <c r="G92" s="8" t="inlineStr">
-        <is>
-          <t>yc</t>
-        </is>
-      </c>
-      <c r="H92" s="6" t="n">
-        <v>3</v>
+      <c r="G92" s="9" t="n"/>
+      <c r="H92" s="9" t="inlineStr">
+        <is>
+          <t>yc</t>
+        </is>
       </c>
       <c r="I92" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="J92" s="6" t="n"/>
+      <c r="J92" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="K92" s="6" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="6" t="n">
@@ -4450,24 +4525,25 @@
           <t>Wet Tissue / ทิชชู่เปียก</t>
         </is>
       </c>
-      <c r="E93" s="7" t="inlineStr">
+      <c r="E93" s="8" t="n"/>
+      <c r="F93" s="7" t="inlineStr">
         <is>
           <t>Pack</t>
         </is>
       </c>
-      <c r="F93" s="8" t="n"/>
-      <c r="G93" s="8" t="inlineStr">
-        <is>
-          <t>yc</t>
-        </is>
-      </c>
-      <c r="H93" s="6" t="n">
-        <v>2</v>
+      <c r="G93" s="9" t="n"/>
+      <c r="H93" s="9" t="inlineStr">
+        <is>
+          <t>yc</t>
+        </is>
       </c>
       <c r="I93" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="J93" s="6" t="n"/>
+      <c r="J93" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="K93" s="6" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="6" t="n">
@@ -4488,22 +4564,23 @@
           <t>Tissue ทิชชู่ลูกค้า</t>
         </is>
       </c>
-      <c r="E94" s="7" t="inlineStr">
+      <c r="E94" s="8" t="n"/>
+      <c r="F94" s="7" t="inlineStr">
         <is>
           <t>Pack</t>
         </is>
       </c>
-      <c r="F94" s="8" t="n"/>
-      <c r="G94" s="8" t="inlineStr">
-        <is>
-          <t>yc</t>
-        </is>
-      </c>
-      <c r="H94" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I94" s="6" t="n"/>
+      <c r="G94" s="9" t="n"/>
+      <c r="H94" s="9" t="inlineStr">
+        <is>
+          <t>yc</t>
+        </is>
+      </c>
+      <c r="I94" s="6" t="n">
+        <v>1</v>
+      </c>
       <c r="J94" s="6" t="n"/>
+      <c r="K94" s="6" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="6" t="n">
@@ -4524,24 +4601,25 @@
           <t>น้ำยาถูพื้น</t>
         </is>
       </c>
-      <c r="E95" s="7" t="inlineStr">
+      <c r="E95" s="8" t="n"/>
+      <c r="F95" s="7" t="inlineStr">
         <is>
           <t>ขวด</t>
         </is>
       </c>
-      <c r="F95" s="8" t="n"/>
-      <c r="G95" s="8" t="inlineStr">
-        <is>
-          <t>yc</t>
-        </is>
-      </c>
-      <c r="H95" s="6" t="n">
-        <v>1</v>
+      <c r="G95" s="9" t="n"/>
+      <c r="H95" s="9" t="inlineStr">
+        <is>
+          <t>yc</t>
+        </is>
       </c>
       <c r="I95" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="J95" s="6" t="n"/>
+      <c r="J95" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K95" s="6" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="6" t="n">
@@ -4562,24 +4640,25 @@
           <t>น้ำยาตัดไขมัน</t>
         </is>
       </c>
-      <c r="E96" s="7" t="inlineStr">
+      <c r="E96" s="8" t="n"/>
+      <c r="F96" s="7" t="inlineStr">
         <is>
           <t>ขวด</t>
         </is>
       </c>
-      <c r="F96" s="8" t="n"/>
-      <c r="G96" s="8" t="inlineStr">
-        <is>
-          <t>yc</t>
-        </is>
-      </c>
-      <c r="H96" s="6" t="n">
-        <v>1</v>
+      <c r="G96" s="9" t="n"/>
+      <c r="H96" s="9" t="inlineStr">
+        <is>
+          <t>yc</t>
+        </is>
       </c>
       <c r="I96" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="J96" s="6" t="n"/>
+      <c r="J96" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K96" s="6" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="6" t="n">
@@ -4600,24 +4679,25 @@
           <t>น้ำยาล้างจาน</t>
         </is>
       </c>
-      <c r="E97" s="7" t="inlineStr">
+      <c r="E97" s="8" t="n"/>
+      <c r="F97" s="7" t="inlineStr">
         <is>
           <t>แพค</t>
         </is>
       </c>
-      <c r="F97" s="8" t="n"/>
-      <c r="G97" s="8" t="inlineStr">
-        <is>
-          <t>yc</t>
-        </is>
-      </c>
-      <c r="H97" s="6" t="n">
-        <v>1</v>
+      <c r="G97" s="9" t="n"/>
+      <c r="H97" s="9" t="inlineStr">
+        <is>
+          <t>yc</t>
+        </is>
       </c>
       <c r="I97" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="J97" s="6" t="n"/>
+      <c r="J97" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K97" s="6" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="6" t="n">
@@ -4638,24 +4718,25 @@
           <t>น้ำยาอเนกประสงค์</t>
         </is>
       </c>
-      <c r="E98" s="7" t="inlineStr">
+      <c r="E98" s="8" t="n"/>
+      <c r="F98" s="7" t="inlineStr">
         <is>
           <t>ขวด</t>
         </is>
       </c>
-      <c r="F98" s="8" t="n"/>
-      <c r="G98" s="8" t="inlineStr">
-        <is>
-          <t>yc</t>
-        </is>
-      </c>
-      <c r="H98" s="6" t="n">
-        <v>1</v>
+      <c r="G98" s="9" t="n"/>
+      <c r="H98" s="9" t="inlineStr">
+        <is>
+          <t>yc</t>
+        </is>
       </c>
       <c r="I98" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="J98" s="6" t="n"/>
+      <c r="J98" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K98" s="6" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="6" t="n">
@@ -4676,24 +4757,25 @@
           <t>น้ำยาล้างเครื่องไอดิม</t>
         </is>
       </c>
-      <c r="E99" s="7" t="inlineStr">
+      <c r="E99" s="8" t="n"/>
+      <c r="F99" s="7" t="inlineStr">
         <is>
           <t>ห่อ</t>
         </is>
       </c>
-      <c r="F99" s="8" t="n"/>
-      <c r="G99" s="8" t="inlineStr">
-        <is>
-          <t>yc</t>
-        </is>
-      </c>
-      <c r="H99" s="6" t="n">
-        <v>1</v>
+      <c r="G99" s="9" t="n"/>
+      <c r="H99" s="9" t="inlineStr">
+        <is>
+          <t>yc</t>
+        </is>
       </c>
       <c r="I99" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="J99" s="6" t="n"/>
+      <c r="J99" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K99" s="6" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="6" t="n">
@@ -4714,24 +4796,25 @@
           <t>Wake Up Call (1)</t>
         </is>
       </c>
-      <c r="E100" s="7" t="inlineStr">
+      <c r="E100" s="8" t="n"/>
+      <c r="F100" s="7" t="inlineStr">
         <is>
           <t>10ถุง/Pack</t>
         </is>
       </c>
-      <c r="F100" s="8" t="n"/>
-      <c r="G100" s="8" t="inlineStr">
-        <is>
-          <t>yc</t>
-        </is>
-      </c>
-      <c r="H100" s="6" t="n">
-        <v>20</v>
+      <c r="G100" s="9" t="n"/>
+      <c r="H100" s="9" t="inlineStr">
+        <is>
+          <t>yc</t>
+        </is>
       </c>
       <c r="I100" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="J100" s="6" t="n"/>
+      <c r="J100" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="K100" s="6" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="6" t="n">
@@ -4752,24 +4835,25 @@
           <t>Energy Sip (2)</t>
         </is>
       </c>
-      <c r="E101" s="7" t="inlineStr">
+      <c r="E101" s="8" t="n"/>
+      <c r="F101" s="7" t="inlineStr">
         <is>
           <t>10ถุง/Pack</t>
         </is>
       </c>
-      <c r="F101" s="8" t="n"/>
-      <c r="G101" s="8" t="inlineStr">
-        <is>
-          <t>yc</t>
-        </is>
-      </c>
-      <c r="H101" s="6" t="n">
-        <v>20</v>
+      <c r="G101" s="9" t="n"/>
+      <c r="H101" s="9" t="inlineStr">
+        <is>
+          <t>yc</t>
+        </is>
       </c>
       <c r="I101" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="J101" s="6" t="n"/>
+      <c r="J101" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="K101" s="6" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="6" t="n">
@@ -4790,24 +4874,25 @@
           <t>Yellow Madness (3)</t>
         </is>
       </c>
-      <c r="E102" s="7" t="inlineStr">
+      <c r="E102" s="8" t="n"/>
+      <c r="F102" s="7" t="inlineStr">
         <is>
           <t>10ถุง/Pack</t>
         </is>
       </c>
-      <c r="F102" s="8" t="n"/>
-      <c r="G102" s="8" t="inlineStr">
-        <is>
-          <t>yc</t>
-        </is>
-      </c>
-      <c r="H102" s="6" t="n">
-        <v>20</v>
+      <c r="G102" s="9" t="n"/>
+      <c r="H102" s="9" t="inlineStr">
+        <is>
+          <t>yc</t>
+        </is>
       </c>
       <c r="I102" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="J102" s="6" t="n"/>
+      <c r="J102" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="K102" s="6" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="6" t="n">
@@ -4828,24 +4913,25 @@
           <t>Ready to Glow (5)</t>
         </is>
       </c>
-      <c r="E103" s="7" t="inlineStr">
+      <c r="E103" s="8" t="n"/>
+      <c r="F103" s="7" t="inlineStr">
         <is>
           <t>10ถุง/Pack</t>
         </is>
       </c>
-      <c r="F103" s="8" t="n"/>
-      <c r="G103" s="8" t="inlineStr">
-        <is>
-          <t>yc</t>
-        </is>
-      </c>
-      <c r="H103" s="6" t="n">
-        <v>20</v>
+      <c r="G103" s="9" t="n"/>
+      <c r="H103" s="9" t="inlineStr">
+        <is>
+          <t>yc</t>
+        </is>
       </c>
       <c r="I103" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="J103" s="6" t="n"/>
+      <c r="J103" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="K103" s="6" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="6" t="n">
@@ -4866,24 +4952,25 @@
           <t>ผงโกโก้ (COCOA)</t>
         </is>
       </c>
-      <c r="E104" s="7" t="inlineStr">
+      <c r="E104" s="8" t="n"/>
+      <c r="F104" s="7" t="inlineStr">
         <is>
           <t>Bag</t>
         </is>
       </c>
-      <c r="F104" s="8" t="n"/>
-      <c r="G104" s="8" t="inlineStr">
-        <is>
-          <t>yc</t>
-        </is>
-      </c>
-      <c r="H104" s="6" t="n">
-        <v>1</v>
+      <c r="G104" s="9" t="n"/>
+      <c r="H104" s="9" t="inlineStr">
+        <is>
+          <t>yc</t>
+        </is>
       </c>
       <c r="I104" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="J104" s="6" t="n"/>
+      <c r="J104" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K104" s="6" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="6" t="n">
@@ -4904,24 +4991,25 @@
           <t>ผงมาคิ (MAQUI)</t>
         </is>
       </c>
-      <c r="E105" s="7" t="inlineStr">
+      <c r="E105" s="8" t="n"/>
+      <c r="F105" s="7" t="inlineStr">
         <is>
           <t>Bag</t>
         </is>
       </c>
-      <c r="F105" s="8" t="n"/>
-      <c r="G105" s="8" t="inlineStr">
-        <is>
-          <t>yc</t>
-        </is>
-      </c>
-      <c r="H105" s="6" t="n">
-        <v>1</v>
+      <c r="G105" s="9" t="n"/>
+      <c r="H105" s="9" t="inlineStr">
+        <is>
+          <t>yc</t>
+        </is>
       </c>
       <c r="I105" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="J105" s="6" t="n"/>
+      <c r="J105" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K105" s="6" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="6" t="n">
@@ -4942,24 +5030,25 @@
           <t>ผงคาม (CAMU)</t>
         </is>
       </c>
-      <c r="E106" s="7" t="inlineStr">
+      <c r="E106" s="8" t="n"/>
+      <c r="F106" s="7" t="inlineStr">
         <is>
           <t>Bag</t>
         </is>
       </c>
-      <c r="F106" s="8" t="n"/>
-      <c r="G106" s="8" t="inlineStr">
-        <is>
-          <t>yc</t>
-        </is>
-      </c>
-      <c r="H106" s="6" t="n">
-        <v>1</v>
+      <c r="G106" s="9" t="n"/>
+      <c r="H106" s="9" t="inlineStr">
+        <is>
+          <t>yc</t>
+        </is>
       </c>
       <c r="I106" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="J106" s="6" t="n"/>
+      <c r="J106" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K106" s="6" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="6" t="n">
@@ -4980,24 +5069,25 @@
           <t>น้ำเชื่อม (Syrup)</t>
         </is>
       </c>
-      <c r="E107" s="7" t="inlineStr">
+      <c r="E107" s="8" t="n"/>
+      <c r="F107" s="7" t="inlineStr">
         <is>
           <t>Bottle</t>
         </is>
       </c>
-      <c r="F107" s="8" t="n"/>
-      <c r="G107" s="8" t="inlineStr">
-        <is>
-          <t>yc</t>
-        </is>
-      </c>
-      <c r="H107" s="6" t="n">
-        <v>1</v>
+      <c r="G107" s="9" t="n"/>
+      <c r="H107" s="9" t="inlineStr">
+        <is>
+          <t>yc</t>
+        </is>
       </c>
       <c r="I107" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="J107" s="6" t="n"/>
+      <c r="J107" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K107" s="6" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="6" t="n">
@@ -5018,24 +5108,25 @@
           <t>Biscoff Spread เล็ก</t>
         </is>
       </c>
-      <c r="E108" s="7" t="inlineStr">
+      <c r="E108" s="8" t="n"/>
+      <c r="F108" s="7" t="inlineStr">
         <is>
           <t>Bottle</t>
         </is>
       </c>
-      <c r="F108" s="8" t="n"/>
-      <c r="G108" s="8" t="inlineStr">
-        <is>
-          <t>yc</t>
-        </is>
-      </c>
-      <c r="H108" s="6" t="n">
-        <v>2</v>
+      <c r="G108" s="9" t="n"/>
+      <c r="H108" s="9" t="inlineStr">
+        <is>
+          <t>yc</t>
+        </is>
       </c>
       <c r="I108" s="6" t="n">
         <v>2</v>
       </c>
       <c r="J108" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="K108" s="6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5058,24 +5149,25 @@
           <t>Biscoff Spread ใหญ่</t>
         </is>
       </c>
-      <c r="E109" s="7" t="inlineStr">
+      <c r="E109" s="8" t="n"/>
+      <c r="F109" s="7" t="inlineStr">
         <is>
           <t>Bottle</t>
         </is>
       </c>
-      <c r="F109" s="8" t="n"/>
-      <c r="G109" s="8" t="inlineStr">
-        <is>
-          <t>yc</t>
-        </is>
-      </c>
-      <c r="H109" s="6" t="n">
-        <v>0</v>
+      <c r="G109" s="9" t="n"/>
+      <c r="H109" s="9" t="inlineStr">
+        <is>
+          <t>yc</t>
+        </is>
       </c>
       <c r="I109" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="J109" s="6" t="n"/>
+      <c r="J109" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K109" s="6" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="6" t="n">
@@ -5096,24 +5188,25 @@
           <t>ซอส Chocolate</t>
         </is>
       </c>
-      <c r="E110" s="7" t="inlineStr">
+      <c r="E110" s="8" t="n"/>
+      <c r="F110" s="7" t="inlineStr">
         <is>
           <t>500/Bag</t>
         </is>
       </c>
-      <c r="F110" s="8" t="n"/>
-      <c r="G110" s="8" t="inlineStr">
-        <is>
-          <t>yc</t>
-        </is>
-      </c>
-      <c r="H110" s="6" t="n">
-        <v>1</v>
+      <c r="G110" s="9" t="n"/>
+      <c r="H110" s="9" t="inlineStr">
+        <is>
+          <t>yc</t>
+        </is>
       </c>
       <c r="I110" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J110" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K110" s="6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5136,24 +5229,25 @@
           <t>ซอส Strawberry</t>
         </is>
       </c>
-      <c r="E111" s="7" t="inlineStr">
+      <c r="E111" s="8" t="n"/>
+      <c r="F111" s="7" t="inlineStr">
         <is>
           <t>500/Bag</t>
         </is>
       </c>
-      <c r="F111" s="8" t="n"/>
-      <c r="G111" s="8" t="inlineStr">
-        <is>
-          <t>yc</t>
-        </is>
-      </c>
-      <c r="H111" s="6" t="n">
-        <v>1</v>
+      <c r="G111" s="9" t="n"/>
+      <c r="H111" s="9" t="inlineStr">
+        <is>
+          <t>yc</t>
+        </is>
       </c>
       <c r="I111" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J111" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K111" s="6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5176,24 +5270,25 @@
           <t>ปีโป้</t>
         </is>
       </c>
-      <c r="E112" s="7" t="inlineStr">
+      <c r="E112" s="8" t="n"/>
+      <c r="F112" s="7" t="inlineStr">
         <is>
           <t>40 อัน/Bag</t>
         </is>
       </c>
-      <c r="F112" s="8" t="n"/>
-      <c r="G112" s="8" t="inlineStr">
-        <is>
-          <t>yc</t>
-        </is>
-      </c>
-      <c r="H112" s="6" t="n">
-        <v>1</v>
+      <c r="G112" s="9" t="n"/>
+      <c r="H112" s="9" t="inlineStr">
+        <is>
+          <t>yc</t>
+        </is>
       </c>
       <c r="I112" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J112" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K112" s="6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5216,24 +5311,25 @@
           <t>ปีโป้ลิ้นจี่</t>
         </is>
       </c>
-      <c r="E113" s="7" t="inlineStr">
+      <c r="E113" s="8" t="n"/>
+      <c r="F113" s="7" t="inlineStr">
         <is>
           <t>กล่อง</t>
         </is>
       </c>
-      <c r="F113" s="8" t="n"/>
-      <c r="G113" s="8" t="inlineStr">
-        <is>
-          <t>yc</t>
-        </is>
-      </c>
-      <c r="H113" s="6" t="n">
-        <v>1</v>
+      <c r="G113" s="9" t="n"/>
+      <c r="H113" s="9" t="inlineStr">
+        <is>
+          <t>yc</t>
+        </is>
       </c>
       <c r="I113" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J113" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K113" s="6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5256,22 +5352,23 @@
           <t>พิสตาชิโอ้เครป</t>
         </is>
       </c>
-      <c r="E114" s="7" t="inlineStr">
+      <c r="E114" s="8" t="n"/>
+      <c r="F114" s="7" t="inlineStr">
         <is>
           <t>กรัม</t>
         </is>
       </c>
-      <c r="F114" s="8" t="n"/>
-      <c r="G114" s="8" t="inlineStr">
-        <is>
-          <t>yc</t>
-        </is>
-      </c>
-      <c r="H114" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I114" s="6" t="n"/>
+      <c r="G114" s="9" t="n"/>
+      <c r="H114" s="9" t="inlineStr">
+        <is>
+          <t>yc</t>
+        </is>
+      </c>
+      <c r="I114" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="J114" s="6" t="n"/>
+      <c r="K114" s="6" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="6" t="n">
@@ -5292,22 +5389,23 @@
           <t>พิสตาชิโอ้บัตเตอร์</t>
         </is>
       </c>
-      <c r="E115" s="7" t="inlineStr">
+      <c r="E115" s="8" t="n"/>
+      <c r="F115" s="7" t="inlineStr">
         <is>
           <t>กรัม</t>
         </is>
       </c>
-      <c r="F115" s="8" t="n"/>
-      <c r="G115" s="8" t="inlineStr">
-        <is>
-          <t>yc</t>
-        </is>
-      </c>
-      <c r="H115" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I115" s="6" t="n"/>
+      <c r="G115" s="9" t="n"/>
+      <c r="H115" s="9" t="inlineStr">
+        <is>
+          <t>yc</t>
+        </is>
+      </c>
+      <c r="I115" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="J115" s="6" t="n"/>
+      <c r="K115" s="6" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="6" t="n">
@@ -5328,22 +5426,23 @@
           <t>พิสตาชิโอ้ท๊อปปิ้ง</t>
         </is>
       </c>
-      <c r="E116" s="7" t="inlineStr">
+      <c r="E116" s="8" t="n"/>
+      <c r="F116" s="7" t="inlineStr">
         <is>
           <t>กรัม</t>
         </is>
       </c>
-      <c r="F116" s="8" t="n"/>
-      <c r="G116" s="8" t="inlineStr">
-        <is>
-          <t>yc</t>
-        </is>
-      </c>
-      <c r="H116" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I116" s="6" t="n"/>
+      <c r="G116" s="9" t="n"/>
+      <c r="H116" s="9" t="inlineStr">
+        <is>
+          <t>yc</t>
+        </is>
+      </c>
+      <c r="I116" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="J116" s="6" t="n"/>
+      <c r="K116" s="6" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="6" t="n">
@@ -5364,26 +5463,25 @@
           <t>Cranberry Cookies</t>
         </is>
       </c>
-      <c r="E117" s="7" t="inlineStr">
+      <c r="E117" s="8" t="n"/>
+      <c r="F117" s="7" t="inlineStr">
         <is>
           <t>กระปุก</t>
         </is>
       </c>
-      <c r="F117" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="G117" s="8" t="inlineStr">
-        <is>
-          <t>yc</t>
-        </is>
-      </c>
-      <c r="H117" s="6" t="n">
-        <v>0</v>
+      <c r="G117" s="9" t="n"/>
+      <c r="H117" s="9" t="inlineStr">
+        <is>
+          <t>yc</t>
+        </is>
       </c>
       <c r="I117" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="J117" s="6" t="n"/>
+      <c r="J117" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K117" s="6" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="6" t="n">
@@ -5404,24 +5502,25 @@
           <t>น้ำยาล้างผลไม้</t>
         </is>
       </c>
-      <c r="E118" s="7" t="inlineStr">
+      <c r="E118" s="8" t="n"/>
+      <c r="F118" s="7" t="inlineStr">
         <is>
           <t>ขวด</t>
         </is>
       </c>
-      <c r="F118" s="8" t="n"/>
-      <c r="G118" s="8" t="inlineStr">
-        <is>
-          <t>yc</t>
-        </is>
-      </c>
-      <c r="H118" s="6" t="n">
-        <v>1</v>
+      <c r="G118" s="9" t="n"/>
+      <c r="H118" s="9" t="inlineStr">
+        <is>
+          <t>yc</t>
+        </is>
       </c>
       <c r="I118" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J118" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K118" s="6" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5444,26 +5543,27 @@
           <t>น้ำยาซักผ้า</t>
         </is>
       </c>
-      <c r="E119" s="7" t="inlineStr">
+      <c r="E119" s="8" t="n"/>
+      <c r="F119" s="7" t="inlineStr">
         <is>
           <t>ขวด</t>
         </is>
       </c>
-      <c r="F119" s="8" t="n"/>
-      <c r="G119" s="8" t="inlineStr">
-        <is>
-          <t>yc</t>
-        </is>
-      </c>
-      <c r="H119" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I119" s="6" t="n"/>
+      <c r="G119" s="9" t="n"/>
+      <c r="H119" s="9" t="inlineStr">
+        <is>
+          <t>yc</t>
+        </is>
+      </c>
+      <c r="I119" s="6" t="n">
+        <v>1</v>
+      </c>
       <c r="J119" s="6" t="n"/>
+      <c r="K119" s="6" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="G2 G3 G4 G5 G6 G7 G8 G9 G10 G11 G12 G13 G14 G15 G16 G17 G18 G19 G20 G21 G22 G23 G24 G25 G26 G27 G28 G29 G30 G31 G32 G33 G34 G35 G36 G37 G38 G39 G40 G41 G42 G43 G44 G45 G46 G47 G48 G49 G50 G51 G52 G53 G54 G55 G56 G57 G58 G59 G60 G61 G62 G63 G64 G65 G66 G67 G68 G69 G70 G71 G72 G73 G74 G75 G76 G77 G78 G79 G80 G81 G82 G83 G84 G85 G86 G87 G88 G89 G90 G91 G92 G93 G94 G95 G96 G97 G98 G99 G100 G101 G102 G103 G104 G105 G106 G107 G108 G109 G110 G111 G112 G113 G114 G115 G116 G117 G118 G119" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Invalid brand" error="Choose yc, staple, or shared from the list." type="list">
+    <dataValidation sqref="H2 H3 H4 H5 H6 H7 H8 H9 H10 H11 H12 H13 H14 H15 H16 H17 H18 H19 H20 H21 H22 H23 H24 H25 H26 H27 H28 H29 H30 H31 H32 H33 H34 H35 H36 H37 H38 H39 H40 H41 H42 H43 H44 H45 H46 H47 H48 H49 H50 H51 H52 H53 H54 H55 H56 H57 H58 H59 H60 H61 H62 H63 H64 H65 H66 H67 H68 H69 H70 H71 H72 H73 H74 H75 H76 H77 H78 H79 H80 H81 H82 H83 H84 H85 H86 H87 H88 H89 H90 H91 H92 H93 H94 H95 H96 H97 H98 H99 H100 H101 H102 H103 H104 H105 H106 H107 H108 H109 H110 H111 H112 H113 H114 H115 H116 H117 H118 H119" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Invalid brand" error="Choose yc, staple, or shared from the list." type="list">
       <formula1>"yc,staple,shared"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5479,7 +5579,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F42"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
@@ -5521,449 +5621,449 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="28" customHeight="1">
-      <c r="A2" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="10" t="inlineStr">
+    <row r="2">
+      <c r="A2" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="11" t="inlineStr">
         <is>
           <t>Belgian Waffle Mix</t>
         </is>
       </c>
-      <c r="C2" s="10" t="inlineStr">
+      <c r="C2" s="11" t="inlineStr">
         <is>
           <t>Staple Bakery</t>
         </is>
       </c>
-      <c r="D2" s="10" t="inlineStr">
+      <c r="D2" s="11" t="inlineStr">
         <is>
           <t>1kg/Bag</t>
         </is>
       </c>
-      <c r="E2" s="9" t="n">
+      <c r="E2" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="F2" s="10" t="inlineStr">
+      <c r="F2" s="11" t="inlineStr">
         <is>
           <t>Example row — delete before sending back, or add rows below</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="n">
+      <c r="A3" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="11" t="inlineStr">
-        <is>
-          <t>Cup (14oz) - Staple</t>
-        </is>
-      </c>
-      <c r="C3" s="11" t="inlineStr">
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>Staple Cup (14oz)</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr">
         <is>
           <t>CUP/ถ้วย</t>
         </is>
       </c>
-      <c r="D3" s="11" t="inlineStr">
+      <c r="D3" s="8" t="inlineStr">
         <is>
           <t>50/pack</t>
         </is>
       </c>
-      <c r="E3" s="8" t="n"/>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>Same size/spec as YC Cup 14oz (it-056) but printed with Staple logo — separate stock item, not shared. Fill in Par NCD.</t>
+      <c r="E3" s="9" t="n"/>
+      <c r="F3" s="8" t="inlineStr">
+        <is>
+          <t>Same size/spec as YC Cup (14oz, it-056) but printed with Staple logo — separate stock item, not shared. Fill in Par NCD.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="n">
+      <c r="A4" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="11" t="n"/>
-      <c r="C4" s="11" t="n"/>
-      <c r="D4" s="11" t="n"/>
-      <c r="E4" s="8" t="n"/>
-      <c r="F4" s="11" t="n"/>
+      <c r="B4" s="8" t="n"/>
+      <c r="C4" s="8" t="n"/>
+      <c r="D4" s="8" t="n"/>
+      <c r="E4" s="9" t="n"/>
+      <c r="F4" s="8" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="n">
+      <c r="A5" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="11" t="n"/>
-      <c r="C5" s="11" t="n"/>
-      <c r="D5" s="11" t="n"/>
-      <c r="E5" s="8" t="n"/>
-      <c r="F5" s="11" t="n"/>
+      <c r="B5" s="8" t="n"/>
+      <c r="C5" s="8" t="n"/>
+      <c r="D5" s="8" t="n"/>
+      <c r="E5" s="9" t="n"/>
+      <c r="F5" s="8" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="n">
+      <c r="A6" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="11" t="n"/>
-      <c r="C6" s="11" t="n"/>
-      <c r="D6" s="11" t="n"/>
-      <c r="E6" s="8" t="n"/>
-      <c r="F6" s="11" t="n"/>
+      <c r="B6" s="8" t="n"/>
+      <c r="C6" s="8" t="n"/>
+      <c r="D6" s="8" t="n"/>
+      <c r="E6" s="9" t="n"/>
+      <c r="F6" s="8" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="n">
+      <c r="A7" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="11" t="n"/>
-      <c r="C7" s="11" t="n"/>
-      <c r="D7" s="11" t="n"/>
-      <c r="E7" s="8" t="n"/>
-      <c r="F7" s="11" t="n"/>
+      <c r="B7" s="8" t="n"/>
+      <c r="C7" s="8" t="n"/>
+      <c r="D7" s="8" t="n"/>
+      <c r="E7" s="9" t="n"/>
+      <c r="F7" s="8" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="n">
+      <c r="A8" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="11" t="n"/>
-      <c r="C8" s="11" t="n"/>
-      <c r="D8" s="11" t="n"/>
-      <c r="E8" s="8" t="n"/>
-      <c r="F8" s="11" t="n"/>
+      <c r="B8" s="8" t="n"/>
+      <c r="C8" s="8" t="n"/>
+      <c r="D8" s="8" t="n"/>
+      <c r="E8" s="9" t="n"/>
+      <c r="F8" s="8" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="n">
+      <c r="A9" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="11" t="n"/>
-      <c r="C9" s="11" t="n"/>
-      <c r="D9" s="11" t="n"/>
-      <c r="E9" s="8" t="n"/>
-      <c r="F9" s="11" t="n"/>
+      <c r="B9" s="8" t="n"/>
+      <c r="C9" s="8" t="n"/>
+      <c r="D9" s="8" t="n"/>
+      <c r="E9" s="9" t="n"/>
+      <c r="F9" s="8" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="n">
+      <c r="A10" s="9" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="11" t="n"/>
-      <c r="C10" s="11" t="n"/>
-      <c r="D10" s="11" t="n"/>
-      <c r="E10" s="8" t="n"/>
-      <c r="F10" s="11" t="n"/>
+      <c r="B10" s="8" t="n"/>
+      <c r="C10" s="8" t="n"/>
+      <c r="D10" s="8" t="n"/>
+      <c r="E10" s="9" t="n"/>
+      <c r="F10" s="8" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="n">
+      <c r="A11" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="11" t="n"/>
-      <c r="C11" s="11" t="n"/>
-      <c r="D11" s="11" t="n"/>
-      <c r="E11" s="8" t="n"/>
-      <c r="F11" s="11" t="n"/>
+      <c r="B11" s="8" t="n"/>
+      <c r="C11" s="8" t="n"/>
+      <c r="D11" s="8" t="n"/>
+      <c r="E11" s="9" t="n"/>
+      <c r="F11" s="8" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="n">
+      <c r="A12" s="9" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="11" t="n"/>
-      <c r="C12" s="11" t="n"/>
-      <c r="D12" s="11" t="n"/>
-      <c r="E12" s="8" t="n"/>
-      <c r="F12" s="11" t="n"/>
+      <c r="B12" s="8" t="n"/>
+      <c r="C12" s="8" t="n"/>
+      <c r="D12" s="8" t="n"/>
+      <c r="E12" s="9" t="n"/>
+      <c r="F12" s="8" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="n">
+      <c r="A13" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="11" t="n"/>
-      <c r="C13" s="11" t="n"/>
-      <c r="D13" s="11" t="n"/>
-      <c r="E13" s="8" t="n"/>
-      <c r="F13" s="11" t="n"/>
+      <c r="B13" s="8" t="n"/>
+      <c r="C13" s="8" t="n"/>
+      <c r="D13" s="8" t="n"/>
+      <c r="E13" s="9" t="n"/>
+      <c r="F13" s="8" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="n">
+      <c r="A14" s="9" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="11" t="n"/>
-      <c r="C14" s="11" t="n"/>
-      <c r="D14" s="11" t="n"/>
-      <c r="E14" s="8" t="n"/>
-      <c r="F14" s="11" t="n"/>
+      <c r="B14" s="8" t="n"/>
+      <c r="C14" s="8" t="n"/>
+      <c r="D14" s="8" t="n"/>
+      <c r="E14" s="9" t="n"/>
+      <c r="F14" s="8" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="8" t="n">
+      <c r="A15" s="9" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="11" t="n"/>
-      <c r="C15" s="11" t="n"/>
-      <c r="D15" s="11" t="n"/>
-      <c r="E15" s="8" t="n"/>
-      <c r="F15" s="11" t="n"/>
+      <c r="B15" s="8" t="n"/>
+      <c r="C15" s="8" t="n"/>
+      <c r="D15" s="8" t="n"/>
+      <c r="E15" s="9" t="n"/>
+      <c r="F15" s="8" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="n">
+      <c r="A16" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="11" t="n"/>
-      <c r="C16" s="11" t="n"/>
-      <c r="D16" s="11" t="n"/>
-      <c r="E16" s="8" t="n"/>
-      <c r="F16" s="11" t="n"/>
+      <c r="B16" s="8" t="n"/>
+      <c r="C16" s="8" t="n"/>
+      <c r="D16" s="8" t="n"/>
+      <c r="E16" s="9" t="n"/>
+      <c r="F16" s="8" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="8" t="n">
+      <c r="A17" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="11" t="n"/>
-      <c r="C17" s="11" t="n"/>
-      <c r="D17" s="11" t="n"/>
-      <c r="E17" s="8" t="n"/>
-      <c r="F17" s="11" t="n"/>
+      <c r="B17" s="8" t="n"/>
+      <c r="C17" s="8" t="n"/>
+      <c r="D17" s="8" t="n"/>
+      <c r="E17" s="9" t="n"/>
+      <c r="F17" s="8" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="n">
+      <c r="A18" s="9" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="11" t="n"/>
-      <c r="C18" s="11" t="n"/>
-      <c r="D18" s="11" t="n"/>
-      <c r="E18" s="8" t="n"/>
-      <c r="F18" s="11" t="n"/>
+      <c r="B18" s="8" t="n"/>
+      <c r="C18" s="8" t="n"/>
+      <c r="D18" s="8" t="n"/>
+      <c r="E18" s="9" t="n"/>
+      <c r="F18" s="8" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="8" t="n">
+      <c r="A19" s="9" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="11" t="n"/>
-      <c r="C19" s="11" t="n"/>
-      <c r="D19" s="11" t="n"/>
-      <c r="E19" s="8" t="n"/>
-      <c r="F19" s="11" t="n"/>
+      <c r="B19" s="8" t="n"/>
+      <c r="C19" s="8" t="n"/>
+      <c r="D19" s="8" t="n"/>
+      <c r="E19" s="9" t="n"/>
+      <c r="F19" s="8" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="8" t="n">
+      <c r="A20" s="9" t="n">
         <v>19</v>
       </c>
-      <c r="B20" s="11" t="n"/>
-      <c r="C20" s="11" t="n"/>
-      <c r="D20" s="11" t="n"/>
-      <c r="E20" s="8" t="n"/>
-      <c r="F20" s="11" t="n"/>
+      <c r="B20" s="8" t="n"/>
+      <c r="C20" s="8" t="n"/>
+      <c r="D20" s="8" t="n"/>
+      <c r="E20" s="9" t="n"/>
+      <c r="F20" s="8" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="8" t="n">
+      <c r="A21" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="11" t="n"/>
-      <c r="C21" s="11" t="n"/>
-      <c r="D21" s="11" t="n"/>
-      <c r="E21" s="8" t="n"/>
-      <c r="F21" s="11" t="n"/>
+      <c r="B21" s="8" t="n"/>
+      <c r="C21" s="8" t="n"/>
+      <c r="D21" s="8" t="n"/>
+      <c r="E21" s="9" t="n"/>
+      <c r="F21" s="8" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="8" t="n">
+      <c r="A22" s="9" t="n">
         <v>21</v>
       </c>
-      <c r="B22" s="11" t="n"/>
-      <c r="C22" s="11" t="n"/>
-      <c r="D22" s="11" t="n"/>
-      <c r="E22" s="8" t="n"/>
-      <c r="F22" s="11" t="n"/>
+      <c r="B22" s="8" t="n"/>
+      <c r="C22" s="8" t="n"/>
+      <c r="D22" s="8" t="n"/>
+      <c r="E22" s="9" t="n"/>
+      <c r="F22" s="8" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="8" t="n">
+      <c r="A23" s="9" t="n">
         <v>22</v>
       </c>
-      <c r="B23" s="11" t="n"/>
-      <c r="C23" s="11" t="n"/>
-      <c r="D23" s="11" t="n"/>
-      <c r="E23" s="8" t="n"/>
-      <c r="F23" s="11" t="n"/>
+      <c r="B23" s="8" t="n"/>
+      <c r="C23" s="8" t="n"/>
+      <c r="D23" s="8" t="n"/>
+      <c r="E23" s="9" t="n"/>
+      <c r="F23" s="8" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="8" t="n">
+      <c r="A24" s="9" t="n">
         <v>23</v>
       </c>
-      <c r="B24" s="11" t="n"/>
-      <c r="C24" s="11" t="n"/>
-      <c r="D24" s="11" t="n"/>
-      <c r="E24" s="8" t="n"/>
-      <c r="F24" s="11" t="n"/>
+      <c r="B24" s="8" t="n"/>
+      <c r="C24" s="8" t="n"/>
+      <c r="D24" s="8" t="n"/>
+      <c r="E24" s="9" t="n"/>
+      <c r="F24" s="8" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="8" t="n">
+      <c r="A25" s="9" t="n">
         <v>24</v>
       </c>
-      <c r="B25" s="11" t="n"/>
-      <c r="C25" s="11" t="n"/>
-      <c r="D25" s="11" t="n"/>
-      <c r="E25" s="8" t="n"/>
-      <c r="F25" s="11" t="n"/>
+      <c r="B25" s="8" t="n"/>
+      <c r="C25" s="8" t="n"/>
+      <c r="D25" s="8" t="n"/>
+      <c r="E25" s="9" t="n"/>
+      <c r="F25" s="8" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="8" t="n">
+      <c r="A26" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="B26" s="11" t="n"/>
-      <c r="C26" s="11" t="n"/>
-      <c r="D26" s="11" t="n"/>
-      <c r="E26" s="8" t="n"/>
-      <c r="F26" s="11" t="n"/>
+      <c r="B26" s="8" t="n"/>
+      <c r="C26" s="8" t="n"/>
+      <c r="D26" s="8" t="n"/>
+      <c r="E26" s="9" t="n"/>
+      <c r="F26" s="8" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="8" t="n">
+      <c r="A27" s="9" t="n">
         <v>26</v>
       </c>
-      <c r="B27" s="11" t="n"/>
-      <c r="C27" s="11" t="n"/>
-      <c r="D27" s="11" t="n"/>
-      <c r="E27" s="8" t="n"/>
-      <c r="F27" s="11" t="n"/>
+      <c r="B27" s="8" t="n"/>
+      <c r="C27" s="8" t="n"/>
+      <c r="D27" s="8" t="n"/>
+      <c r="E27" s="9" t="n"/>
+      <c r="F27" s="8" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="8" t="n">
+      <c r="A28" s="9" t="n">
         <v>27</v>
       </c>
-      <c r="B28" s="11" t="n"/>
-      <c r="C28" s="11" t="n"/>
-      <c r="D28" s="11" t="n"/>
-      <c r="E28" s="8" t="n"/>
-      <c r="F28" s="11" t="n"/>
+      <c r="B28" s="8" t="n"/>
+      <c r="C28" s="8" t="n"/>
+      <c r="D28" s="8" t="n"/>
+      <c r="E28" s="9" t="n"/>
+      <c r="F28" s="8" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="8" t="n">
+      <c r="A29" s="9" t="n">
         <v>28</v>
       </c>
-      <c r="B29" s="11" t="n"/>
-      <c r="C29" s="11" t="n"/>
-      <c r="D29" s="11" t="n"/>
-      <c r="E29" s="8" t="n"/>
-      <c r="F29" s="11" t="n"/>
+      <c r="B29" s="8" t="n"/>
+      <c r="C29" s="8" t="n"/>
+      <c r="D29" s="8" t="n"/>
+      <c r="E29" s="9" t="n"/>
+      <c r="F29" s="8" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="8" t="n">
+      <c r="A30" s="9" t="n">
         <v>29</v>
       </c>
-      <c r="B30" s="11" t="n"/>
-      <c r="C30" s="11" t="n"/>
-      <c r="D30" s="11" t="n"/>
-      <c r="E30" s="8" t="n"/>
-      <c r="F30" s="11" t="n"/>
+      <c r="B30" s="8" t="n"/>
+      <c r="C30" s="8" t="n"/>
+      <c r="D30" s="8" t="n"/>
+      <c r="E30" s="9" t="n"/>
+      <c r="F30" s="8" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="8" t="n">
+      <c r="A31" s="9" t="n">
         <v>30</v>
       </c>
-      <c r="B31" s="11" t="n"/>
-      <c r="C31" s="11" t="n"/>
-      <c r="D31" s="11" t="n"/>
-      <c r="E31" s="8" t="n"/>
-      <c r="F31" s="11" t="n"/>
+      <c r="B31" s="8" t="n"/>
+      <c r="C31" s="8" t="n"/>
+      <c r="D31" s="8" t="n"/>
+      <c r="E31" s="9" t="n"/>
+      <c r="F31" s="8" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="8" t="n">
+      <c r="A32" s="9" t="n">
         <v>31</v>
       </c>
-      <c r="B32" s="11" t="n"/>
-      <c r="C32" s="11" t="n"/>
-      <c r="D32" s="11" t="n"/>
-      <c r="E32" s="8" t="n"/>
-      <c r="F32" s="11" t="n"/>
+      <c r="B32" s="8" t="n"/>
+      <c r="C32" s="8" t="n"/>
+      <c r="D32" s="8" t="n"/>
+      <c r="E32" s="9" t="n"/>
+      <c r="F32" s="8" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="8" t="n">
+      <c r="A33" s="9" t="n">
         <v>32</v>
       </c>
-      <c r="B33" s="11" t="n"/>
-      <c r="C33" s="11" t="n"/>
-      <c r="D33" s="11" t="n"/>
-      <c r="E33" s="8" t="n"/>
-      <c r="F33" s="11" t="n"/>
+      <c r="B33" s="8" t="n"/>
+      <c r="C33" s="8" t="n"/>
+      <c r="D33" s="8" t="n"/>
+      <c r="E33" s="9" t="n"/>
+      <c r="F33" s="8" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="8" t="n">
+      <c r="A34" s="9" t="n">
         <v>33</v>
       </c>
-      <c r="B34" s="11" t="n"/>
-      <c r="C34" s="11" t="n"/>
-      <c r="D34" s="11" t="n"/>
-      <c r="E34" s="8" t="n"/>
-      <c r="F34" s="11" t="n"/>
+      <c r="B34" s="8" t="n"/>
+      <c r="C34" s="8" t="n"/>
+      <c r="D34" s="8" t="n"/>
+      <c r="E34" s="9" t="n"/>
+      <c r="F34" s="8" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="8" t="n">
+      <c r="A35" s="9" t="n">
         <v>34</v>
       </c>
-      <c r="B35" s="11" t="n"/>
-      <c r="C35" s="11" t="n"/>
-      <c r="D35" s="11" t="n"/>
-      <c r="E35" s="8" t="n"/>
-      <c r="F35" s="11" t="n"/>
+      <c r="B35" s="8" t="n"/>
+      <c r="C35" s="8" t="n"/>
+      <c r="D35" s="8" t="n"/>
+      <c r="E35" s="9" t="n"/>
+      <c r="F35" s="8" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="8" t="n">
+      <c r="A36" s="9" t="n">
         <v>35</v>
       </c>
-      <c r="B36" s="11" t="n"/>
-      <c r="C36" s="11" t="n"/>
-      <c r="D36" s="11" t="n"/>
-      <c r="E36" s="8" t="n"/>
-      <c r="F36" s="11" t="n"/>
+      <c r="B36" s="8" t="n"/>
+      <c r="C36" s="8" t="n"/>
+      <c r="D36" s="8" t="n"/>
+      <c r="E36" s="9" t="n"/>
+      <c r="F36" s="8" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="8" t="n">
+      <c r="A37" s="9" t="n">
         <v>36</v>
       </c>
-      <c r="B37" s="11" t="n"/>
-      <c r="C37" s="11" t="n"/>
-      <c r="D37" s="11" t="n"/>
-      <c r="E37" s="8" t="n"/>
-      <c r="F37" s="11" t="n"/>
+      <c r="B37" s="8" t="n"/>
+      <c r="C37" s="8" t="n"/>
+      <c r="D37" s="8" t="n"/>
+      <c r="E37" s="9" t="n"/>
+      <c r="F37" s="8" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="8" t="n">
+      <c r="A38" s="9" t="n">
         <v>37</v>
       </c>
-      <c r="B38" s="11" t="n"/>
-      <c r="C38" s="11" t="n"/>
-      <c r="D38" s="11" t="n"/>
-      <c r="E38" s="8" t="n"/>
-      <c r="F38" s="11" t="n"/>
+      <c r="B38" s="8" t="n"/>
+      <c r="C38" s="8" t="n"/>
+      <c r="D38" s="8" t="n"/>
+      <c r="E38" s="9" t="n"/>
+      <c r="F38" s="8" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="8" t="n">
+      <c r="A39" s="9" t="n">
         <v>38</v>
       </c>
-      <c r="B39" s="11" t="n"/>
-      <c r="C39" s="11" t="n"/>
-      <c r="D39" s="11" t="n"/>
-      <c r="E39" s="8" t="n"/>
-      <c r="F39" s="11" t="n"/>
+      <c r="B39" s="8" t="n"/>
+      <c r="C39" s="8" t="n"/>
+      <c r="D39" s="8" t="n"/>
+      <c r="E39" s="9" t="n"/>
+      <c r="F39" s="8" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="8" t="n">
+      <c r="A40" s="9" t="n">
         <v>39</v>
       </c>
-      <c r="B40" s="11" t="n"/>
-      <c r="C40" s="11" t="n"/>
-      <c r="D40" s="11" t="n"/>
-      <c r="E40" s="8" t="n"/>
-      <c r="F40" s="11" t="n"/>
+      <c r="B40" s="8" t="n"/>
+      <c r="C40" s="8" t="n"/>
+      <c r="D40" s="8" t="n"/>
+      <c r="E40" s="9" t="n"/>
+      <c r="F40" s="8" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="8" t="n">
+      <c r="A41" s="9" t="n">
         <v>40</v>
       </c>
-      <c r="B41" s="11" t="n"/>
-      <c r="C41" s="11" t="n"/>
-      <c r="D41" s="11" t="n"/>
-      <c r="E41" s="8" t="n"/>
-      <c r="F41" s="11" t="n"/>
+      <c r="B41" s="8" t="n"/>
+      <c r="C41" s="8" t="n"/>
+      <c r="D41" s="8" t="n"/>
+      <c r="E41" s="9" t="n"/>
+      <c r="F41" s="8" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="8" t="n">
+      <c r="A42" s="9" t="n">
         <v>41</v>
       </c>
-      <c r="B42" s="11" t="n"/>
-      <c r="C42" s="11" t="n"/>
-      <c r="D42" s="11" t="n"/>
-      <c r="E42" s="8" t="n"/>
-      <c r="F42" s="11" t="n"/>
+      <c r="B42" s="8" t="n"/>
+      <c r="C42" s="8" t="n"/>
+      <c r="D42" s="8" t="n"/>
+      <c r="E42" s="9" t="n"/>
+      <c r="F42" s="8" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/NCD_Brand_Tagging.xlsx
+++ b/NCD_Brand_Tagging.xlsx
@@ -3690,7 +3690,11 @@
           <t>ถุงกระดาษแก้วเดี่ยว</t>
         </is>
       </c>
-      <c r="E72" s="8" t="n"/>
+      <c r="E72" s="8" t="inlineStr">
+        <is>
+          <t>YC Single Cup Paper Bag</t>
+        </is>
+      </c>
       <c r="F72" s="7" t="inlineStr">
         <is>
           <t>ใบ</t>
@@ -3731,7 +3735,11 @@
           <t>ถุงกระดาษแก้วคู่</t>
         </is>
       </c>
-      <c r="E73" s="8" t="n"/>
+      <c r="E73" s="8" t="inlineStr">
+        <is>
+          <t>YC Double Cup Paper Bag</t>
+        </is>
+      </c>
       <c r="F73" s="7" t="inlineStr">
         <is>
           <t>ใบ</t>
@@ -3772,7 +3780,11 @@
           <t>ถุงกระดาษใหญ่</t>
         </is>
       </c>
-      <c r="E74" s="8" t="n"/>
+      <c r="E74" s="8" t="inlineStr">
+        <is>
+          <t>YC Large Paper Bag</t>
+        </is>
+      </c>
       <c r="F74" s="7" t="inlineStr">
         <is>
           <t>ใบ</t>
@@ -5679,31 +5691,79 @@
       <c r="A4" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="8" t="n"/>
-      <c r="C4" s="8" t="n"/>
-      <c r="D4" s="8" t="n"/>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>Staple Single Cup Paper Bag</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>Bags</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>ใบ</t>
+        </is>
+      </c>
       <c r="E4" s="9" t="n"/>
-      <c r="F4" s="8" t="n"/>
+      <c r="F4" s="8" t="inlineStr">
+        <is>
+          <t>Staple version of YC's ถุงกระดาษแก้วเดี่ยว (it-071) — different design, separate stock item. Fill in Par NCD.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="8" t="n"/>
-      <c r="C5" s="8" t="n"/>
-      <c r="D5" s="8" t="n"/>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>Staple Double Cup Paper Bag</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>Bags</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>ใบ</t>
+        </is>
+      </c>
       <c r="E5" s="9" t="n"/>
-      <c r="F5" s="8" t="n"/>
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>Staple version of YC's ถุงกระดาษแก้วคู่ (it-072) — different design, separate stock item. Fill in Par NCD.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="8" t="n"/>
-      <c r="C6" s="8" t="n"/>
-      <c r="D6" s="8" t="n"/>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>Staple Large Paper Bag</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>Bags</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>ใบ</t>
+        </is>
+      </c>
       <c r="E6" s="9" t="n"/>
-      <c r="F6" s="8" t="n"/>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>Staple version of YC's ถุงกระดาษใหญ่ (it-073) — different design, separate stock item. Fill in Par NCD.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="9" t="n">

--- a/NCD_Brand_Tagging.xlsx
+++ b/NCD_Brand_Tagging.xlsx
@@ -3690,11 +3690,7 @@
           <t>ถุงกระดาษแก้วเดี่ยว</t>
         </is>
       </c>
-      <c r="E72" s="8" t="inlineStr">
-        <is>
-          <t>YC Single Cup Paper Bag</t>
-        </is>
-      </c>
+      <c r="E72" s="8" t="n"/>
       <c r="F72" s="7" t="inlineStr">
         <is>
           <t>ใบ</t>
@@ -3703,7 +3699,7 @@
       <c r="G72" s="9" t="n"/>
       <c r="H72" s="9" t="inlineStr">
         <is>
-          <t>yc</t>
+          <t>shared</t>
         </is>
       </c>
       <c r="I72" s="6" t="n">
@@ -3735,11 +3731,7 @@
           <t>ถุงกระดาษแก้วคู่</t>
         </is>
       </c>
-      <c r="E73" s="8" t="inlineStr">
-        <is>
-          <t>YC Double Cup Paper Bag</t>
-        </is>
-      </c>
+      <c r="E73" s="8" t="n"/>
       <c r="F73" s="7" t="inlineStr">
         <is>
           <t>ใบ</t>
@@ -3748,7 +3740,7 @@
       <c r="G73" s="9" t="n"/>
       <c r="H73" s="9" t="inlineStr">
         <is>
-          <t>yc</t>
+          <t>shared</t>
         </is>
       </c>
       <c r="I73" s="6" t="n">
@@ -3780,11 +3772,7 @@
           <t>ถุงกระดาษใหญ่</t>
         </is>
       </c>
-      <c r="E74" s="8" t="inlineStr">
-        <is>
-          <t>YC Large Paper Bag</t>
-        </is>
-      </c>
+      <c r="E74" s="8" t="n"/>
       <c r="F74" s="7" t="inlineStr">
         <is>
           <t>ใบ</t>
@@ -3793,7 +3781,7 @@
       <c r="G74" s="9" t="n"/>
       <c r="H74" s="9" t="inlineStr">
         <is>
-          <t>yc</t>
+          <t>shared</t>
         </is>
       </c>
       <c r="I74" s="6" t="n">
@@ -5691,79 +5679,31 @@
       <c r="A4" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="8" t="inlineStr">
-        <is>
-          <t>Staple Single Cup Paper Bag</t>
-        </is>
-      </c>
-      <c r="C4" s="8" t="inlineStr">
-        <is>
-          <t>Bags</t>
-        </is>
-      </c>
-      <c r="D4" s="8" t="inlineStr">
-        <is>
-          <t>ใบ</t>
-        </is>
-      </c>
+      <c r="B4" s="8" t="n"/>
+      <c r="C4" s="8" t="n"/>
+      <c r="D4" s="8" t="n"/>
       <c r="E4" s="9" t="n"/>
-      <c r="F4" s="8" t="inlineStr">
-        <is>
-          <t>Staple version of YC's ถุงกระดาษแก้วเดี่ยว (it-071) — different design, separate stock item. Fill in Par NCD.</t>
-        </is>
-      </c>
+      <c r="F4" s="8" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="8" t="inlineStr">
-        <is>
-          <t>Staple Double Cup Paper Bag</t>
-        </is>
-      </c>
-      <c r="C5" s="8" t="inlineStr">
-        <is>
-          <t>Bags</t>
-        </is>
-      </c>
-      <c r="D5" s="8" t="inlineStr">
-        <is>
-          <t>ใบ</t>
-        </is>
-      </c>
+      <c r="B5" s="8" t="n"/>
+      <c r="C5" s="8" t="n"/>
+      <c r="D5" s="8" t="n"/>
       <c r="E5" s="9" t="n"/>
-      <c r="F5" s="8" t="inlineStr">
-        <is>
-          <t>Staple version of YC's ถุงกระดาษแก้วคู่ (it-072) — different design, separate stock item. Fill in Par NCD.</t>
-        </is>
-      </c>
+      <c r="F5" s="8" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="8" t="inlineStr">
-        <is>
-          <t>Staple Large Paper Bag</t>
-        </is>
-      </c>
-      <c r="C6" s="8" t="inlineStr">
-        <is>
-          <t>Bags</t>
-        </is>
-      </c>
-      <c r="D6" s="8" t="inlineStr">
-        <is>
-          <t>ใบ</t>
-        </is>
-      </c>
+      <c r="B6" s="8" t="n"/>
+      <c r="C6" s="8" t="n"/>
+      <c r="D6" s="8" t="n"/>
       <c r="E6" s="9" t="n"/>
-      <c r="F6" s="8" t="inlineStr">
-        <is>
-          <t>Staple version of YC's ถุงกระดาษใหญ่ (it-073) — different design, separate stock item. Fill in Par NCD.</t>
-        </is>
-      </c>
+      <c r="F6" s="8" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="9" t="n">

--- a/NCD_Brand_Tagging.xlsx
+++ b/NCD_Brand_Tagging.xlsx
@@ -537,7 +537,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A36"/>
+  <dimension ref="A1:A40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -740,36 +740,64 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Row 4 is a filled-in example — please delete it before sending back, or just add</t>
+          <t xml:space="preserve">  Despite the sheet name, this also covers brand-new items that will be SHARED between</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  your rows below it.</t>
+          <t xml:space="preserve">  YC and Staple at NCD but don't exist anywhere else yet (e.g. a new bag design used by</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Category can be an existing one (see 'Existing Items' sheet) or a brand-new category name.</t>
+          <t xml:space="preserve">  both brands at NCD only, different from the bag design NVP/SND/KCN currently use).</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">  Set the Brand column to yc / staple / shared accordingly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  A few rows are already pre-filled based on what's been confirmed so far — check them,</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  then add your own rows below.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Category can be an existing one (see 'Existing Items' sheet) or a brand-new category name.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">  Par level = normal full-stock quantity to keep on the shelf at NCD.</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="4" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
         <is>
           <t>When done, send this file back and it will be imported directly into the system.</t>
         </is>
@@ -3699,7 +3727,7 @@
       <c r="G72" s="9" t="n"/>
       <c r="H72" s="9" t="inlineStr">
         <is>
-          <t>shared</t>
+          <t>yc</t>
         </is>
       </c>
       <c r="I72" s="6" t="n">
@@ -3740,7 +3768,7 @@
       <c r="G73" s="9" t="n"/>
       <c r="H73" s="9" t="inlineStr">
         <is>
-          <t>shared</t>
+          <t>yc</t>
         </is>
       </c>
       <c r="I73" s="6" t="n">
@@ -3781,7 +3809,7 @@
       <c r="G74" s="9" t="n"/>
       <c r="H74" s="9" t="inlineStr">
         <is>
-          <t>shared</t>
+          <t>yc</t>
         </is>
       </c>
       <c r="I74" s="6" t="n">
@@ -5578,15 +5606,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F42"/>
+  <dimension ref="A1:G42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -5612,10 +5641,15 @@
       </c>
       <c r="E1" s="5" t="inlineStr">
         <is>
+          <t>Brand (yc / staple / shared)</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
           <t>Par NCD</t>
         </is>
       </c>
-      <c r="F1" s="5" t="inlineStr">
+      <c r="G1" s="5" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -5640,10 +5674,15 @@
           <t>1kg/Bag</t>
         </is>
       </c>
-      <c r="E2" s="10" t="n">
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>staple</t>
+        </is>
+      </c>
+      <c r="F2" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="F2" s="11" t="inlineStr">
+      <c r="G2" s="11" t="inlineStr">
         <is>
           <t>Example row — delete before sending back, or add rows below</t>
         </is>
@@ -5668,8 +5707,13 @@
           <t>50/pack</t>
         </is>
       </c>
-      <c r="E3" s="9" t="n"/>
-      <c r="F3" s="8" t="inlineStr">
+      <c r="E3" s="8" t="inlineStr">
+        <is>
+          <t>staple</t>
+        </is>
+      </c>
+      <c r="F3" s="9" t="n"/>
+      <c r="G3" s="8" t="inlineStr">
         <is>
           <t>Same size/spec as YC Cup (14oz, it-056) but printed with Staple logo — separate stock item, not shared. Fill in Par NCD.</t>
         </is>
@@ -5679,31 +5723,94 @@
       <c r="A4" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="8" t="n"/>
-      <c r="C4" s="8" t="n"/>
-      <c r="D4" s="8" t="n"/>
-      <c r="E4" s="9" t="n"/>
-      <c r="F4" s="8" t="n"/>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>NCD Single Cup Paper Bag (new design)</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>Bags</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>ใบ</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="inlineStr">
+        <is>
+          <t>shared</t>
+        </is>
+      </c>
+      <c r="F4" s="9" t="n"/>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>New bag design used ONLY at NCD, shared by both YC and Staple. NOT the same item as YC's existing ถุงกระดาษแก้วเดี่ยว (it-071) used at NVP/SND/KCN — that one stays a separate, unrelated item. Fill in Par NCD.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="8" t="n"/>
-      <c r="C5" s="8" t="n"/>
-      <c r="D5" s="8" t="n"/>
-      <c r="E5" s="9" t="n"/>
-      <c r="F5" s="8" t="n"/>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>NCD Double Cup Paper Bag (new design)</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>Bags</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>ใบ</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>shared</t>
+        </is>
+      </c>
+      <c r="F5" s="9" t="n"/>
+      <c r="G5" s="8" t="inlineStr">
+        <is>
+          <t>New bag design used ONLY at NCD, shared by both YC and Staple. NOT the same item as YC's existing ถุงกระดาษแก้วคู่ (it-072) used at NVP/SND/KCN — that one stays a separate, unrelated item. Fill in Par NCD.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="8" t="n"/>
-      <c r="C6" s="8" t="n"/>
-      <c r="D6" s="8" t="n"/>
-      <c r="E6" s="9" t="n"/>
-      <c r="F6" s="8" t="n"/>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>NCD Large Paper Bag (new design)</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>Bags</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>ใบ</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>shared</t>
+        </is>
+      </c>
+      <c r="F6" s="9" t="n"/>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>New bag design used ONLY at NCD, shared by both YC and Staple. NOT the same item as YC's existing ถุงกระดาษใหญ่ (it-073) used at NVP/SND/KCN — that one stays a separate, unrelated item. Fill in Par NCD.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="9" t="n">
@@ -5712,8 +5819,9 @@
       <c r="B7" s="8" t="n"/>
       <c r="C7" s="8" t="n"/>
       <c r="D7" s="8" t="n"/>
-      <c r="E7" s="9" t="n"/>
-      <c r="F7" s="8" t="n"/>
+      <c r="E7" s="8" t="n"/>
+      <c r="F7" s="9" t="n"/>
+      <c r="G7" s="8" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="9" t="n">
@@ -5722,8 +5830,9 @@
       <c r="B8" s="8" t="n"/>
       <c r="C8" s="8" t="n"/>
       <c r="D8" s="8" t="n"/>
-      <c r="E8" s="9" t="n"/>
-      <c r="F8" s="8" t="n"/>
+      <c r="E8" s="8" t="n"/>
+      <c r="F8" s="9" t="n"/>
+      <c r="G8" s="8" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="9" t="n">
@@ -5732,8 +5841,9 @@
       <c r="B9" s="8" t="n"/>
       <c r="C9" s="8" t="n"/>
       <c r="D9" s="8" t="n"/>
-      <c r="E9" s="9" t="n"/>
-      <c r="F9" s="8" t="n"/>
+      <c r="E9" s="8" t="n"/>
+      <c r="F9" s="9" t="n"/>
+      <c r="G9" s="8" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="9" t="n">
@@ -5742,8 +5852,9 @@
       <c r="B10" s="8" t="n"/>
       <c r="C10" s="8" t="n"/>
       <c r="D10" s="8" t="n"/>
-      <c r="E10" s="9" t="n"/>
-      <c r="F10" s="8" t="n"/>
+      <c r="E10" s="8" t="n"/>
+      <c r="F10" s="9" t="n"/>
+      <c r="G10" s="8" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="9" t="n">
@@ -5752,8 +5863,9 @@
       <c r="B11" s="8" t="n"/>
       <c r="C11" s="8" t="n"/>
       <c r="D11" s="8" t="n"/>
-      <c r="E11" s="9" t="n"/>
-      <c r="F11" s="8" t="n"/>
+      <c r="E11" s="8" t="n"/>
+      <c r="F11" s="9" t="n"/>
+      <c r="G11" s="8" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="9" t="n">
@@ -5762,8 +5874,9 @@
       <c r="B12" s="8" t="n"/>
       <c r="C12" s="8" t="n"/>
       <c r="D12" s="8" t="n"/>
-      <c r="E12" s="9" t="n"/>
-      <c r="F12" s="8" t="n"/>
+      <c r="E12" s="8" t="n"/>
+      <c r="F12" s="9" t="n"/>
+      <c r="G12" s="8" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="9" t="n">
@@ -5772,8 +5885,9 @@
       <c r="B13" s="8" t="n"/>
       <c r="C13" s="8" t="n"/>
       <c r="D13" s="8" t="n"/>
-      <c r="E13" s="9" t="n"/>
-      <c r="F13" s="8" t="n"/>
+      <c r="E13" s="8" t="n"/>
+      <c r="F13" s="9" t="n"/>
+      <c r="G13" s="8" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="9" t="n">
@@ -5782,8 +5896,9 @@
       <c r="B14" s="8" t="n"/>
       <c r="C14" s="8" t="n"/>
       <c r="D14" s="8" t="n"/>
-      <c r="E14" s="9" t="n"/>
-      <c r="F14" s="8" t="n"/>
+      <c r="E14" s="8" t="n"/>
+      <c r="F14" s="9" t="n"/>
+      <c r="G14" s="8" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="9" t="n">
@@ -5792,8 +5907,9 @@
       <c r="B15" s="8" t="n"/>
       <c r="C15" s="8" t="n"/>
       <c r="D15" s="8" t="n"/>
-      <c r="E15" s="9" t="n"/>
-      <c r="F15" s="8" t="n"/>
+      <c r="E15" s="8" t="n"/>
+      <c r="F15" s="9" t="n"/>
+      <c r="G15" s="8" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="9" t="n">
@@ -5802,8 +5918,9 @@
       <c r="B16" s="8" t="n"/>
       <c r="C16" s="8" t="n"/>
       <c r="D16" s="8" t="n"/>
-      <c r="E16" s="9" t="n"/>
-      <c r="F16" s="8" t="n"/>
+      <c r="E16" s="8" t="n"/>
+      <c r="F16" s="9" t="n"/>
+      <c r="G16" s="8" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="9" t="n">
@@ -5812,8 +5929,9 @@
       <c r="B17" s="8" t="n"/>
       <c r="C17" s="8" t="n"/>
       <c r="D17" s="8" t="n"/>
-      <c r="E17" s="9" t="n"/>
-      <c r="F17" s="8" t="n"/>
+      <c r="E17" s="8" t="n"/>
+      <c r="F17" s="9" t="n"/>
+      <c r="G17" s="8" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="9" t="n">
@@ -5822,8 +5940,9 @@
       <c r="B18" s="8" t="n"/>
       <c r="C18" s="8" t="n"/>
       <c r="D18" s="8" t="n"/>
-      <c r="E18" s="9" t="n"/>
-      <c r="F18" s="8" t="n"/>
+      <c r="E18" s="8" t="n"/>
+      <c r="F18" s="9" t="n"/>
+      <c r="G18" s="8" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="9" t="n">
@@ -5832,8 +5951,9 @@
       <c r="B19" s="8" t="n"/>
       <c r="C19" s="8" t="n"/>
       <c r="D19" s="8" t="n"/>
-      <c r="E19" s="9" t="n"/>
-      <c r="F19" s="8" t="n"/>
+      <c r="E19" s="8" t="n"/>
+      <c r="F19" s="9" t="n"/>
+      <c r="G19" s="8" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="9" t="n">
@@ -5842,8 +5962,9 @@
       <c r="B20" s="8" t="n"/>
       <c r="C20" s="8" t="n"/>
       <c r="D20" s="8" t="n"/>
-      <c r="E20" s="9" t="n"/>
-      <c r="F20" s="8" t="n"/>
+      <c r="E20" s="8" t="n"/>
+      <c r="F20" s="9" t="n"/>
+      <c r="G20" s="8" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="9" t="n">
@@ -5852,8 +5973,9 @@
       <c r="B21" s="8" t="n"/>
       <c r="C21" s="8" t="n"/>
       <c r="D21" s="8" t="n"/>
-      <c r="E21" s="9" t="n"/>
-      <c r="F21" s="8" t="n"/>
+      <c r="E21" s="8" t="n"/>
+      <c r="F21" s="9" t="n"/>
+      <c r="G21" s="8" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="9" t="n">
@@ -5862,8 +5984,9 @@
       <c r="B22" s="8" t="n"/>
       <c r="C22" s="8" t="n"/>
       <c r="D22" s="8" t="n"/>
-      <c r="E22" s="9" t="n"/>
-      <c r="F22" s="8" t="n"/>
+      <c r="E22" s="8" t="n"/>
+      <c r="F22" s="9" t="n"/>
+      <c r="G22" s="8" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="9" t="n">
@@ -5872,8 +5995,9 @@
       <c r="B23" s="8" t="n"/>
       <c r="C23" s="8" t="n"/>
       <c r="D23" s="8" t="n"/>
-      <c r="E23" s="9" t="n"/>
-      <c r="F23" s="8" t="n"/>
+      <c r="E23" s="8" t="n"/>
+      <c r="F23" s="9" t="n"/>
+      <c r="G23" s="8" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="9" t="n">
@@ -5882,8 +6006,9 @@
       <c r="B24" s="8" t="n"/>
       <c r="C24" s="8" t="n"/>
       <c r="D24" s="8" t="n"/>
-      <c r="E24" s="9" t="n"/>
-      <c r="F24" s="8" t="n"/>
+      <c r="E24" s="8" t="n"/>
+      <c r="F24" s="9" t="n"/>
+      <c r="G24" s="8" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="9" t="n">
@@ -5892,8 +6017,9 @@
       <c r="B25" s="8" t="n"/>
       <c r="C25" s="8" t="n"/>
       <c r="D25" s="8" t="n"/>
-      <c r="E25" s="9" t="n"/>
-      <c r="F25" s="8" t="n"/>
+      <c r="E25" s="8" t="n"/>
+      <c r="F25" s="9" t="n"/>
+      <c r="G25" s="8" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="9" t="n">
@@ -5902,8 +6028,9 @@
       <c r="B26" s="8" t="n"/>
       <c r="C26" s="8" t="n"/>
       <c r="D26" s="8" t="n"/>
-      <c r="E26" s="9" t="n"/>
-      <c r="F26" s="8" t="n"/>
+      <c r="E26" s="8" t="n"/>
+      <c r="F26" s="9" t="n"/>
+      <c r="G26" s="8" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="9" t="n">
@@ -5912,8 +6039,9 @@
       <c r="B27" s="8" t="n"/>
       <c r="C27" s="8" t="n"/>
       <c r="D27" s="8" t="n"/>
-      <c r="E27" s="9" t="n"/>
-      <c r="F27" s="8" t="n"/>
+      <c r="E27" s="8" t="n"/>
+      <c r="F27" s="9" t="n"/>
+      <c r="G27" s="8" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="9" t="n">
@@ -5922,8 +6050,9 @@
       <c r="B28" s="8" t="n"/>
       <c r="C28" s="8" t="n"/>
       <c r="D28" s="8" t="n"/>
-      <c r="E28" s="9" t="n"/>
-      <c r="F28" s="8" t="n"/>
+      <c r="E28" s="8" t="n"/>
+      <c r="F28" s="9" t="n"/>
+      <c r="G28" s="8" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="9" t="n">
@@ -5932,8 +6061,9 @@
       <c r="B29" s="8" t="n"/>
       <c r="C29" s="8" t="n"/>
       <c r="D29" s="8" t="n"/>
-      <c r="E29" s="9" t="n"/>
-      <c r="F29" s="8" t="n"/>
+      <c r="E29" s="8" t="n"/>
+      <c r="F29" s="9" t="n"/>
+      <c r="G29" s="8" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="9" t="n">
@@ -5942,8 +6072,9 @@
       <c r="B30" s="8" t="n"/>
       <c r="C30" s="8" t="n"/>
       <c r="D30" s="8" t="n"/>
-      <c r="E30" s="9" t="n"/>
-      <c r="F30" s="8" t="n"/>
+      <c r="E30" s="8" t="n"/>
+      <c r="F30" s="9" t="n"/>
+      <c r="G30" s="8" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="9" t="n">
@@ -5952,8 +6083,9 @@
       <c r="B31" s="8" t="n"/>
       <c r="C31" s="8" t="n"/>
       <c r="D31" s="8" t="n"/>
-      <c r="E31" s="9" t="n"/>
-      <c r="F31" s="8" t="n"/>
+      <c r="E31" s="8" t="n"/>
+      <c r="F31" s="9" t="n"/>
+      <c r="G31" s="8" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="9" t="n">
@@ -5962,8 +6094,9 @@
       <c r="B32" s="8" t="n"/>
       <c r="C32" s="8" t="n"/>
       <c r="D32" s="8" t="n"/>
-      <c r="E32" s="9" t="n"/>
-      <c r="F32" s="8" t="n"/>
+      <c r="E32" s="8" t="n"/>
+      <c r="F32" s="9" t="n"/>
+      <c r="G32" s="8" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="9" t="n">
@@ -5972,8 +6105,9 @@
       <c r="B33" s="8" t="n"/>
       <c r="C33" s="8" t="n"/>
       <c r="D33" s="8" t="n"/>
-      <c r="E33" s="9" t="n"/>
-      <c r="F33" s="8" t="n"/>
+      <c r="E33" s="8" t="n"/>
+      <c r="F33" s="9" t="n"/>
+      <c r="G33" s="8" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="9" t="n">
@@ -5982,8 +6116,9 @@
       <c r="B34" s="8" t="n"/>
       <c r="C34" s="8" t="n"/>
       <c r="D34" s="8" t="n"/>
-      <c r="E34" s="9" t="n"/>
-      <c r="F34" s="8" t="n"/>
+      <c r="E34" s="8" t="n"/>
+      <c r="F34" s="9" t="n"/>
+      <c r="G34" s="8" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="9" t="n">
@@ -5992,8 +6127,9 @@
       <c r="B35" s="8" t="n"/>
       <c r="C35" s="8" t="n"/>
       <c r="D35" s="8" t="n"/>
-      <c r="E35" s="9" t="n"/>
-      <c r="F35" s="8" t="n"/>
+      <c r="E35" s="8" t="n"/>
+      <c r="F35" s="9" t="n"/>
+      <c r="G35" s="8" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="9" t="n">
@@ -6002,8 +6138,9 @@
       <c r="B36" s="8" t="n"/>
       <c r="C36" s="8" t="n"/>
       <c r="D36" s="8" t="n"/>
-      <c r="E36" s="9" t="n"/>
-      <c r="F36" s="8" t="n"/>
+      <c r="E36" s="8" t="n"/>
+      <c r="F36" s="9" t="n"/>
+      <c r="G36" s="8" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="9" t="n">
@@ -6012,8 +6149,9 @@
       <c r="B37" s="8" t="n"/>
       <c r="C37" s="8" t="n"/>
       <c r="D37" s="8" t="n"/>
-      <c r="E37" s="9" t="n"/>
-      <c r="F37" s="8" t="n"/>
+      <c r="E37" s="8" t="n"/>
+      <c r="F37" s="9" t="n"/>
+      <c r="G37" s="8" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="9" t="n">
@@ -6022,8 +6160,9 @@
       <c r="B38" s="8" t="n"/>
       <c r="C38" s="8" t="n"/>
       <c r="D38" s="8" t="n"/>
-      <c r="E38" s="9" t="n"/>
-      <c r="F38" s="8" t="n"/>
+      <c r="E38" s="8" t="n"/>
+      <c r="F38" s="9" t="n"/>
+      <c r="G38" s="8" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="9" t="n">
@@ -6032,8 +6171,9 @@
       <c r="B39" s="8" t="n"/>
       <c r="C39" s="8" t="n"/>
       <c r="D39" s="8" t="n"/>
-      <c r="E39" s="9" t="n"/>
-      <c r="F39" s="8" t="n"/>
+      <c r="E39" s="8" t="n"/>
+      <c r="F39" s="9" t="n"/>
+      <c r="G39" s="8" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="9" t="n">
@@ -6042,8 +6182,9 @@
       <c r="B40" s="8" t="n"/>
       <c r="C40" s="8" t="n"/>
       <c r="D40" s="8" t="n"/>
-      <c r="E40" s="9" t="n"/>
-      <c r="F40" s="8" t="n"/>
+      <c r="E40" s="8" t="n"/>
+      <c r="F40" s="9" t="n"/>
+      <c r="G40" s="8" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="9" t="n">
@@ -6052,8 +6193,9 @@
       <c r="B41" s="8" t="n"/>
       <c r="C41" s="8" t="n"/>
       <c r="D41" s="8" t="n"/>
-      <c r="E41" s="9" t="n"/>
-      <c r="F41" s="8" t="n"/>
+      <c r="E41" s="8" t="n"/>
+      <c r="F41" s="9" t="n"/>
+      <c r="G41" s="8" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="9" t="n">
@@ -6062,10 +6204,16 @@
       <c r="B42" s="8" t="n"/>
       <c r="C42" s="8" t="n"/>
       <c r="D42" s="8" t="n"/>
-      <c r="E42" s="9" t="n"/>
-      <c r="F42" s="8" t="n"/>
+      <c r="E42" s="8" t="n"/>
+      <c r="F42" s="9" t="n"/>
+      <c r="G42" s="8" t="n"/>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="E3 E4 E5 E6 E7 E8 E9 E10 E11 E12 E13 E14 E15 E16 E17 E18 E19 E20 E21 E22 E23 E24 E25 E26 E27 E28 E29 E30 E31 E32 E33 E34 E35 E36 E37 E38 E39 E40 E41 E42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Invalid brand" error="Choose yc, staple, or shared from the list." type="list">
+      <formula1>"yc,staple,shared"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/NCD_Brand_Tagging.xlsx
+++ b/NCD_Brand_Tagging.xlsx
@@ -5725,7 +5725,7 @@
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>NCD Single Cup Paper Bag (new design)</t>
+          <t>Single Cup Paper Bag</t>
         </is>
       </c>
       <c r="C4" s="8" t="inlineStr">
@@ -5756,7 +5756,7 @@
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>NCD Double Cup Paper Bag (new design)</t>
+          <t>Double Cup Paper Bag</t>
         </is>
       </c>
       <c r="C5" s="8" t="inlineStr">
@@ -5787,7 +5787,7 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>NCD Large Paper Bag (new design)</t>
+          <t>S Brown Paper Bag</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
@@ -5808,7 +5808,7 @@
       <c r="F6" s="9" t="n"/>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>New bag design used ONLY at NCD, shared by both YC and Staple. NOT the same item as YC's existing ถุงกระดาษใหญ่ (it-073) used at NVP/SND/KCN — that one stays a separate, unrelated item. Fill in Par NCD.</t>
+          <t>New NCD-only bag, shared by both YC and Staple. Fill in Par NCD.</t>
         </is>
       </c>
     </row>
@@ -5816,12 +5816,32 @@
       <c r="A7" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="8" t="n"/>
-      <c r="C7" s="8" t="n"/>
-      <c r="D7" s="8" t="n"/>
-      <c r="E7" s="8" t="n"/>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>M Brown Paper Bag</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>Bags</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>ใบ</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>shared</t>
+        </is>
+      </c>
       <c r="F7" s="9" t="n"/>
-      <c r="G7" s="8" t="n"/>
+      <c r="G7" s="8" t="inlineStr">
+        <is>
+          <t>New NCD-only bag, shared by both YC and Staple. Fill in Par NCD.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="9" t="n">

--- a/NCD_Brand_Tagging.xlsx
+++ b/NCD_Brand_Tagging.xlsx
@@ -1579,7 +1579,7 @@
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>Drink / แยมกระปุก</t>
+          <t>Drink/Yogurt Pouch</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
@@ -1614,7 +1614,7 @@
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>Drink / แยมกระปุก</t>
+          <t>Drink/Yogurt Pouch</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>Drink / แยมกระปุก</t>
+          <t>Drink/Yogurt Pouch</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>Drink / แยมกระปุก</t>
+          <t>Drink/Yogurt Pouch</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
@@ -1735,7 +1735,7 @@
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>Drink / แยมกระปุก</t>
+          <t>Drink/Yogurt Pouch</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>Drink / แยมกระปุก</t>
+          <t>Drink/Yogurt Pouch</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>Drink / แยมกระปุก</t>
+          <t>Drink/Yogurt Pouch</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
@@ -1858,7 +1858,7 @@
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>Drink / แยมกระปุก</t>
+          <t>Drink/Yogurt Pouch</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">

--- a/NCD_Brand_Tagging.xlsx
+++ b/NCD_Brand_Tagging.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -64,6 +64,9 @@
       <i val="1"/>
       <color rgb="00808080"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="4">
@@ -112,7 +115,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -147,6 +150,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -537,7 +541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A40"/>
+  <dimension ref="A1:A52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -800,6 +804,83 @@
       <c r="A40" s="4" t="inlineStr">
         <is>
           <t>When done, send this file back and it will be imported directly into the system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>NCD 'To-Go' section (added 2026-08-06) — items customers pick up and take home</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>themselves, separate from the fresh made-to-order menu at the counter. Only NCD has</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>this section currently.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Column L on 'Existing Items' and column H on 'New Staple Items' — 'To-Go Category'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Leave BLANK for anything not part of NCD's To-Go section (unchanged everywhere else).</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Current To-Go sub-categories: To-Go Yogurt, To-Go Beverage, To-Go Snack,</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    To-Go Sandwich &amp; Salad, To-Go Cheese.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  7 items moved from 'Drink/Yogurt Pouch' into To-Go Yogurt/Beverage (see column L).</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Peanut Butter (it-018) stayed put — not currently sold, category revisit later.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  To-Go Sandwich &amp; Salad / To-Go Snack / To-Go Cheese have no items yet — add them as</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    new rows in 'New Staple Items' with the Category set to one of those 3 names.</t>
         </is>
       </c>
     </row>
@@ -814,7 +895,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K119"/>
+  <dimension ref="A1:L119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -886,6 +967,11 @@
           <t>Par KCN (ref)</t>
         </is>
       </c>
+      <c r="L1" s="12" t="inlineStr">
+        <is>
+          <t>To-Go Category at NCD (blank = not in this section)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="6" t="n">
@@ -1641,6 +1727,11 @@
         <v>12</v>
       </c>
       <c r="K20" s="6" t="n"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>To-Go Beverage</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="n">
@@ -1682,6 +1773,11 @@
       <c r="K21" s="6" t="n">
         <v>5</v>
       </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>To-Go Yogurt</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="n">
@@ -1723,6 +1819,11 @@
       <c r="K22" s="6" t="n">
         <v>5</v>
       </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>To-Go Yogurt</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="n">
@@ -1764,6 +1865,11 @@
       <c r="K23" s="6" t="n">
         <v>5</v>
       </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>To-Go Yogurt</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="n">
@@ -1805,6 +1911,11 @@
       <c r="K24" s="6" t="n">
         <v>5</v>
       </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>To-Go Yogurt</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="n">
@@ -1846,6 +1957,11 @@
       <c r="K25" s="6" t="n">
         <v>5</v>
       </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>To-Go Yogurt</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="n">
@@ -1886,6 +2002,11 @@
       </c>
       <c r="K26" s="6" t="n">
         <v>5</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>To-Go Yogurt</t>
+        </is>
       </c>
     </row>
     <row r="27">
@@ -5606,7 +5727,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G42"/>
+  <dimension ref="A1:H42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -5654,6 +5775,11 @@
           <t>Notes</t>
         </is>
       </c>
+      <c r="H1" s="12" t="inlineStr">
+        <is>
+          <t>To-Go Category (blank = not part of NCD's To-Go section)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="10" t="n">

--- a/NCD_Brand_Tagging.xlsx
+++ b/NCD_Brand_Tagging.xlsx
@@ -2,9 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17220" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" state="visible" r:id="rId1"/>
@@ -12,7 +11,7 @@
     <sheet name="New Staple Items" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1" iterateDelta="0.0001"/>
 </workbook>
 </file>
 
@@ -29,44 +28,54 @@
     </font>
     <font>
       <name val="Arial"/>
+      <family val="2"/>
       <b val="1"/>
-      <color rgb="00542916"/>
+      <color rgb="FF542916"/>
       <sz val="14"/>
     </font>
     <font>
       <name val="Arial"/>
-      <color rgb="002B241C"/>
+      <family val="2"/>
+      <color rgb="FF2B241C"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
-      <color rgb="002B241C"/>
+      <family val="2"/>
+      <color rgb="FF2B241C"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Arial"/>
+      <family val="2"/>
       <b val="1"/>
-      <color rgb="00542916"/>
+      <color rgb="FF542916"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Arial"/>
+      <family val="2"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Arial"/>
+      <family val="2"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
+      <family val="2"/>
       <i val="1"/>
-      <color rgb="00808080"/>
+      <color rgb="FF808080"/>
       <sz val="10"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <family val="2"/>
       <b val="1"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="4">
@@ -78,14 +87,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2565C"/>
-        <bgColor rgb="00F2565C"/>
+        <fgColor rgb="FFF2565C"/>
+        <bgColor rgb="FFF2565C"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF9C4"/>
-        <bgColor rgb="00FFF9C4"/>
+        <fgColor rgb="FFFFF9C4"/>
+        <bgColor rgb="FFFFF9C4"/>
       </patternFill>
     </fill>
   </fills>
@@ -99,17 +108,18 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00D9D9D9"/>
+        <color rgb="FFD9D9D9"/>
       </left>
       <right style="thin">
-        <color rgb="00D9D9D9"/>
+        <color rgb="FFD9D9D9"/>
       </right>
       <top style="thin">
-        <color rgb="00D9D9D9"/>
+        <color rgb="FFD9D9D9"/>
       </top>
       <bottom style="thin">
-        <color rgb="00D9D9D9"/>
+        <color rgb="FFD9D9D9"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -153,7 +163,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -542,7 +552,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:A52"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
   </cols>
@@ -555,7 +565,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr"/>
+      <c r="A2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -579,7 +589,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr"/>
+      <c r="A6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -708,7 +718,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr"/>
+      <c r="A25" s="2" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
@@ -732,7 +742,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr"/>
+      <c r="A29" s="2" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
@@ -798,7 +808,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr"/>
+      <c r="A39" s="2" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
@@ -896,7 +906,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L119"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
@@ -906,9 +916,7 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
     <col width="30" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="9" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -1382,6 +1390,11 @@
       <c r="K11" s="6" t="n">
         <v>7</v>
       </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>To-Go Yogurt</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="n">
@@ -1423,6 +1436,11 @@
       <c r="K12" s="6" t="n">
         <v>2</v>
       </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>To-Go Yogurt</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="n">
@@ -2047,6 +2065,11 @@
         <v>4</v>
       </c>
       <c r="K27" s="6" t="n"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>To-Go Snack</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="n">
@@ -2086,6 +2109,11 @@
         <v>4</v>
       </c>
       <c r="K28" s="6" t="n"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>To-Go Snack</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="n">
@@ -2125,6 +2153,11 @@
         <v>0</v>
       </c>
       <c r="K29" s="6" t="n"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>To-Go Snack</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="n">
@@ -5631,6 +5664,11 @@
         <v>0</v>
       </c>
       <c r="K117" s="6" t="n"/>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>To-Go Snack</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="6" t="n">
@@ -5712,7 +5750,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="H2 H3 H4 H5 H6 H7 H8 H9 H10 H11 H12 H13 H14 H15 H16 H17 H18 H19 H20 H21 H22 H23 H24 H25 H26 H27 H28 H29 H30 H31 H32 H33 H34 H35 H36 H37 H38 H39 H40 H41 H42 H43 H44 H45 H46 H47 H48 H49 H50 H51 H52 H53 H54 H55 H56 H57 H58 H59 H60 H61 H62 H63 H64 H65 H66 H67 H68 H69 H70 H71 H72 H73 H74 H75 H76 H77 H78 H79 H80 H81 H82 H83 H84 H85 H86 H87 H88 H89 H90 H91 H92 H93 H94 H95 H96 H97 H98 H99 H100 H101 H102 H103 H104 H105 H106 H107 H108 H109 H110 H111 H112 H113 H114 H115 H116 H117 H118 H119" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Invalid brand" error="Choose yc, staple, or shared from the list." type="list">
+    <dataValidation sqref="H2:H119" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Invalid brand" error="Choose yc, staple, or shared from the list." type="list">
       <formula1>"yc,staple,shared"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5728,7 +5766,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:H42"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
@@ -5781,7 +5819,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="28" customHeight="1">
       <c r="A2" s="10" t="n">
         <v>1</v>
       </c>
@@ -5814,7 +5852,7 @@
         </is>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="42" customHeight="1">
       <c r="A3" s="9" t="n">
         <v>2</v>
       </c>
@@ -5845,7 +5883,7 @@
         </is>
       </c>
     </row>
-    <row r="4">
+    <row r="4" ht="70" customHeight="1">
       <c r="A4" s="9" t="n">
         <v>3</v>
       </c>
@@ -5876,7 +5914,7 @@
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="70" customHeight="1">
       <c r="A5" s="9" t="n">
         <v>4</v>
       </c>
@@ -5907,7 +5945,7 @@
         </is>
       </c>
     </row>
-    <row r="6">
+    <row r="6" ht="28" customHeight="1">
       <c r="A6" s="9" t="n">
         <v>5</v>
       </c>
@@ -5938,7 +5976,7 @@
         </is>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="28" customHeight="1">
       <c r="A7" s="9" t="n">
         <v>6</v>
       </c>
@@ -5973,10 +6011,26 @@
       <c r="A8" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="8" t="n"/>
-      <c r="C8" s="8" t="n"/>
-      <c r="D8" s="8" t="n"/>
-      <c r="E8" s="8" t="n"/>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>Feta Cheese</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>To-Go Cheese</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>กระปุก</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>shared</t>
+        </is>
+      </c>
       <c r="F8" s="9" t="n"/>
       <c r="G8" s="8" t="n"/>
     </row>
@@ -5984,10 +6038,26 @@
       <c r="A9" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="8" t="n"/>
-      <c r="C9" s="8" t="n"/>
-      <c r="D9" s="8" t="n"/>
-      <c r="E9" s="8" t="n"/>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>Ricotta</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>To-Go Cheese</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>กระปุก</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>shared</t>
+        </is>
+      </c>
       <c r="F9" s="9" t="n"/>
       <c r="G9" s="8" t="n"/>
     </row>
@@ -5995,10 +6065,26 @@
       <c r="A10" s="9" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="8" t="n"/>
-      <c r="C10" s="8" t="n"/>
-      <c r="D10" s="8" t="n"/>
-      <c r="E10" s="8" t="n"/>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>Ham Cheese Sandwich</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>To-Go Sandwich &amp; Salad</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>ชิ้น</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>shared</t>
+        </is>
+      </c>
       <c r="F10" s="9" t="n"/>
       <c r="G10" s="8" t="n"/>
     </row>
@@ -6006,10 +6092,26 @@
       <c r="A11" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="8" t="n"/>
-      <c r="C11" s="8" t="n"/>
-      <c r="D11" s="8" t="n"/>
-      <c r="E11" s="8" t="n"/>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>Egg Salad Sandwich</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>To-Go Sandwich &amp; Salad</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>ชิ้น</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>shared</t>
+        </is>
+      </c>
       <c r="F11" s="9" t="n"/>
       <c r="G11" s="8" t="n"/>
     </row>
@@ -6017,10 +6119,26 @@
       <c r="A12" s="9" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="8" t="n"/>
-      <c r="C12" s="8" t="n"/>
-      <c r="D12" s="8" t="n"/>
-      <c r="E12" s="8" t="n"/>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>Tuna Sandwich</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>To-Go Sandwich &amp; Salad</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>ชิ้น</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>shared</t>
+        </is>
+      </c>
       <c r="F12" s="9" t="n"/>
       <c r="G12" s="8" t="n"/>
     </row>
@@ -6028,10 +6146,26 @@
       <c r="A13" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="8" t="n"/>
-      <c r="C13" s="8" t="n"/>
-      <c r="D13" s="8" t="n"/>
-      <c r="E13" s="8" t="n"/>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>Sour Hour - Ginger Lemon</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>To-Go Beverage</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>กระป๋อง</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="inlineStr">
+        <is>
+          <t>shared</t>
+        </is>
+      </c>
       <c r="F13" s="9" t="n"/>
       <c r="G13" s="8" t="n"/>
     </row>
@@ -6039,10 +6173,26 @@
       <c r="A14" s="9" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="8" t="n"/>
-      <c r="C14" s="8" t="n"/>
-      <c r="D14" s="8" t="n"/>
-      <c r="E14" s="8" t="n"/>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>Sour Hour - Peach Lychee</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>To-Go Beverage</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>กระป๋อง</t>
+        </is>
+      </c>
+      <c r="E14" s="8" t="inlineStr">
+        <is>
+          <t>shared</t>
+        </is>
+      </c>
       <c r="F14" s="9" t="n"/>
       <c r="G14" s="8" t="n"/>
     </row>
@@ -6050,10 +6200,26 @@
       <c r="A15" s="9" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="8" t="n"/>
-      <c r="C15" s="8" t="n"/>
-      <c r="D15" s="8" t="n"/>
-      <c r="E15" s="8" t="n"/>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>San Pellegrino</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>To-Go Beverage</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>ขวด</t>
+        </is>
+      </c>
+      <c r="E15" s="8" t="inlineStr">
+        <is>
+          <t>shared</t>
+        </is>
+      </c>
       <c r="F15" s="9" t="n"/>
       <c r="G15" s="8" t="n"/>
     </row>
@@ -6061,10 +6227,26 @@
       <c r="A16" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="8" t="n"/>
-      <c r="C16" s="8" t="n"/>
-      <c r="D16" s="8" t="n"/>
-      <c r="E16" s="8" t="n"/>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>Coca Cola</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>To-Go Beverage</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>กระป๋อง</t>
+        </is>
+      </c>
+      <c r="E16" s="8" t="inlineStr">
+        <is>
+          <t>shared</t>
+        </is>
+      </c>
       <c r="F16" s="9" t="n"/>
       <c r="G16" s="8" t="n"/>
     </row>
@@ -6072,10 +6254,26 @@
       <c r="A17" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="8" t="n"/>
-      <c r="C17" s="8" t="n"/>
-      <c r="D17" s="8" t="n"/>
-      <c r="E17" s="8" t="n"/>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>Sprite</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>To-Go Beverage</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>กระป๋อง</t>
+        </is>
+      </c>
+      <c r="E17" s="8" t="inlineStr">
+        <is>
+          <t>shared</t>
+        </is>
+      </c>
       <c r="F17" s="9" t="n"/>
       <c r="G17" s="8" t="n"/>
     </row>

--- a/NCD_Brand_Tagging.xlsx
+++ b/NCD_Brand_Tagging.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/praee/Desktop/CLAUDE/BQMP OPS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B331131-D54B-E34C-8040-DE365673B36C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BE1FCAC-729F-DD4D-A549-DBACF1DFBFF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17220" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -74,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="874" uniqueCount="452">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1041" uniqueCount="502">
   <si>
     <t>No.</t>
   </si>
@@ -1399,9 +1399,6 @@
     <t>Sticker Salad1</t>
   </si>
   <si>
-    <t>Coconut Water</t>
-  </si>
-  <si>
     <t>Orange Juice</t>
   </si>
   <si>
@@ -1430,6 +1427,159 @@
   </si>
   <si>
     <t>Sause Spread</t>
+  </si>
+  <si>
+    <t>ไม้เสียบ sourdough</t>
+  </si>
+  <si>
+    <t>Ham</t>
+  </si>
+  <si>
+    <t>Cheddar</t>
+  </si>
+  <si>
+    <t>Mozzarella</t>
+  </si>
+  <si>
+    <t>Whole Grain Mustard</t>
+  </si>
+  <si>
+    <t>Mayo</t>
+  </si>
+  <si>
+    <t>Pesto</t>
+  </si>
+  <si>
+    <t>Cheese</t>
+  </si>
+  <si>
+    <t>แตงกวาดอง</t>
+  </si>
+  <si>
+    <t>Jalapeno</t>
+  </si>
+  <si>
+    <t>Sourdough</t>
+  </si>
+  <si>
+    <t>คู่</t>
+  </si>
+  <si>
+    <t>Bread</t>
+  </si>
+  <si>
+    <t>Butter</t>
+  </si>
+  <si>
+    <t>ก้อน</t>
+  </si>
+  <si>
+    <t>Strawberry Jam for Sourdough</t>
+  </si>
+  <si>
+    <t>Strawberry peach PASH</t>
+  </si>
+  <si>
+    <t>Mango passion PASH</t>
+  </si>
+  <si>
+    <t>Coconut Water Bottle</t>
+  </si>
+  <si>
+    <t>Orange Juice Bottle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coconut Water </t>
+  </si>
+  <si>
+    <t>Smoothies/Juice</t>
+  </si>
+  <si>
+    <t>Bacon Jam</t>
+  </si>
+  <si>
+    <t>Tomato</t>
+  </si>
+  <si>
+    <t>Mixed Salad</t>
+  </si>
+  <si>
+    <t>Fresh Mozzarella</t>
+  </si>
+  <si>
+    <t>Tuna Mousse</t>
+  </si>
+  <si>
+    <t>Onion</t>
+  </si>
+  <si>
+    <t>Chicken Waldorf</t>
+  </si>
+  <si>
+    <t>Havarti</t>
+  </si>
+  <si>
+    <t>Shallot</t>
+  </si>
+  <si>
+    <t>Feta Cheese for add-ons</t>
+  </si>
+  <si>
+    <t>Chicken Breast</t>
+  </si>
+  <si>
+    <t>Bacon</t>
+  </si>
+  <si>
+    <t>Vinaigrette</t>
+  </si>
+  <si>
+    <t>Dressings</t>
+  </si>
+  <si>
+    <t>Truffle Cream</t>
+  </si>
+  <si>
+    <t>Black Capsule</t>
+  </si>
+  <si>
+    <t>Grey Capsule</t>
+  </si>
+  <si>
+    <t>Brown Capsule</t>
+  </si>
+  <si>
+    <t>Coffee</t>
+  </si>
+  <si>
+    <t>Milk</t>
+  </si>
+  <si>
+    <t>แกลอน</t>
+  </si>
+  <si>
+    <t>Oat Milk</t>
+  </si>
+  <si>
+    <t>Capsule</t>
+  </si>
+  <si>
+    <t>Low-fat Cream Salad</t>
+  </si>
+  <si>
+    <t>หัว</t>
+  </si>
+  <si>
+    <t>Sugar sachet</t>
+  </si>
+  <si>
+    <t>Syrup</t>
+  </si>
+  <si>
+    <t>Monkfruit Syrup</t>
+  </si>
+  <si>
+    <t>Chocolate Fudge Drink</t>
   </si>
 </sst>
 </file>
@@ -1528,7 +1678,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -1562,11 +1712,29 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFD9D9D9"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD9D9D9"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1605,6 +1773,36 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -6003,7 +6201,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:H45"/>
+  <dimension ref="A1:H82"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -6415,7 +6613,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C19" s="8" t="s">
         <v>38</v>
@@ -6436,7 +6634,7 @@
         <v>19</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C20" s="8" t="s">
         <v>38</v>
@@ -6457,7 +6655,7 @@
         <v>20</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C21" s="8" t="s">
         <v>38</v>
@@ -6814,7 +7012,7 @@
         <v>37</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>441</v>
+        <v>469</v>
       </c>
       <c r="C38" s="8" t="s">
         <v>69</v>
@@ -6835,7 +7033,7 @@
         <v>38</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>442</v>
+        <v>470</v>
       </c>
       <c r="C39" s="8" t="s">
         <v>69</v>
@@ -6856,7 +7054,7 @@
         <v>39</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C40" s="8" t="s">
         <v>238</v>
@@ -6877,7 +7075,7 @@
         <v>40</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C41" s="8" t="s">
         <v>238</v>
@@ -6898,7 +7096,7 @@
         <v>41</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C42" s="8" t="s">
         <v>238</v>
@@ -6915,24 +7113,825 @@
       <c r="G42" s="8"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A43" s="9">
+        <v>42</v>
+      </c>
+      <c r="B43" s="14" t="s">
+        <v>475</v>
+      </c>
       <c r="C43" s="14" t="s">
+        <v>448</v>
+      </c>
+      <c r="D43" s="14" t="s">
+        <v>269</v>
+      </c>
+      <c r="E43" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="G43" s="8" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A44" s="9">
+        <v>43</v>
+      </c>
+      <c r="B44" s="14" t="s">
+        <v>477</v>
+      </c>
+      <c r="C44" s="14" t="s">
         <v>449</v>
       </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="C44" s="14" t="s">
+      <c r="D44" s="14" t="s">
+        <v>242</v>
+      </c>
+      <c r="E44" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="G44" s="8" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A45" s="9">
+        <v>44</v>
+      </c>
+      <c r="B45" s="14" t="s">
+        <v>455</v>
+      </c>
+      <c r="C45" s="14" t="s">
         <v>450</v>
       </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="C45" s="14" t="s">
+      <c r="D45" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="E45" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="F45" s="17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A46" s="9">
+        <v>45</v>
+      </c>
+      <c r="B46" t="s">
         <v>451</v>
+      </c>
+      <c r="C46" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="D46" t="s">
+        <v>269</v>
+      </c>
+      <c r="E46" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="F46" s="15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A47" s="9">
+        <v>46</v>
+      </c>
+      <c r="B47" s="14" t="s">
+        <v>452</v>
+      </c>
+      <c r="C47" s="14" t="s">
+        <v>449</v>
+      </c>
+      <c r="D47" t="s">
+        <v>283</v>
+      </c>
+      <c r="E47" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="G47" s="8" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A48" s="9">
+        <v>47</v>
+      </c>
+      <c r="B48" s="14" t="s">
+        <v>453</v>
+      </c>
+      <c r="C48" s="14" t="s">
+        <v>458</v>
+      </c>
+      <c r="D48" t="s">
+        <v>269</v>
+      </c>
+      <c r="E48" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="F48" s="18">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A49" s="9">
+        <v>48</v>
+      </c>
+      <c r="B49" s="14" t="s">
+        <v>454</v>
+      </c>
+      <c r="C49" s="14" t="s">
+        <v>458</v>
+      </c>
+      <c r="D49" t="s">
+        <v>269</v>
+      </c>
+      <c r="E49" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="F49" s="18">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A50" s="9">
+        <v>49</v>
+      </c>
+      <c r="B50" s="14" t="s">
+        <v>456</v>
+      </c>
+      <c r="C50" s="14" t="s">
+        <v>450</v>
+      </c>
+      <c r="D50" t="s">
+        <v>269</v>
+      </c>
+      <c r="E50" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="F50" s="18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A51" s="9">
+        <v>50</v>
+      </c>
+      <c r="B51" s="14" t="s">
+        <v>459</v>
+      </c>
+      <c r="C51" s="14" t="s">
+        <v>448</v>
+      </c>
+      <c r="D51" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="E51" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="F51" s="18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A52" s="9">
+        <v>51</v>
+      </c>
+      <c r="B52" s="14" t="s">
+        <v>457</v>
+      </c>
+      <c r="C52" s="14" t="s">
+        <v>450</v>
+      </c>
+      <c r="D52" t="s">
+        <v>269</v>
+      </c>
+      <c r="E52" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="F52" s="18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A53" s="16">
+        <v>52</v>
+      </c>
+      <c r="B53" s="14" t="s">
+        <v>460</v>
+      </c>
+      <c r="C53" s="14" t="s">
+        <v>448</v>
+      </c>
+      <c r="D53" t="s">
+        <v>269</v>
+      </c>
+      <c r="E53" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="F53" s="18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A54" s="16">
+        <v>53</v>
+      </c>
+      <c r="B54" s="14" t="s">
+        <v>492</v>
+      </c>
+      <c r="C54" s="14" t="s">
+        <v>491</v>
+      </c>
+      <c r="D54" s="14" t="s">
+        <v>493</v>
+      </c>
+      <c r="E54" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="F54" s="18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A55" s="16">
+        <v>54</v>
+      </c>
+      <c r="B55" s="14" t="s">
+        <v>461</v>
+      </c>
+      <c r="C55" s="14" t="s">
+        <v>463</v>
+      </c>
+      <c r="D55" t="s">
+        <v>462</v>
+      </c>
+      <c r="E55" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="F55" s="18">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A56" s="18">
+        <v>55</v>
+      </c>
+      <c r="B56" s="14" t="s">
+        <v>464</v>
+      </c>
+      <c r="C56" s="14" t="s">
+        <v>450</v>
+      </c>
+      <c r="D56" t="s">
+        <v>465</v>
+      </c>
+      <c r="E56" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="F56" s="20"/>
+      <c r="G56" s="8" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A57" s="19">
+        <v>56</v>
+      </c>
+      <c r="B57" s="14" t="s">
+        <v>466</v>
+      </c>
+      <c r="C57" s="14" t="s">
+        <v>450</v>
+      </c>
+      <c r="D57" t="s">
+        <v>269</v>
+      </c>
+      <c r="E57" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="F57" s="21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A58" s="19">
+        <v>56</v>
+      </c>
+      <c r="B58" s="22" t="s">
+        <v>467</v>
+      </c>
+      <c r="C58" s="14" t="s">
+        <v>472</v>
+      </c>
+      <c r="D58" t="s">
+        <v>269</v>
+      </c>
+      <c r="E58" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="F58" s="18">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A59" s="19">
+        <v>56</v>
+      </c>
+      <c r="B59" s="22" t="s">
+        <v>468</v>
+      </c>
+      <c r="C59" s="14" t="s">
+        <v>472</v>
+      </c>
+      <c r="D59" t="s">
+        <v>269</v>
+      </c>
+      <c r="E59" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="F59" s="18">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A60" s="19">
+        <v>57</v>
+      </c>
+      <c r="B60" s="14" t="s">
+        <v>441</v>
+      </c>
+      <c r="C60" s="14" t="s">
+        <v>472</v>
+      </c>
+      <c r="D60" t="s">
+        <v>269</v>
+      </c>
+      <c r="E60" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="F60" s="18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A61" s="19">
+        <v>58</v>
+      </c>
+      <c r="B61" s="14" t="s">
+        <v>471</v>
+      </c>
+      <c r="C61" s="14" t="s">
+        <v>472</v>
+      </c>
+      <c r="D61" t="s">
+        <v>269</v>
+      </c>
+      <c r="E61" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="F61" s="18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A62" s="19">
+        <v>59</v>
+      </c>
+      <c r="B62" s="14" t="s">
+        <v>473</v>
+      </c>
+      <c r="C62" s="14" t="s">
+        <v>449</v>
+      </c>
+      <c r="D62" t="s">
+        <v>269</v>
+      </c>
+      <c r="E62" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="F62" s="18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A63" s="19">
+        <v>60</v>
+      </c>
+      <c r="B63" s="14" t="s">
+        <v>474</v>
+      </c>
+      <c r="C63" s="14" t="s">
+        <v>448</v>
+      </c>
+      <c r="D63" t="s">
+        <v>149</v>
+      </c>
+      <c r="E63" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="G63" s="8" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A64" s="19">
+        <v>61</v>
+      </c>
+      <c r="B64" s="14" t="s">
+        <v>476</v>
+      </c>
+      <c r="C64" s="14" t="s">
+        <v>458</v>
+      </c>
+      <c r="D64" t="s">
+        <v>269</v>
+      </c>
+      <c r="E64" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="F64" s="24">
+        <v>1</v>
+      </c>
+      <c r="G64" s="8"/>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A65" s="19">
+        <v>62</v>
+      </c>
+      <c r="B65" s="14" t="s">
+        <v>478</v>
+      </c>
+      <c r="C65" s="14" t="s">
+        <v>448</v>
+      </c>
+      <c r="D65" t="s">
+        <v>269</v>
+      </c>
+      <c r="E65" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="G65" s="8" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A66" s="19">
+        <v>63</v>
+      </c>
+      <c r="B66" s="14" t="s">
+        <v>479</v>
+      </c>
+      <c r="C66" s="14" t="s">
+        <v>449</v>
+      </c>
+      <c r="D66" t="s">
+        <v>64</v>
+      </c>
+      <c r="E66" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="F66">
+        <v>1</v>
+      </c>
+      <c r="G66" s="8"/>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A67" s="19">
+        <v>64</v>
+      </c>
+      <c r="B67" s="14" t="s">
+        <v>480</v>
+      </c>
+      <c r="C67" s="23" t="s">
+        <v>458</v>
+      </c>
+      <c r="D67" t="s">
+        <v>269</v>
+      </c>
+      <c r="E67" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="F67">
+        <v>1</v>
+      </c>
+      <c r="G67" s="8"/>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A68" s="19">
+        <v>65</v>
+      </c>
+      <c r="B68" s="14" t="s">
+        <v>481</v>
+      </c>
+      <c r="C68" s="23" t="s">
+        <v>448</v>
+      </c>
+      <c r="D68" t="s">
+        <v>497</v>
+      </c>
+      <c r="E68" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="G68" s="8" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A69" s="19">
+        <v>66</v>
+      </c>
+      <c r="B69" s="14" t="s">
+        <v>482</v>
+      </c>
+      <c r="C69" s="23" t="s">
+        <v>458</v>
+      </c>
+      <c r="D69" t="s">
+        <v>64</v>
+      </c>
+      <c r="E69" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="F69">
+        <v>1</v>
+      </c>
+      <c r="G69" s="8"/>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A70" s="19">
+        <v>67</v>
+      </c>
+      <c r="B70" s="14" t="s">
+        <v>483</v>
+      </c>
+      <c r="C70" s="23" t="s">
+        <v>449</v>
+      </c>
+      <c r="D70" t="s">
+        <v>269</v>
+      </c>
+      <c r="E70" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="G70" s="8" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A71" s="19">
+        <v>68</v>
+      </c>
+      <c r="B71" s="14" t="s">
+        <v>484</v>
+      </c>
+      <c r="C71" s="23" t="s">
+        <v>449</v>
+      </c>
+      <c r="D71" t="s">
+        <v>269</v>
+      </c>
+      <c r="E71" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="G71" s="8" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A72" s="19">
+        <v>69</v>
+      </c>
+      <c r="B72" s="14" t="s">
+        <v>485</v>
+      </c>
+      <c r="C72" s="23" t="s">
+        <v>486</v>
+      </c>
+      <c r="D72" t="s">
+        <v>269</v>
+      </c>
+      <c r="E72" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="F72">
+        <v>1</v>
+      </c>
+      <c r="G72" s="8"/>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A73" s="19">
+        <v>70</v>
+      </c>
+      <c r="B73" s="14" t="s">
+        <v>487</v>
+      </c>
+      <c r="C73" s="23" t="s">
+        <v>486</v>
+      </c>
+      <c r="D73" t="s">
+        <v>269</v>
+      </c>
+      <c r="E73" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="F73">
+        <v>1</v>
+      </c>
+      <c r="G73" s="8"/>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A74" s="19">
+        <v>71</v>
+      </c>
+      <c r="B74" s="14" t="s">
+        <v>496</v>
+      </c>
+      <c r="C74" s="23" t="s">
+        <v>486</v>
+      </c>
+      <c r="D74" t="s">
+        <v>269</v>
+      </c>
+      <c r="E74" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="F74">
+        <v>1</v>
+      </c>
+      <c r="G74" s="8"/>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A75" s="19">
+        <v>72</v>
+      </c>
+      <c r="B75" s="14" t="s">
+        <v>488</v>
+      </c>
+      <c r="C75" s="23" t="s">
+        <v>491</v>
+      </c>
+      <c r="D75" t="s">
+        <v>495</v>
+      </c>
+      <c r="E75" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="F75">
+        <v>20</v>
+      </c>
+      <c r="G75" s="8"/>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A76" s="19">
+        <v>73</v>
+      </c>
+      <c r="B76" s="14" t="s">
+        <v>489</v>
+      </c>
+      <c r="C76" s="23" t="s">
+        <v>491</v>
+      </c>
+      <c r="D76" t="s">
+        <v>495</v>
+      </c>
+      <c r="E76" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="F76">
+        <v>20</v>
+      </c>
+      <c r="G76" s="8"/>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A77" s="19">
+        <v>74</v>
+      </c>
+      <c r="B77" s="14" t="s">
+        <v>490</v>
+      </c>
+      <c r="C77" s="23" t="s">
+        <v>491</v>
+      </c>
+      <c r="D77" t="s">
+        <v>495</v>
+      </c>
+      <c r="E77" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="F77">
+        <v>20</v>
+      </c>
+      <c r="G77" s="8"/>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A78" s="19">
+        <v>75</v>
+      </c>
+      <c r="B78" s="14" t="s">
+        <v>494</v>
+      </c>
+      <c r="C78" s="14" t="s">
+        <v>491</v>
+      </c>
+      <c r="D78" t="s">
+        <v>306</v>
+      </c>
+      <c r="E78" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="F78">
+        <v>2</v>
+      </c>
+      <c r="G78" s="8"/>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A79" s="19">
+        <v>76</v>
+      </c>
+      <c r="B79" s="14" t="s">
+        <v>498</v>
+      </c>
+      <c r="C79" s="14" t="s">
+        <v>491</v>
+      </c>
+      <c r="D79" t="s">
+        <v>264</v>
+      </c>
+      <c r="E79" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="F79" s="20">
+        <v>1</v>
+      </c>
+      <c r="G79" s="8"/>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A80" s="19">
+        <v>77</v>
+      </c>
+      <c r="B80" s="14" t="s">
+        <v>499</v>
+      </c>
+      <c r="C80" s="14" t="s">
+        <v>491</v>
+      </c>
+      <c r="D80" t="s">
+        <v>269</v>
+      </c>
+      <c r="E80" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="F80">
+        <v>1</v>
+      </c>
+      <c r="G80" s="8" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A81" s="19">
+        <v>78</v>
+      </c>
+      <c r="B81" s="14" t="s">
+        <v>500</v>
+      </c>
+      <c r="C81" s="14" t="s">
+        <v>491</v>
+      </c>
+      <c r="D81" t="s">
+        <v>67</v>
+      </c>
+      <c r="E81" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="F81" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A82" s="19">
+        <v>79</v>
+      </c>
+      <c r="B82" s="14" t="s">
+        <v>501</v>
+      </c>
+      <c r="C82" s="14" t="s">
+        <v>491</v>
+      </c>
+      <c r="D82" t="s">
+        <v>264</v>
+      </c>
+      <c r="E82" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="F82">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="10" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" errorTitle="Invalid brand" error="Choose yc, staple, or shared from the list." sqref="E3:E42" xr:uid="{00000000-0002-0000-0200-000000000000}">
+    <dataValidation type="list" errorTitle="Invalid brand" error="Choose yc, staple, or shared from the list." sqref="E3:E82" xr:uid="{00000000-0002-0000-0200-000000000000}">
       <formula1>"yc,staple,shared"</formula1>
     </dataValidation>
   </dataValidations>

--- a/NCD_Brand_Tagging.xlsx
+++ b/NCD_Brand_Tagging.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10802"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/praee/Desktop/CLAUDE/BQMP OPS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BE1FCAC-729F-DD4D-A549-DBACF1DFBFF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81166571-3007-AC4C-B29A-6EFA991AC35E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17220" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,20 @@
     <sheet name="Existing Items" sheetId="2" r:id="rId2"/>
     <sheet name="New Staple Items" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="0" iterateDelta="1E-4"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -74,7 +87,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1041" uniqueCount="502">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1068" uniqueCount="510">
   <si>
     <t>No.</t>
   </si>
@@ -1255,21 +1268,12 @@
     <t>Ricotta</t>
   </si>
   <si>
-    <t>Ham Cheese Sandwich</t>
-  </si>
-  <si>
     <t>To-Go Sandwich &amp; Salad</t>
   </si>
   <si>
     <t>ชิ้น</t>
   </si>
   <si>
-    <t>Egg Salad Sandwich</t>
-  </si>
-  <si>
-    <t>Tuna Sandwich</t>
-  </si>
-  <si>
     <t>Sour Hour - Ginger Lemon</t>
   </si>
   <si>
@@ -1402,15 +1406,6 @@
     <t>Orange Juice</t>
   </si>
   <si>
-    <t>Yogurt Bowl 1</t>
-  </si>
-  <si>
-    <t>Yogurt Bowl 2</t>
-  </si>
-  <si>
-    <t>Yogurt Bowl 3</t>
-  </si>
-  <si>
     <t>Plastic Wrap</t>
   </si>
   <si>
@@ -1580,13 +1575,55 @@
   </si>
   <si>
     <t>Chocolate Fudge Drink</t>
+  </si>
+  <si>
+    <t>Chicken Caesar Wrap</t>
+  </si>
+  <si>
+    <t>Chicken Pesto Wrap</t>
+  </si>
+  <si>
+    <t>Tuna  eggs and cheese wrap</t>
+  </si>
+  <si>
+    <t>Chicken Waldorf Salad</t>
+  </si>
+  <si>
+    <t>Chicken Caesar Salad</t>
+  </si>
+  <si>
+    <t>Tuna Herb Salad</t>
+  </si>
+  <si>
+    <t>Apple pecan pie greek yogurt</t>
+  </si>
+  <si>
+    <t>PB&amp;J greek yogurt</t>
+  </si>
+  <si>
+    <t>Blueberry pie greek yogurt</t>
+  </si>
+  <si>
+    <t>Biscoff overnight oats</t>
+  </si>
+  <si>
+    <t>To-Go Overnight Oats</t>
+  </si>
+  <si>
+    <t>Dark Chocolate Chia Pudding</t>
+  </si>
+  <si>
+    <t>Honey Yogurt Chia Pudding</t>
+  </si>
+  <si>
+    <t>To-Go Chia Pudding</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1656,6 +1693,11 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="YAHOUAhS5u0_0"/>
     </font>
   </fonts>
   <fills count="4">
@@ -1801,9 +1843,7 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2107,272 +2147,272 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:A57"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="100" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:1" ht="22" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>321</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:1">
       <c r="A2" s="2"/>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:1">
       <c r="A3" s="3" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:1">
       <c r="A4" s="3" t="s">
         <v>323</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:1">
       <c r="A5" s="3" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:1">
       <c r="A6" s="2"/>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:1">
       <c r="A7" s="4" t="s">
         <v>325</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:1">
       <c r="A8" s="3" t="s">
         <v>326</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:1">
       <c r="A9" s="3" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:1">
       <c r="A10" s="3" t="s">
         <v>328</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:1">
       <c r="A11" s="3" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:1">
       <c r="A12" s="3" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:1">
       <c r="A13" s="3" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:1">
       <c r="A14" s="3" t="s">
         <v>332</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:1">
       <c r="A15" s="3" t="s">
         <v>333</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:1">
       <c r="A16" s="3" t="s">
         <v>334</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:1">
       <c r="A17" s="3" t="s">
         <v>335</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:1">
       <c r="A18" s="3" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:1">
       <c r="A19" s="3" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:1">
       <c r="A20" s="3" t="s">
         <v>338</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:1">
       <c r="A21" s="3" t="s">
         <v>339</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:1">
       <c r="A22" s="3" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:1">
       <c r="A23" s="3" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:1">
       <c r="A24" s="3" t="s">
         <v>342</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:1">
       <c r="A25" s="2"/>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:1">
       <c r="A26" s="3" t="s">
         <v>343</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:1">
       <c r="A27" s="3" t="s">
         <v>344</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:1">
       <c r="A28" s="3" t="s">
         <v>345</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:1">
       <c r="A29" s="2"/>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:1">
       <c r="A30" s="4" t="s">
         <v>346</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:1">
       <c r="A31" s="3" t="s">
         <v>347</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:1">
       <c r="A32" s="3" t="s">
         <v>348</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:1">
       <c r="A33" s="3" t="s">
         <v>349</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:1">
       <c r="A34" s="3" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:1">
       <c r="A35" s="3" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:1">
       <c r="A36" s="3" t="s">
         <v>352</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:1">
       <c r="A37" s="3" t="s">
         <v>353</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:1">
       <c r="A38" s="3" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:1">
       <c r="A39" s="2"/>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:1">
       <c r="A40" s="4" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:1">
       <c r="A42" t="s">
         <v>356</v>
       </c>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:1">
       <c r="A43" t="s">
         <v>357</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:1">
       <c r="A44" t="s">
         <v>358</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:1">
       <c r="A45" t="s">
         <v>359</v>
       </c>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:1">
       <c r="A46" t="s">
         <v>360</v>
       </c>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:1">
       <c r="A47" t="s">
         <v>361</v>
       </c>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:1">
       <c r="A48" t="s">
         <v>362</v>
       </c>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:1">
       <c r="A49" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:1">
       <c r="A50" t="s">
         <v>364</v>
       </c>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:1">
       <c r="A51" t="s">
         <v>365</v>
       </c>
     </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:1">
       <c r="A52" t="s">
         <v>366</v>
       </c>
     </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:1">
       <c r="A54" t="s">
         <v>367</v>
       </c>
     </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:1">
       <c r="A55" t="s">
         <v>368</v>
       </c>
     </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:1">
       <c r="A56" t="s">
         <v>369</v>
       </c>
     </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:1">
       <c r="A57" t="s">
         <v>370</v>
       </c>
@@ -2385,7 +2425,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:M119"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>
@@ -2398,7 +2438,7 @@
     <col min="9" max="11" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:13" ht="30" customHeight="1">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -2439,7 +2479,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:13">
       <c r="A2" s="6">
         <v>1</v>
       </c>
@@ -2472,7 +2512,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:13">
       <c r="A3" s="6">
         <v>2</v>
       </c>
@@ -2486,7 +2526,7 @@
         <v>19</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="F3" s="7" t="s">
         <v>16</v>
@@ -2507,7 +2547,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:13">
       <c r="A4" s="6">
         <v>3</v>
       </c>
@@ -2538,7 +2578,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13">
       <c r="A5" s="6">
         <v>4</v>
       </c>
@@ -2569,7 +2609,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13">
       <c r="A6" s="6">
         <v>5</v>
       </c>
@@ -2600,7 +2640,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13">
       <c r="A7" s="6">
         <v>6</v>
       </c>
@@ -2631,7 +2671,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:13">
       <c r="A8" s="6">
         <v>7</v>
       </c>
@@ -2662,7 +2702,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:13">
       <c r="A9" s="6">
         <v>8</v>
       </c>
@@ -2693,7 +2733,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:13">
       <c r="A10" s="6">
         <v>9</v>
       </c>
@@ -2724,7 +2764,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:13">
       <c r="A11" s="6">
         <v>10</v>
       </c>
@@ -2760,7 +2800,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:13">
       <c r="A12" s="6">
         <v>11</v>
       </c>
@@ -2796,7 +2836,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:13">
       <c r="A13" s="6">
         <v>12</v>
       </c>
@@ -2825,7 +2865,7 @@
       </c>
       <c r="K13" s="6"/>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:13">
       <c r="A14" s="6">
         <v>13</v>
       </c>
@@ -2854,7 +2894,7 @@
       </c>
       <c r="K14" s="6"/>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:13">
       <c r="A15" s="6">
         <v>14</v>
       </c>
@@ -2881,7 +2921,7 @@
       <c r="J15" s="6"/>
       <c r="K15" s="6"/>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:13">
       <c r="A16" s="6">
         <v>15</v>
       </c>
@@ -2908,7 +2948,7 @@
       <c r="J16" s="6"/>
       <c r="K16" s="6"/>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:12">
       <c r="A17" s="6">
         <v>16</v>
       </c>
@@ -2937,7 +2977,7 @@
       </c>
       <c r="K17" s="6"/>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:12">
       <c r="A18" s="6">
         <v>17</v>
       </c>
@@ -2951,7 +2991,7 @@
         <v>60</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="F18" s="7" t="s">
         <v>57</v>
@@ -2970,7 +3010,7 @@
       </c>
       <c r="K18" s="6"/>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:12">
       <c r="A19" s="6">
         <v>18</v>
       </c>
@@ -2995,7 +3035,7 @@
       <c r="J19" s="6"/>
       <c r="K19" s="6"/>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:12">
       <c r="A20" s="6">
         <v>19</v>
       </c>
@@ -3009,7 +3049,7 @@
         <v>66</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="F20" s="7" t="s">
         <v>67</v>
@@ -3031,7 +3071,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:12">
       <c r="A21" s="6">
         <v>20</v>
       </c>
@@ -3045,7 +3085,7 @@
         <v>71</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="F21" s="7" t="s">
         <v>72</v>
@@ -3069,7 +3109,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:12">
       <c r="A22" s="6">
         <v>21</v>
       </c>
@@ -3083,7 +3123,7 @@
         <v>74</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="F22" s="7" t="s">
         <v>72</v>
@@ -3107,7 +3147,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:12">
       <c r="A23" s="6">
         <v>22</v>
       </c>
@@ -3121,7 +3161,7 @@
         <v>76</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="F23" s="7" t="s">
         <v>72</v>
@@ -3145,7 +3185,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:12">
       <c r="A24" s="6">
         <v>23</v>
       </c>
@@ -3159,7 +3199,7 @@
         <v>78</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="F24" s="7" t="s">
         <v>72</v>
@@ -3183,7 +3223,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:12">
       <c r="A25" s="6">
         <v>24</v>
       </c>
@@ -3197,7 +3237,7 @@
         <v>80</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="F25" s="7" t="s">
         <v>72</v>
@@ -3221,7 +3261,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:12">
       <c r="A26" s="6">
         <v>25</v>
       </c>
@@ -3235,7 +3275,7 @@
         <v>82</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="F26" s="7" t="s">
         <v>72</v>
@@ -3259,7 +3299,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:12">
       <c r="A27" s="6">
         <v>26</v>
       </c>
@@ -3273,7 +3313,7 @@
         <v>85</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="F27" s="7" t="s">
         <v>64</v>
@@ -3295,7 +3335,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:12">
       <c r="A28" s="6">
         <v>27</v>
       </c>
@@ -3309,7 +3349,7 @@
         <v>89</v>
       </c>
       <c r="E28" s="8" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="F28" s="7" t="s">
         <v>64</v>
@@ -3331,7 +3371,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:12">
       <c r="A29" s="6">
         <v>28</v>
       </c>
@@ -3365,7 +3405,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:12">
       <c r="A30" s="6">
         <v>29</v>
       </c>
@@ -3398,7 +3438,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:12">
       <c r="A31" s="6">
         <v>30</v>
       </c>
@@ -3431,7 +3471,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:12">
       <c r="A32" s="6">
         <v>31</v>
       </c>
@@ -3464,7 +3504,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:11">
       <c r="A33" s="6">
         <v>32</v>
       </c>
@@ -3497,7 +3537,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:11">
       <c r="A34" s="6">
         <v>33</v>
       </c>
@@ -3530,7 +3570,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:11">
       <c r="A35" s="6">
         <v>34</v>
       </c>
@@ -3561,7 +3601,7 @@
       </c>
       <c r="K35" s="6"/>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:11">
       <c r="A36" s="6">
         <v>35</v>
       </c>
@@ -3592,7 +3632,7 @@
       </c>
       <c r="K36" s="6"/>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:11">
       <c r="A37" s="6">
         <v>36</v>
       </c>
@@ -3623,7 +3663,7 @@
       </c>
       <c r="K37" s="6"/>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:11">
       <c r="A38" s="6">
         <v>37</v>
       </c>
@@ -3654,7 +3694,7 @@
       </c>
       <c r="K38" s="6"/>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:11">
       <c r="A39" s="6">
         <v>38</v>
       </c>
@@ -3687,7 +3727,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:11">
       <c r="A40" s="6">
         <v>39</v>
       </c>
@@ -3720,7 +3760,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:11">
       <c r="A41" s="6">
         <v>40</v>
       </c>
@@ -3753,7 +3793,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:11">
       <c r="A42" s="6">
         <v>41</v>
       </c>
@@ -3784,7 +3824,7 @@
       </c>
       <c r="K42" s="6"/>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:11">
       <c r="A43" s="6">
         <v>42</v>
       </c>
@@ -3815,7 +3855,7 @@
       </c>
       <c r="K43" s="6"/>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:11">
       <c r="A44" s="6">
         <v>43</v>
       </c>
@@ -3848,7 +3888,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:11">
       <c r="A45" s="6">
         <v>44</v>
       </c>
@@ -3873,7 +3913,7 @@
       <c r="J45" s="6"/>
       <c r="K45" s="6"/>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:11">
       <c r="A46" s="6">
         <v>45</v>
       </c>
@@ -3898,7 +3938,7 @@
       <c r="J46" s="6"/>
       <c r="K46" s="6"/>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:11">
       <c r="A47" s="6">
         <v>46</v>
       </c>
@@ -3931,7 +3971,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:11">
       <c r="A48" s="6">
         <v>47</v>
       </c>
@@ -3956,7 +3996,7 @@
       <c r="J48" s="6"/>
       <c r="K48" s="6"/>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:11">
       <c r="A49" s="6">
         <v>48</v>
       </c>
@@ -3989,7 +4029,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:11">
       <c r="A50" s="6">
         <v>49</v>
       </c>
@@ -4022,7 +4062,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:11">
       <c r="A51" s="6">
         <v>50</v>
       </c>
@@ -4055,7 +4095,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:11">
       <c r="A52" s="6">
         <v>51</v>
       </c>
@@ -4088,7 +4128,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:11">
       <c r="A53" s="6">
         <v>52</v>
       </c>
@@ -4102,7 +4142,7 @@
         <v>157</v>
       </c>
       <c r="E53" s="7" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="F53" s="7" t="s">
         <v>126</v>
@@ -4123,7 +4163,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:11">
       <c r="A54" s="6">
         <v>53</v>
       </c>
@@ -4154,7 +4194,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:11">
       <c r="A55" s="6">
         <v>54</v>
       </c>
@@ -4185,7 +4225,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:11">
       <c r="A56" s="6">
         <v>55</v>
       </c>
@@ -4199,7 +4239,7 @@
         <v>165</v>
       </c>
       <c r="E56" s="8" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="F56" s="7" t="s">
         <v>161</v>
@@ -4220,7 +4260,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:11">
       <c r="A57" s="6">
         <v>56</v>
       </c>
@@ -4255,7 +4295,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:11">
       <c r="A58" s="6">
         <v>57</v>
       </c>
@@ -4269,7 +4309,7 @@
         <v>171</v>
       </c>
       <c r="E58" s="8" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="F58" s="7" t="s">
         <v>161</v>
@@ -4290,7 +4330,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:11">
       <c r="A59" s="6">
         <v>58</v>
       </c>
@@ -4304,7 +4344,7 @@
         <v>173</v>
       </c>
       <c r="E59" s="8" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="F59" s="7" t="s">
         <v>161</v>
@@ -4325,7 +4365,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:11">
       <c r="A60" s="6">
         <v>59</v>
       </c>
@@ -4339,7 +4379,7 @@
         <v>175</v>
       </c>
       <c r="E60" s="8" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="F60" s="7" t="s">
         <v>161</v>
@@ -4360,7 +4400,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:11">
       <c r="A61" s="6">
         <v>60</v>
       </c>
@@ -4393,7 +4433,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:11">
       <c r="A62" s="6">
         <v>61</v>
       </c>
@@ -4407,7 +4447,7 @@
         <v>180</v>
       </c>
       <c r="E62" s="7" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="F62" s="7" t="s">
         <v>161</v>
@@ -4428,7 +4468,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:11">
       <c r="A63" s="6">
         <v>62</v>
       </c>
@@ -4459,7 +4499,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:11">
       <c r="A64" s="6">
         <v>63</v>
       </c>
@@ -4473,7 +4513,7 @@
         <v>184</v>
       </c>
       <c r="E64" s="8" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="F64" s="7" t="s">
         <v>161</v>
@@ -4494,7 +4534,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:11">
       <c r="A65" s="6">
         <v>64</v>
       </c>
@@ -4527,7 +4567,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:11">
       <c r="A66" s="6">
         <v>65</v>
       </c>
@@ -4560,7 +4600,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:11">
       <c r="A67" s="6">
         <v>66</v>
       </c>
@@ -4593,7 +4633,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:11">
       <c r="A68" s="6">
         <v>67</v>
       </c>
@@ -4626,7 +4666,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:11">
       <c r="A69" s="6">
         <v>68</v>
       </c>
@@ -4659,7 +4699,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:11">
       <c r="A70" s="6">
         <v>69</v>
       </c>
@@ -4690,7 +4730,7 @@
       </c>
       <c r="K70" s="6"/>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:11">
       <c r="A71" s="6">
         <v>70</v>
       </c>
@@ -4723,7 +4763,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:11">
       <c r="A72" s="6">
         <v>71</v>
       </c>
@@ -4754,7 +4794,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:11">
       <c r="A73" s="6">
         <v>72</v>
       </c>
@@ -4785,7 +4825,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:11">
       <c r="A74" s="6">
         <v>73</v>
       </c>
@@ -4816,7 +4856,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:11">
       <c r="A75" s="6">
         <v>74</v>
       </c>
@@ -4847,7 +4887,7 @@
       </c>
       <c r="K75" s="6"/>
     </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:11">
       <c r="A76" s="6">
         <v>75</v>
       </c>
@@ -4880,7 +4920,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:11">
       <c r="A77" s="6">
         <v>76</v>
       </c>
@@ -4913,7 +4953,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:11">
       <c r="A78" s="6">
         <v>77</v>
       </c>
@@ -4946,7 +4986,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:11">
       <c r="A79" s="6">
         <v>78</v>
       </c>
@@ -4979,7 +5019,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:11">
       <c r="A80" s="6">
         <v>79</v>
       </c>
@@ -5008,7 +5048,7 @@
       </c>
       <c r="K80" s="6"/>
     </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:11">
       <c r="A81" s="6">
         <v>80</v>
       </c>
@@ -5037,7 +5077,7 @@
       </c>
       <c r="K81" s="6"/>
     </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:11">
       <c r="A82" s="6">
         <v>81</v>
       </c>
@@ -5066,7 +5106,7 @@
       </c>
       <c r="K82" s="6"/>
     </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:11">
       <c r="A83" s="6">
         <v>82</v>
       </c>
@@ -5095,7 +5135,7 @@
       </c>
       <c r="K83" s="6"/>
     </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:11">
       <c r="A84" s="6">
         <v>83</v>
       </c>
@@ -5126,7 +5166,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:11">
       <c r="A85" s="6">
         <v>84</v>
       </c>
@@ -5155,7 +5195,7 @@
       </c>
       <c r="K85" s="6"/>
     </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:11">
       <c r="A86" s="6">
         <v>85</v>
       </c>
@@ -5188,7 +5228,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:11">
       <c r="A87" s="6">
         <v>86</v>
       </c>
@@ -5219,7 +5259,7 @@
       </c>
       <c r="K87" s="6"/>
     </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:11">
       <c r="A88" s="6">
         <v>87</v>
       </c>
@@ -5250,7 +5290,7 @@
       </c>
       <c r="K88" s="6"/>
     </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:11">
       <c r="A89" s="6">
         <v>88</v>
       </c>
@@ -5279,7 +5319,7 @@
       </c>
       <c r="K89" s="6"/>
     </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:11">
       <c r="A90" s="6">
         <v>89</v>
       </c>
@@ -5310,7 +5350,7 @@
       </c>
       <c r="K90" s="6"/>
     </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:11">
       <c r="A91" s="6">
         <v>90</v>
       </c>
@@ -5339,7 +5379,7 @@
       <c r="J91" s="6"/>
       <c r="K91" s="6"/>
     </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:11">
       <c r="A92" s="6">
         <v>91</v>
       </c>
@@ -5370,7 +5410,7 @@
       </c>
       <c r="K92" s="6"/>
     </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:11">
       <c r="A93" s="6">
         <v>92</v>
       </c>
@@ -5401,7 +5441,7 @@
       </c>
       <c r="K93" s="6"/>
     </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:11">
       <c r="A94" s="6">
         <v>93</v>
       </c>
@@ -5430,7 +5470,7 @@
       <c r="J94" s="6"/>
       <c r="K94" s="6"/>
     </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:11">
       <c r="A95" s="6">
         <v>94</v>
       </c>
@@ -5461,7 +5501,7 @@
       </c>
       <c r="K95" s="6"/>
     </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:11">
       <c r="A96" s="6">
         <v>95</v>
       </c>
@@ -5492,7 +5532,7 @@
       </c>
       <c r="K96" s="6"/>
     </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:11">
       <c r="A97" s="6">
         <v>96</v>
       </c>
@@ -5523,7 +5563,7 @@
       </c>
       <c r="K97" s="6"/>
     </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:11">
       <c r="A98" s="6">
         <v>97</v>
       </c>
@@ -5554,7 +5594,7 @@
       </c>
       <c r="K98" s="6"/>
     </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:11">
       <c r="A99" s="6">
         <v>98</v>
       </c>
@@ -5585,7 +5625,7 @@
       </c>
       <c r="K99" s="6"/>
     </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:11">
       <c r="A100" s="6">
         <v>99</v>
       </c>
@@ -5614,7 +5654,7 @@
       </c>
       <c r="K100" s="6"/>
     </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:11">
       <c r="A101" s="6">
         <v>100</v>
       </c>
@@ -5643,7 +5683,7 @@
       </c>
       <c r="K101" s="6"/>
     </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:11">
       <c r="A102" s="6">
         <v>101</v>
       </c>
@@ -5672,7 +5712,7 @@
       </c>
       <c r="K102" s="6"/>
     </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:11">
       <c r="A103" s="6">
         <v>102</v>
       </c>
@@ -5701,7 +5741,7 @@
       </c>
       <c r="K103" s="6"/>
     </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:11">
       <c r="A104" s="6">
         <v>103</v>
       </c>
@@ -5730,7 +5770,7 @@
       </c>
       <c r="K104" s="6"/>
     </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:11">
       <c r="A105" s="6">
         <v>104</v>
       </c>
@@ -5759,7 +5799,7 @@
       </c>
       <c r="K105" s="6"/>
     </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:11">
       <c r="A106" s="6">
         <v>105</v>
       </c>
@@ -5788,7 +5828,7 @@
       </c>
       <c r="K106" s="6"/>
     </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:11">
       <c r="A107" s="6">
         <v>106</v>
       </c>
@@ -5817,7 +5857,7 @@
       </c>
       <c r="K107" s="6"/>
     </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:11">
       <c r="A108" s="6">
         <v>107</v>
       </c>
@@ -5850,7 +5890,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:11">
       <c r="A109" s="6">
         <v>108</v>
       </c>
@@ -5879,7 +5919,7 @@
       </c>
       <c r="K109" s="6"/>
     </row>
-    <row r="110" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:11">
       <c r="A110" s="6">
         <v>109</v>
       </c>
@@ -5912,7 +5952,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:11">
       <c r="A111" s="6">
         <v>110</v>
       </c>
@@ -5945,7 +5985,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:11">
       <c r="A112" s="6">
         <v>111</v>
       </c>
@@ -5978,7 +6018,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:12">
       <c r="A113" s="6">
         <v>112</v>
       </c>
@@ -6011,7 +6051,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:12">
       <c r="A114" s="6">
         <v>113</v>
       </c>
@@ -6038,7 +6078,7 @@
       <c r="J114" s="6"/>
       <c r="K114" s="6"/>
     </row>
-    <row r="115" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:12">
       <c r="A115" s="6">
         <v>114</v>
       </c>
@@ -6065,7 +6105,7 @@
       <c r="J115" s="6"/>
       <c r="K115" s="6"/>
     </row>
-    <row r="116" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:12">
       <c r="A116" s="6">
         <v>115</v>
       </c>
@@ -6092,7 +6132,7 @@
       <c r="J116" s="6"/>
       <c r="K116" s="6"/>
     </row>
-    <row r="117" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:12">
       <c r="A117" s="6">
         <v>116</v>
       </c>
@@ -6126,7 +6166,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="118" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:12">
       <c r="A118" s="6">
         <v>117</v>
       </c>
@@ -6159,7 +6199,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="119" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:12">
       <c r="A119" s="6">
         <v>118</v>
       </c>
@@ -6201,8 +6241,8 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:H82"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:H92"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
@@ -6213,7 +6253,7 @@
     <col min="7" max="7" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="26" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" ht="26" customHeight="1">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -6239,7 +6279,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" ht="28" customHeight="1">
       <c r="A2" s="10">
         <v>1</v>
       </c>
@@ -6262,7 +6302,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" ht="42" customHeight="1">
       <c r="A3" s="9">
         <v>2</v>
       </c>
@@ -6285,7 +6325,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="70" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" ht="70" customHeight="1">
       <c r="A4" s="9">
         <v>3</v>
       </c>
@@ -6308,7 +6348,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="70" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8" ht="70" customHeight="1">
       <c r="A5" s="9">
         <v>4</v>
       </c>
@@ -6331,7 +6371,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8" ht="28" customHeight="1">
       <c r="A6" s="9">
         <v>5</v>
       </c>
@@ -6354,7 +6394,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:8" ht="28" customHeight="1">
       <c r="A7" s="9">
         <v>6</v>
       </c>
@@ -6377,7 +6417,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:8">
       <c r="A8" s="9">
         <v>7</v>
       </c>
@@ -6398,7 +6438,7 @@
       </c>
       <c r="G8" s="8"/>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:8">
       <c r="A9" s="9">
         <v>8</v>
       </c>
@@ -6419,81 +6459,75 @@
       </c>
       <c r="G9" s="8"/>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:8">
       <c r="A10" s="9">
         <v>9</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="22" t="s">
+        <v>496</v>
+      </c>
+      <c r="C10" s="8" t="s">
         <v>393</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="D10" s="8" t="s">
         <v>394</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>395</v>
       </c>
       <c r="E10" s="8" t="s">
         <v>86</v>
       </c>
       <c r="F10" s="9"/>
-      <c r="G10" s="8" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G10" s="8"/>
+    </row>
+    <row r="11" spans="1:8">
       <c r="A11" s="9">
         <v>10</v>
       </c>
-      <c r="B11" s="8" t="s">
-        <v>396</v>
+      <c r="B11" s="22" t="s">
+        <v>497</v>
       </c>
       <c r="C11" s="8" t="s">
+        <v>393</v>
+      </c>
+      <c r="D11" s="8" t="s">
         <v>394</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>395</v>
       </c>
       <c r="E11" s="8" t="s">
         <v>86</v>
       </c>
       <c r="F11" s="9"/>
-      <c r="G11" s="8" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G11" s="8"/>
+    </row>
+    <row r="12" spans="1:8">
       <c r="A12" s="9">
         <v>11</v>
       </c>
-      <c r="B12" s="8" t="s">
-        <v>397</v>
+      <c r="B12" s="22" t="s">
+        <v>498</v>
       </c>
       <c r="C12" s="8" t="s">
+        <v>393</v>
+      </c>
+      <c r="D12" s="8" t="s">
         <v>394</v>
-      </c>
-      <c r="D12" s="8" t="s">
-        <v>395</v>
       </c>
       <c r="E12" s="8" t="s">
         <v>86</v>
       </c>
       <c r="F12" s="9"/>
-      <c r="G12" s="8" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G12" s="8"/>
+    </row>
+    <row r="13" spans="1:8">
       <c r="A13" s="9">
         <v>12</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="C13" s="8" t="s">
         <v>69</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="E13" s="8" t="s">
         <v>86</v>
@@ -6503,18 +6537,18 @@
       </c>
       <c r="G13" s="8"/>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:8">
       <c r="A14" s="9">
         <v>13</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="C14" s="8" t="s">
         <v>69</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="E14" s="8" t="s">
         <v>86</v>
@@ -6524,12 +6558,12 @@
       </c>
       <c r="G14" s="8"/>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:8">
       <c r="A15" s="9">
         <v>14</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="C15" s="8" t="s">
         <v>69</v>
@@ -6545,18 +6579,18 @@
       </c>
       <c r="G15" s="8"/>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:8">
       <c r="A16" s="9">
         <v>15</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="C16" s="8" t="s">
         <v>69</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="E16" s="8" t="s">
         <v>86</v>
@@ -6566,18 +6600,18 @@
       </c>
       <c r="G16" s="8"/>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7">
       <c r="A17" s="9">
         <v>16</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="C17" s="8" t="s">
         <v>69</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="E17" s="8" t="s">
         <v>86</v>
@@ -6587,18 +6621,18 @@
       </c>
       <c r="G17" s="8"/>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7">
       <c r="A18" s="9">
         <v>17</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="C18" s="8" t="s">
         <v>238</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="E18" s="8" t="s">
         <v>68</v>
@@ -6608,12 +6642,12 @@
       </c>
       <c r="G18" s="8"/>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7">
       <c r="A19" s="9">
         <v>18</v>
       </c>
-      <c r="B19" s="8" t="s">
-        <v>442</v>
+      <c r="B19" t="s">
+        <v>502</v>
       </c>
       <c r="C19" s="8" t="s">
         <v>38</v>
@@ -6626,15 +6660,15 @@
       </c>
       <c r="F19" s="9"/>
       <c r="G19" s="8" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
       <c r="A20" s="9">
         <v>19</v>
       </c>
-      <c r="B20" s="8" t="s">
-        <v>443</v>
+      <c r="B20" t="s">
+        <v>503</v>
       </c>
       <c r="C20" s="8" t="s">
         <v>38</v>
@@ -6647,15 +6681,15 @@
       </c>
       <c r="F20" s="9"/>
       <c r="G20" s="8" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
       <c r="A21" s="9">
         <v>20</v>
       </c>
-      <c r="B21" s="8" t="s">
-        <v>444</v>
+      <c r="B21" t="s">
+        <v>504</v>
       </c>
       <c r="C21" s="8" t="s">
         <v>38</v>
@@ -6668,21 +6702,21 @@
       </c>
       <c r="F21" s="9"/>
       <c r="G21" s="8" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
       <c r="A22" s="9">
         <v>21</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="C22" s="8" t="s">
         <v>238</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="E22" s="8" t="s">
         <v>68</v>
@@ -6692,18 +6726,18 @@
       </c>
       <c r="G22" s="8"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:7">
       <c r="A23" s="9">
         <v>22</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="C23" s="8" t="s">
         <v>238</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="E23" s="8" t="s">
         <v>68</v>
@@ -6713,12 +6747,12 @@
       </c>
       <c r="G23" s="8"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:7">
       <c r="A24" s="9">
         <v>23</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="C24" s="7" t="s">
         <v>159</v>
@@ -6734,12 +6768,12 @@
       </c>
       <c r="G24" s="8"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:7">
       <c r="A25" s="9">
         <v>24</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="C25" s="8" t="s">
         <v>242</v>
@@ -6755,12 +6789,12 @@
       </c>
       <c r="G25" s="8"/>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:7">
       <c r="A26" s="9">
         <v>25</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="C26" s="7" t="s">
         <v>177</v>
@@ -6776,12 +6810,12 @@
       </c>
       <c r="G26" s="8"/>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:7">
       <c r="A27" s="9">
         <v>26</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="C27" s="7" t="s">
         <v>186</v>
@@ -6797,12 +6831,12 @@
       </c>
       <c r="G27" s="8"/>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:7">
       <c r="A28" s="9">
         <v>27</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="C28" s="7" t="s">
         <v>186</v>
@@ -6818,12 +6852,12 @@
       </c>
       <c r="G28" s="8"/>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:7">
       <c r="A29" s="9">
         <v>28</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="C29" s="8" t="s">
         <v>242</v>
@@ -6839,12 +6873,12 @@
       </c>
       <c r="G29" s="8"/>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:7">
       <c r="A30" s="9">
         <v>29</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="C30" s="7" t="s">
         <v>231</v>
@@ -6860,12 +6894,12 @@
       </c>
       <c r="G30" s="8"/>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:7">
       <c r="A31" s="9">
         <v>30</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="C31" s="7" t="s">
         <v>231</v>
@@ -6881,12 +6915,12 @@
       </c>
       <c r="G31" s="8"/>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:7">
       <c r="A32" s="9">
         <v>31</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="C32" s="7" t="s">
         <v>231</v>
@@ -6902,12 +6936,12 @@
       </c>
       <c r="G32" s="8"/>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:7">
       <c r="A33" s="9">
         <v>32</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C33" s="7" t="s">
         <v>231</v>
@@ -6923,12 +6957,12 @@
       </c>
       <c r="G33" s="8"/>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:7">
       <c r="A34" s="9">
         <v>33</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="C34" s="7" t="s">
         <v>231</v>
@@ -6944,12 +6978,12 @@
       </c>
       <c r="G34" s="8"/>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:7">
       <c r="A35" s="9">
         <v>34</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="C35" s="7" t="s">
         <v>231</v>
@@ -6965,12 +6999,12 @@
       </c>
       <c r="G35" s="8"/>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:7">
       <c r="A36" s="9">
         <v>35</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C36" s="7" t="s">
         <v>231</v>
@@ -6986,12 +7020,12 @@
       </c>
       <c r="G36" s="8"/>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:7">
       <c r="A37" s="9">
         <v>36</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="C37" s="7" t="s">
         <v>231</v>
@@ -7007,12 +7041,12 @@
       </c>
       <c r="G37" s="8"/>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:7">
       <c r="A38" s="9">
         <v>37</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>469</v>
+        <v>463</v>
       </c>
       <c r="C38" s="8" t="s">
         <v>69</v>
@@ -7025,15 +7059,15 @@
       </c>
       <c r="F38" s="9"/>
       <c r="G38" s="8" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
       <c r="A39" s="9">
         <v>38</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>470</v>
+        <v>464</v>
       </c>
       <c r="C39" s="8" t="s">
         <v>69</v>
@@ -7046,15 +7080,15 @@
       </c>
       <c r="F39" s="9"/>
       <c r="G39" s="8" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
       <c r="A40" s="9">
         <v>39</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>446</v>
+        <v>440</v>
       </c>
       <c r="C40" s="8" t="s">
         <v>238</v>
@@ -7070,12 +7104,12 @@
       </c>
       <c r="G40" s="8"/>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:7">
       <c r="A41" s="9">
         <v>40</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="C41" s="8" t="s">
         <v>238</v>
@@ -7091,18 +7125,18 @@
       </c>
       <c r="G41" s="8"/>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:7">
       <c r="A42" s="9">
         <v>41</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>445</v>
+        <v>439</v>
       </c>
       <c r="C42" s="8" t="s">
         <v>238</v>
       </c>
       <c r="D42" s="8" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="E42" s="8" t="s">
         <v>86</v>
@@ -7112,15 +7146,15 @@
       </c>
       <c r="G42" s="8"/>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:7">
       <c r="A43" s="9">
         <v>42</v>
       </c>
       <c r="B43" s="14" t="s">
-        <v>475</v>
+        <v>469</v>
       </c>
       <c r="C43" s="14" t="s">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="D43" s="14" t="s">
         <v>269</v>
@@ -7129,18 +7163,18 @@
         <v>86</v>
       </c>
       <c r="G43" s="8" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
       <c r="A44" s="9">
         <v>43</v>
       </c>
       <c r="B44" s="14" t="s">
-        <v>477</v>
+        <v>471</v>
       </c>
       <c r="C44" s="14" t="s">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="D44" s="14" t="s">
         <v>242</v>
@@ -7149,18 +7183,18 @@
         <v>86</v>
       </c>
       <c r="G44" s="8" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
       <c r="A45" s="9">
         <v>44</v>
       </c>
       <c r="B45" s="14" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="C45" s="14" t="s">
-        <v>450</v>
+        <v>444</v>
       </c>
       <c r="D45" s="14" t="s">
         <v>64</v>
@@ -7172,12 +7206,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:7">
       <c r="A46" s="9">
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>451</v>
+        <v>445</v>
       </c>
       <c r="C46" s="7" t="s">
         <v>186</v>
@@ -7192,15 +7226,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:7">
       <c r="A47" s="9">
         <v>46</v>
       </c>
       <c r="B47" s="14" t="s">
-        <v>452</v>
+        <v>446</v>
       </c>
       <c r="C47" s="14" t="s">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="D47" t="s">
         <v>283</v>
@@ -7209,18 +7243,18 @@
         <v>86</v>
       </c>
       <c r="G47" s="8" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7">
       <c r="A48" s="9">
         <v>47</v>
       </c>
       <c r="B48" s="14" t="s">
-        <v>453</v>
+        <v>447</v>
       </c>
       <c r="C48" s="14" t="s">
-        <v>458</v>
+        <v>452</v>
       </c>
       <c r="D48" t="s">
         <v>269</v>
@@ -7232,15 +7266,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:7">
       <c r="A49" s="9">
         <v>48</v>
       </c>
       <c r="B49" s="14" t="s">
-        <v>454</v>
+        <v>448</v>
       </c>
       <c r="C49" s="14" t="s">
-        <v>458</v>
+        <v>452</v>
       </c>
       <c r="D49" t="s">
         <v>269</v>
@@ -7252,15 +7286,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:7">
       <c r="A50" s="9">
         <v>49</v>
       </c>
       <c r="B50" s="14" t="s">
-        <v>456</v>
+        <v>450</v>
       </c>
       <c r="C50" s="14" t="s">
-        <v>450</v>
+        <v>444</v>
       </c>
       <c r="D50" t="s">
         <v>269</v>
@@ -7272,15 +7306,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:7">
       <c r="A51" s="9">
         <v>50</v>
       </c>
       <c r="B51" s="14" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="C51" s="14" t="s">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="D51" s="14" t="s">
         <v>64</v>
@@ -7292,15 +7326,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:7">
       <c r="A52" s="9">
         <v>51</v>
       </c>
       <c r="B52" s="14" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="C52" s="14" t="s">
-        <v>450</v>
+        <v>444</v>
       </c>
       <c r="D52" t="s">
         <v>269</v>
@@ -7312,15 +7346,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:7">
       <c r="A53" s="16">
         <v>52</v>
       </c>
       <c r="B53" s="14" t="s">
-        <v>460</v>
+        <v>454</v>
       </c>
       <c r="C53" s="14" t="s">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="D53" t="s">
         <v>269</v>
@@ -7332,18 +7366,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:7">
       <c r="A54" s="16">
         <v>53</v>
       </c>
       <c r="B54" s="14" t="s">
-        <v>492</v>
+        <v>486</v>
       </c>
       <c r="C54" s="14" t="s">
-        <v>491</v>
+        <v>485</v>
       </c>
       <c r="D54" s="14" t="s">
-        <v>493</v>
+        <v>487</v>
       </c>
       <c r="E54" s="8" t="s">
         <v>86</v>
@@ -7352,18 +7386,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:7">
       <c r="A55" s="16">
         <v>54</v>
       </c>
       <c r="B55" s="14" t="s">
-        <v>461</v>
+        <v>455</v>
       </c>
       <c r="C55" s="14" t="s">
-        <v>463</v>
+        <v>457</v>
       </c>
       <c r="D55" t="s">
-        <v>462</v>
+        <v>456</v>
       </c>
       <c r="E55" s="8" t="s">
         <v>86</v>
@@ -7372,36 +7406,36 @@
         <v>20</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:7">
       <c r="A56" s="18">
         <v>55</v>
       </c>
       <c r="B56" s="14" t="s">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="C56" s="14" t="s">
-        <v>450</v>
+        <v>444</v>
       </c>
       <c r="D56" t="s">
-        <v>465</v>
+        <v>459</v>
       </c>
       <c r="E56" s="8" t="s">
         <v>86</v>
       </c>
       <c r="F56" s="20"/>
       <c r="G56" s="8" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7">
       <c r="A57" s="19">
         <v>56</v>
       </c>
       <c r="B57" s="14" t="s">
-        <v>466</v>
+        <v>460</v>
       </c>
       <c r="C57" s="14" t="s">
-        <v>450</v>
+        <v>444</v>
       </c>
       <c r="D57" t="s">
         <v>269</v>
@@ -7413,15 +7447,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:7">
       <c r="A58" s="19">
         <v>56</v>
       </c>
       <c r="B58" s="22" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="C58" s="14" t="s">
-        <v>472</v>
+        <v>466</v>
       </c>
       <c r="D58" t="s">
         <v>269</v>
@@ -7433,15 +7467,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:7">
       <c r="A59" s="19">
         <v>56</v>
       </c>
       <c r="B59" s="22" t="s">
-        <v>468</v>
+        <v>462</v>
       </c>
       <c r="C59" s="14" t="s">
-        <v>472</v>
+        <v>466</v>
       </c>
       <c r="D59" t="s">
         <v>269</v>
@@ -7453,15 +7487,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:7">
       <c r="A60" s="19">
         <v>57</v>
       </c>
       <c r="B60" s="14" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="C60" s="14" t="s">
-        <v>472</v>
+        <v>466</v>
       </c>
       <c r="D60" t="s">
         <v>269</v>
@@ -7473,15 +7507,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:7">
       <c r="A61" s="19">
         <v>58</v>
       </c>
       <c r="B61" s="14" t="s">
-        <v>471</v>
+        <v>465</v>
       </c>
       <c r="C61" s="14" t="s">
-        <v>472</v>
+        <v>466</v>
       </c>
       <c r="D61" t="s">
         <v>269</v>
@@ -7493,15 +7527,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:7">
       <c r="A62" s="19">
         <v>59</v>
       </c>
       <c r="B62" s="14" t="s">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="C62" s="14" t="s">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="D62" t="s">
         <v>269</v>
@@ -7513,15 +7547,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:7">
       <c r="A63" s="19">
         <v>60</v>
       </c>
       <c r="B63" s="14" t="s">
-        <v>474</v>
+        <v>468</v>
       </c>
       <c r="C63" s="14" t="s">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="D63" t="s">
         <v>149</v>
@@ -7530,18 +7564,18 @@
         <v>86</v>
       </c>
       <c r="G63" s="8" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.2">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7">
       <c r="A64" s="19">
         <v>61</v>
       </c>
       <c r="B64" s="14" t="s">
-        <v>476</v>
+        <v>470</v>
       </c>
       <c r="C64" s="14" t="s">
-        <v>458</v>
+        <v>452</v>
       </c>
       <c r="D64" t="s">
         <v>269</v>
@@ -7549,20 +7583,20 @@
       <c r="E64" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="F64" s="24">
+      <c r="F64" s="18">
         <v>1</v>
       </c>
       <c r="G64" s="8"/>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:7">
       <c r="A65" s="19">
         <v>62</v>
       </c>
       <c r="B65" s="14" t="s">
-        <v>478</v>
+        <v>472</v>
       </c>
       <c r="C65" s="14" t="s">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="D65" t="s">
         <v>269</v>
@@ -7571,18 +7605,18 @@
         <v>86</v>
       </c>
       <c r="G65" s="8" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.2">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7">
       <c r="A66" s="19">
         <v>63</v>
       </c>
       <c r="B66" s="14" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="C66" s="14" t="s">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="D66" t="s">
         <v>64</v>
@@ -7595,15 +7629,15 @@
       </c>
       <c r="G66" s="8"/>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:7">
       <c r="A67" s="19">
         <v>64</v>
       </c>
       <c r="B67" s="14" t="s">
-        <v>480</v>
+        <v>474</v>
       </c>
       <c r="C67" s="23" t="s">
-        <v>458</v>
+        <v>452</v>
       </c>
       <c r="D67" t="s">
         <v>269</v>
@@ -7616,35 +7650,35 @@
       </c>
       <c r="G67" s="8"/>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:7">
       <c r="A68" s="19">
         <v>65</v>
       </c>
       <c r="B68" s="14" t="s">
-        <v>481</v>
+        <v>475</v>
       </c>
       <c r="C68" s="23" t="s">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="D68" t="s">
-        <v>497</v>
+        <v>491</v>
       </c>
       <c r="E68" s="8" t="s">
         <v>86</v>
       </c>
       <c r="G68" s="8" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.2">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7">
       <c r="A69" s="19">
         <v>66</v>
       </c>
       <c r="B69" s="14" t="s">
-        <v>482</v>
+        <v>476</v>
       </c>
       <c r="C69" s="23" t="s">
-        <v>458</v>
+        <v>452</v>
       </c>
       <c r="D69" t="s">
         <v>64</v>
@@ -7657,15 +7691,15 @@
       </c>
       <c r="G69" s="8"/>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:7">
       <c r="A70" s="19">
         <v>67</v>
       </c>
       <c r="B70" s="14" t="s">
-        <v>483</v>
+        <v>477</v>
       </c>
       <c r="C70" s="23" t="s">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="D70" t="s">
         <v>269</v>
@@ -7674,18 +7708,18 @@
         <v>86</v>
       </c>
       <c r="G70" s="8" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.2">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7">
       <c r="A71" s="19">
         <v>68</v>
       </c>
       <c r="B71" s="14" t="s">
-        <v>484</v>
+        <v>478</v>
       </c>
       <c r="C71" s="23" t="s">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="D71" t="s">
         <v>269</v>
@@ -7694,18 +7728,18 @@
         <v>86</v>
       </c>
       <c r="G71" s="8" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.2">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7">
       <c r="A72" s="19">
         <v>69</v>
       </c>
       <c r="B72" s="14" t="s">
-        <v>485</v>
+        <v>479</v>
       </c>
       <c r="C72" s="23" t="s">
-        <v>486</v>
+        <v>480</v>
       </c>
       <c r="D72" t="s">
         <v>269</v>
@@ -7718,15 +7752,15 @@
       </c>
       <c r="G72" s="8"/>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:7">
       <c r="A73" s="19">
         <v>70</v>
       </c>
       <c r="B73" s="14" t="s">
-        <v>487</v>
+        <v>481</v>
       </c>
       <c r="C73" s="23" t="s">
-        <v>486</v>
+        <v>480</v>
       </c>
       <c r="D73" t="s">
         <v>269</v>
@@ -7739,15 +7773,15 @@
       </c>
       <c r="G73" s="8"/>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:7">
       <c r="A74" s="19">
         <v>71</v>
       </c>
       <c r="B74" s="14" t="s">
-        <v>496</v>
+        <v>490</v>
       </c>
       <c r="C74" s="23" t="s">
-        <v>486</v>
+        <v>480</v>
       </c>
       <c r="D74" t="s">
         <v>269</v>
@@ -7760,18 +7794,18 @@
       </c>
       <c r="G74" s="8"/>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:7">
       <c r="A75" s="19">
         <v>72</v>
       </c>
       <c r="B75" s="14" t="s">
-        <v>488</v>
+        <v>482</v>
       </c>
       <c r="C75" s="23" t="s">
-        <v>491</v>
+        <v>485</v>
       </c>
       <c r="D75" t="s">
-        <v>495</v>
+        <v>489</v>
       </c>
       <c r="E75" s="8" t="s">
         <v>86</v>
@@ -7781,18 +7815,18 @@
       </c>
       <c r="G75" s="8"/>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:7">
       <c r="A76" s="19">
         <v>73</v>
       </c>
       <c r="B76" s="14" t="s">
+        <v>483</v>
+      </c>
+      <c r="C76" s="23" t="s">
+        <v>485</v>
+      </c>
+      <c r="D76" t="s">
         <v>489</v>
-      </c>
-      <c r="C76" s="23" t="s">
-        <v>491</v>
-      </c>
-      <c r="D76" t="s">
-        <v>495</v>
       </c>
       <c r="E76" s="8" t="s">
         <v>86</v>
@@ -7802,18 +7836,18 @@
       </c>
       <c r="G76" s="8"/>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:7">
       <c r="A77" s="19">
         <v>74</v>
       </c>
       <c r="B77" s="14" t="s">
-        <v>490</v>
+        <v>484</v>
       </c>
       <c r="C77" s="23" t="s">
-        <v>491</v>
+        <v>485</v>
       </c>
       <c r="D77" t="s">
-        <v>495</v>
+        <v>489</v>
       </c>
       <c r="E77" s="8" t="s">
         <v>86</v>
@@ -7823,15 +7857,15 @@
       </c>
       <c r="G77" s="8"/>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:7">
       <c r="A78" s="19">
         <v>75</v>
       </c>
       <c r="B78" s="14" t="s">
-        <v>494</v>
+        <v>488</v>
       </c>
       <c r="C78" s="14" t="s">
-        <v>491</v>
+        <v>485</v>
       </c>
       <c r="D78" t="s">
         <v>306</v>
@@ -7844,15 +7878,15 @@
       </c>
       <c r="G78" s="8"/>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:7">
       <c r="A79" s="19">
         <v>76</v>
       </c>
       <c r="B79" s="14" t="s">
-        <v>498</v>
+        <v>492</v>
       </c>
       <c r="C79" s="14" t="s">
-        <v>491</v>
+        <v>485</v>
       </c>
       <c r="D79" t="s">
         <v>264</v>
@@ -7865,15 +7899,15 @@
       </c>
       <c r="G79" s="8"/>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:7">
       <c r="A80" s="19">
         <v>77</v>
       </c>
       <c r="B80" s="14" t="s">
-        <v>499</v>
+        <v>493</v>
       </c>
       <c r="C80" s="14" t="s">
-        <v>491</v>
+        <v>485</v>
       </c>
       <c r="D80" t="s">
         <v>269</v>
@@ -7885,18 +7919,18 @@
         <v>1</v>
       </c>
       <c r="G80" s="8" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.2">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7">
       <c r="A81" s="19">
         <v>78</v>
       </c>
       <c r="B81" s="14" t="s">
-        <v>500</v>
+        <v>494</v>
       </c>
       <c r="C81" s="14" t="s">
-        <v>491</v>
+        <v>485</v>
       </c>
       <c r="D81" t="s">
         <v>67</v>
@@ -7908,15 +7942,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:7">
       <c r="A82" s="19">
         <v>79</v>
       </c>
       <c r="B82" s="14" t="s">
-        <v>501</v>
+        <v>495</v>
       </c>
       <c r="C82" s="14" t="s">
-        <v>491</v>
+        <v>485</v>
       </c>
       <c r="D82" t="s">
         <v>264</v>
@@ -7926,12 +7960,152 @@
       </c>
       <c r="F82">
         <v>1</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7">
+      <c r="A83" s="19">
+        <v>80</v>
+      </c>
+      <c r="B83" s="24" t="s">
+        <v>499</v>
+      </c>
+      <c r="C83" s="8" t="s">
+        <v>393</v>
+      </c>
+      <c r="D83" t="s">
+        <v>44</v>
+      </c>
+      <c r="E83" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="G83" s="8" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7">
+      <c r="A84" s="19">
+        <v>81</v>
+      </c>
+      <c r="B84" t="s">
+        <v>501</v>
+      </c>
+      <c r="C84" s="8" t="s">
+        <v>393</v>
+      </c>
+      <c r="D84" t="s">
+        <v>44</v>
+      </c>
+      <c r="E84" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="G84" s="8" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7">
+      <c r="A85" s="19">
+        <v>82</v>
+      </c>
+      <c r="B85" t="s">
+        <v>500</v>
+      </c>
+      <c r="C85" s="8" t="s">
+        <v>393</v>
+      </c>
+      <c r="D85" t="s">
+        <v>44</v>
+      </c>
+      <c r="E85" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="G85" s="8" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7">
+      <c r="A86" s="19">
+        <v>83</v>
+      </c>
+      <c r="B86" t="s">
+        <v>505</v>
+      </c>
+      <c r="C86" s="8" t="s">
+        <v>506</v>
+      </c>
+      <c r="D86" t="s">
+        <v>44</v>
+      </c>
+      <c r="E86" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G86" s="8" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7">
+      <c r="A87" s="19">
+        <v>84</v>
+      </c>
+      <c r="B87" t="s">
+        <v>507</v>
+      </c>
+      <c r="C87" s="8" t="s">
+        <v>509</v>
+      </c>
+      <c r="D87" t="s">
+        <v>44</v>
+      </c>
+      <c r="E87" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G87" s="8" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7">
+      <c r="A88" s="19">
+        <v>85</v>
+      </c>
+      <c r="B88" t="s">
+        <v>508</v>
+      </c>
+      <c r="C88" s="8" t="s">
+        <v>509</v>
+      </c>
+      <c r="D88" t="s">
+        <v>44</v>
+      </c>
+      <c r="E88" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G88" s="8" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7">
+      <c r="A89" s="19">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7">
+      <c r="A90" s="19">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7">
+      <c r="A91" s="19">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7">
+      <c r="A92" s="19">
+        <v>89</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="10" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" errorTitle="Invalid brand" error="Choose yc, staple, or shared from the list." sqref="E3:E82" xr:uid="{00000000-0002-0000-0200-000000000000}">
+    <dataValidation type="list" errorTitle="Invalid brand" error="Choose yc, staple, or shared from the list." sqref="E3:E88" xr:uid="{00000000-0002-0000-0200-000000000000}">
       <formula1>"yc,staple,shared"</formula1>
     </dataValidation>
   </dataValidations>

--- a/NCD_Brand_Tagging.xlsx
+++ b/NCD_Brand_Tagging.xlsx
@@ -7012,7 +7012,7 @@
     <row r="11" ht="20" customHeight="1" s="28">
       <c r="A11" s="34" t="inlineStr">
         <is>
-          <t>Meat  (6 รายการ · ขาด Par NCD 4)  คอลัมน์ซ้าย</t>
+          <t>Meat  (6 รายการ · ขาด Par NCD 1)  คอลัมน์ซ้าย</t>
         </is>
       </c>
       <c r="B11" s="26" t="n"/>
@@ -7029,7 +7029,7 @@
       </c>
       <c r="B12" s="20" t="inlineStr">
         <is>
-          <t>Bacon</t>
+          <t>Ham</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -7060,7 +7060,7 @@
       </c>
       <c r="B13" s="20" t="inlineStr">
         <is>
-          <t>Chicken Breast</t>
+          <t>Bacon</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
@@ -7078,12 +7078,10 @@
           <t>staple</t>
         </is>
       </c>
-      <c r="F13" s="36" t="n"/>
-      <c r="G13" s="35" t="inlineStr">
-        <is>
-          <t>ยังไม่รู้จำนวน</t>
-        </is>
-      </c>
+      <c r="F13" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="35" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="36" t="n">
@@ -7091,7 +7089,7 @@
       </c>
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>Ham</t>
+          <t>Chicken Breast</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
@@ -7109,12 +7107,10 @@
           <t>staple</t>
         </is>
       </c>
-      <c r="F14" s="36" t="n"/>
-      <c r="G14" s="35" t="inlineStr">
-        <is>
-          <t>ยังไม่รู้จำนวน</t>
-        </is>
-      </c>
+      <c r="F14" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="35" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="36" t="n">
@@ -7140,12 +7136,10 @@
           <t>staple</t>
         </is>
       </c>
-      <c r="F15" s="36" t="n"/>
-      <c r="G15" s="35" t="inlineStr">
-        <is>
-          <t>ยังไม่รู้จำนวน</t>
-        </is>
-      </c>
+      <c r="F15" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="35" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="19" t="n">
@@ -7499,7 +7493,7 @@
     <row r="29" ht="20" customHeight="1" s="28">
       <c r="A29" s="34" t="inlineStr">
         <is>
-          <t>Vegetable  (6 รายการ · ขาด Par NCD 4)  คอลัมน์ซ้าย</t>
+          <t>Vegetable  (6 รายการ)  คอลัมน์ซ้าย</t>
         </is>
       </c>
       <c r="B29" s="26" t="n"/>
@@ -7534,12 +7528,10 @@
           <t>staple</t>
         </is>
       </c>
-      <c r="F30" s="36" t="n"/>
-      <c r="G30" s="35" t="inlineStr">
-        <is>
-          <t>ยังไม่รู้จำนวน</t>
-        </is>
-      </c>
+      <c r="F30" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" s="35" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="36" t="n">
@@ -7565,12 +7557,10 @@
           <t>staple</t>
         </is>
       </c>
-      <c r="F31" s="36" t="n"/>
-      <c r="G31" s="35" t="inlineStr">
-        <is>
-          <t>ยังไม่รู้จำนวน</t>
-        </is>
-      </c>
+      <c r="F31" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" s="35" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="36" t="n">
@@ -7596,12 +7586,10 @@
           <t>staple</t>
         </is>
       </c>
-      <c r="F32" s="36" t="n"/>
-      <c r="G32" s="35" t="inlineStr">
-        <is>
-          <t>ยังไม่รู้จำนวน</t>
-        </is>
-      </c>
+      <c r="F32" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" s="35" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="36" t="n">
@@ -7627,12 +7615,10 @@
           <t>staple</t>
         </is>
       </c>
-      <c r="F33" s="36" t="n"/>
-      <c r="G33" s="35" t="inlineStr">
-        <is>
-          <t>ยังไม่รู้จำนวน</t>
-        </is>
-      </c>
+      <c r="F33" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" s="35" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="19" t="n">
@@ -7695,7 +7681,7 @@
     <row r="36" ht="20" customHeight="1" s="28">
       <c r="A36" s="34" t="inlineStr">
         <is>
-          <t>Coffee  (9 รายการ · ขาด Par NCD 1)  คอลัมน์ซ้าย</t>
+          <t>Coffee  (9 รายการ)  คอลัมน์ซ้าย</t>
         </is>
       </c>
       <c r="B36" s="26" t="n"/>
@@ -7730,7 +7716,9 @@
           <t>staple</t>
         </is>
       </c>
-      <c r="F37" s="19" t="n"/>
+      <c r="F37" s="19" t="n">
+        <v>0</v>
+      </c>
       <c r="G37" s="20" t="n"/>
     </row>
     <row r="38">
@@ -8073,7 +8061,7 @@
     <row r="50" ht="20" customHeight="1" s="28">
       <c r="A50" s="37" t="inlineStr">
         <is>
-          <t>To-Go Yogurt  (3 รายการ · ขาด Par NCD 3)  คอลัมน์ซ้าย</t>
+          <t>To-Go Yogurt  (3 รายการ)  คอลัมน์ซ้าย</t>
         </is>
       </c>
       <c r="B50" s="23" t="n"/>
@@ -8108,12 +8096,10 @@
           <t>yc</t>
         </is>
       </c>
-      <c r="F51" s="36" t="n"/>
-      <c r="G51" s="35" t="inlineStr">
-        <is>
-          <t>ยังไม่รู้จำนวน</t>
-        </is>
-      </c>
+      <c r="F51" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" s="35" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="36" t="n">
@@ -8139,12 +8125,10 @@
           <t>yc</t>
         </is>
       </c>
-      <c r="F52" s="36" t="n"/>
-      <c r="G52" s="35" t="inlineStr">
-        <is>
-          <t>ยังไม่รู้จำนวน</t>
-        </is>
-      </c>
+      <c r="F52" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" s="35" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="36" t="n">
@@ -8170,17 +8154,15 @@
           <t>yc</t>
         </is>
       </c>
-      <c r="F53" s="36" t="n"/>
-      <c r="G53" s="35" t="inlineStr">
-        <is>
-          <t>ยังไม่รู้จำนวน</t>
-        </is>
-      </c>
+      <c r="F53" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" s="35" t="n"/>
     </row>
     <row r="54" ht="20" customHeight="1" s="28">
       <c r="A54" s="37" t="inlineStr">
         <is>
-          <t>To-Go Beverage  (7 รายการ · ขาด Par NCD 2)  คอลัมน์ซ้าย</t>
+          <t>To-Go Beverage  (7 รายการ)  คอลัมน์ซ้าย</t>
         </is>
       </c>
       <c r="B54" s="23" t="n"/>
@@ -8215,12 +8197,10 @@
           <t>staple</t>
         </is>
       </c>
-      <c r="F55" s="36" t="n"/>
-      <c r="G55" s="35" t="inlineStr">
-        <is>
-          <t>ยังไม่รู้จำนวน</t>
-        </is>
-      </c>
+      <c r="F55" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G55" s="35" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="36" t="n">
@@ -8246,12 +8226,10 @@
           <t>staple</t>
         </is>
       </c>
-      <c r="F56" s="36" t="n"/>
-      <c r="G56" s="35" t="inlineStr">
-        <is>
-          <t>ยังไม่รู้จำนวน</t>
-        </is>
-      </c>
+      <c r="F56" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G56" s="35" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="19" t="n">
@@ -8401,7 +8379,7 @@
     <row r="62" ht="20" customHeight="1" s="28">
       <c r="A62" s="37" t="inlineStr">
         <is>
-          <t>To-Go Sandwich &amp; Salad  (6 รายการ · ขาด Par NCD 6)  คอลัมน์ซ้าย</t>
+          <t>To-Go Sandwich &amp; Salad  (6 รายการ)  คอลัมน์ซ้าย</t>
         </is>
       </c>
       <c r="B62" s="23" t="n"/>
@@ -8436,12 +8414,10 @@
           <t>staple</t>
         </is>
       </c>
-      <c r="F63" s="36" t="n"/>
-      <c r="G63" s="35" t="inlineStr">
-        <is>
-          <t>ยังไม่รู้จำนวน</t>
-        </is>
-      </c>
+      <c r="F63" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G63" s="35" t="n"/>
       <c r="I63" s="7" t="n"/>
     </row>
     <row r="64">
@@ -8468,7 +8444,9 @@
           <t>staple</t>
         </is>
       </c>
-      <c r="F64" s="36" t="n"/>
+      <c r="F64" s="36" t="n">
+        <v>0</v>
+      </c>
       <c r="G64" s="35" t="n"/>
       <c r="I64" s="7" t="n"/>
     </row>
@@ -8496,7 +8474,9 @@
           <t>staple</t>
         </is>
       </c>
-      <c r="F65" s="36" t="n"/>
+      <c r="F65" s="36" t="n">
+        <v>0</v>
+      </c>
       <c r="G65" s="35" t="n"/>
       <c r="I65" s="7" t="n"/>
     </row>
@@ -8524,12 +8504,10 @@
           <t>staple</t>
         </is>
       </c>
-      <c r="F66" s="36" t="n"/>
-      <c r="G66" s="35" t="inlineStr">
-        <is>
-          <t>ยังไม่รู้จำนวน</t>
-        </is>
-      </c>
+      <c r="F66" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G66" s="35" t="n"/>
       <c r="I66" s="7" t="n"/>
     </row>
     <row r="67">
@@ -8556,7 +8534,9 @@
           <t>staple</t>
         </is>
       </c>
-      <c r="F67" s="36" t="n"/>
+      <c r="F67" s="36" t="n">
+        <v>0</v>
+      </c>
       <c r="G67" s="35" t="n"/>
       <c r="I67" s="7" t="n"/>
     </row>
@@ -8584,12 +8564,10 @@
           <t>staple</t>
         </is>
       </c>
-      <c r="F68" s="36" t="n"/>
-      <c r="G68" s="35" t="inlineStr">
-        <is>
-          <t>ยังไม่รู้จำนวน</t>
-        </is>
-      </c>
+      <c r="F68" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G68" s="35" t="n"/>
       <c r="I68" s="7" t="n"/>
     </row>
     <row r="69" ht="20" customHeight="1" s="28">
@@ -8665,7 +8643,7 @@
     <row r="72" ht="20" customHeight="1" s="28">
       <c r="A72" s="37" t="inlineStr">
         <is>
-          <t>To-Go Chia Pudding  (2 รายการ · ขาด Par NCD 2)  คอลัมน์ซ้าย</t>
+          <t>To-Go Chia Pudding  (2 รายการ)  คอลัมน์ซ้าย</t>
         </is>
       </c>
       <c r="B72" s="23" t="n"/>
@@ -8700,12 +8678,10 @@
           <t>yc</t>
         </is>
       </c>
-      <c r="F73" s="36" t="n"/>
-      <c r="G73" s="35" t="inlineStr">
-        <is>
-          <t>ยังไม่รู้จำนวน</t>
-        </is>
-      </c>
+      <c r="F73" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G73" s="35" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="36" t="n">
@@ -8731,17 +8707,15 @@
           <t>yc</t>
         </is>
       </c>
-      <c r="F74" s="36" t="n"/>
-      <c r="G74" s="35" t="inlineStr">
-        <is>
-          <t>ยังไม่รู้จำนวน</t>
-        </is>
-      </c>
+      <c r="F74" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G74" s="35" t="n"/>
     </row>
     <row r="75" ht="20" customHeight="1" s="28">
       <c r="A75" s="37" t="inlineStr">
         <is>
-          <t>To-Go Overnight Oats  (1 รายการ · ขาด Par NCD 1)  คอลัมน์ซ้าย</t>
+          <t>To-Go Overnight Oats  (1 รายการ)  คอลัมน์ซ้าย</t>
         </is>
       </c>
       <c r="B75" s="23" t="n"/>
@@ -8776,12 +8750,10 @@
           <t>yc</t>
         </is>
       </c>
-      <c r="F76" s="36" t="n"/>
-      <c r="G76" s="35" t="inlineStr">
-        <is>
-          <t>ยังไม่รู้จำนวน</t>
-        </is>
-      </c>
+      <c r="F76" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G76" s="35" t="n"/>
     </row>
     <row r="77" ht="20" customHeight="1" s="28">
       <c r="A77" s="37" t="inlineStr">

--- a/NCD_Brand_Tagging.xlsx
+++ b/NCD_Brand_Tagging.xlsx
@@ -8609,7 +8609,11 @@
         </is>
       </c>
       <c r="F70" s="19" t="n"/>
-      <c r="G70" s="35" t="n"/>
+      <c r="G70" s="35" t="inlineStr">
+        <is>
+          <t>ยังไม่ขาย</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="19" t="n">

--- a/NCD_Brand_Tagging.xlsx
+++ b/NCD_Brand_Tagging.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="17">
+  <fonts count="18">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -118,6 +118,10 @@
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="FF5A2E1B"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
       <sz val="11"/>
     </font>
   </fonts>
@@ -225,7 +229,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -336,6 +340,13 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1193,7 +1204,7 @@
     <row r="2" ht="20" customHeight="1" s="28">
       <c r="A2" s="34" t="inlineStr">
         <is>
-          <t>Yogurt 1kg/Box  (9 รายการ · มีที่ NCD 2 · คอลัมน์ซ้าย)</t>
+          <t>Yogurt 1kg/Box  (9 รายการ · มีที่ NCD 3 · คอลัมน์ซ้าย)</t>
         </is>
       </c>
       <c r="B2" s="26" t="n"/>
@@ -1300,47 +1311,49 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="29" t="n">
+      <c r="A5" s="41" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="30" t="inlineStr">
+      <c r="B5" s="42" t="inlineStr">
         <is>
           <t>it-009</t>
         </is>
       </c>
-      <c r="C5" s="30" t="inlineStr">
+      <c r="C5" s="42" t="inlineStr">
         <is>
           <t>Yogurt 1kg/Box</t>
         </is>
       </c>
-      <c r="D5" s="30" t="inlineStr">
+      <c r="D5" s="42" t="inlineStr">
         <is>
           <t>Plain Yogurt (ธรรมชาติ)</t>
         </is>
       </c>
-      <c r="E5" s="31" t="n"/>
-      <c r="F5" s="30" t="inlineStr">
+      <c r="E5" s="44" t="n"/>
+      <c r="F5" s="42" t="inlineStr">
         <is>
           <t>1kg/Box</t>
         </is>
       </c>
-      <c r="G5" s="32" t="n"/>
-      <c r="H5" s="32" t="inlineStr">
-        <is>
-          <t>yc</t>
-        </is>
-      </c>
-      <c r="I5" s="29" t="n">
+      <c r="G5" s="45" t="n">
+        <v>4</v>
+      </c>
+      <c r="H5" s="45" t="inlineStr">
+        <is>
+          <t>yc</t>
+        </is>
+      </c>
+      <c r="I5" s="41" t="n">
         <v>6</v>
       </c>
-      <c r="J5" s="29" t="n">
+      <c r="J5" s="41" t="n">
         <v>6</v>
       </c>
-      <c r="K5" s="29" t="n">
+      <c r="K5" s="41" t="n">
         <v>4</v>
       </c>
-      <c r="L5" s="33" t="n"/>
-      <c r="M5" s="33" t="n"/>
+      <c r="L5" s="46" t="n"/>
+      <c r="M5" s="46" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="12" t="n">
